--- a/data/historico/semana_319.xlsx
+++ b/data/historico/semana_319.xlsx
@@ -21,17 +21,17 @@
     <sheet name="Ranking" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo Geral'!$A$2:$AC$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por Área'!$A$2:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo Geral'!$A$2:$AC$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por Área'!$A$2:$N$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Visitas Duplicadas'!$A$2:$J$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Visitas Suspeitas'!$A$2:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Visitas Negativas'!$A$2:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 15min'!$A$2:$J$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ranking'!$A$2:$E$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ranking'!$A$2:$E$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -694,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1112,124 +1112,221 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X5" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>R$ 128,76</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="n"/>
+      <c r="AA5" s="4" t="n"/>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC5" s="4" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>% Rápidas até 10%</t>
         </is>
       </c>
-      <c r="C8" s="8" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="C9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>% Rápidas entre 11% e 20%</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="C10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>% Rápidas acima de 20%</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="C11" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>⚠️ SEQUÊNCIA SUSPEITA</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Duas ou mais visitas consecutivas do mesmo agente registradas no MESMO MINUTO de chegada são marcadas como suspeitas (o e-Visita não registra segundos, então o critério de negócio de 50s de diferença equivale, na prática, a 'mesmo minuto') — sugere lançamento em lote no sistema, não visita real de campo. Colunas: 'Visitas em Sequência Suspeita' (total de visitas envolvidas) e 'Maior Sequência Suspeita' (maior número de visitas seguidas nessa condição). Na aba 'Visitas Suspeitas', a coluna 'Diferença p/ Anterior (s)*' fica em branco quando o alerta da linha veio do par com a visita SEGUINTE (não da anterior).</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>🍽️ VISITAS NO HORÁRIO DE ALMOÇO</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="70" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Coluna 'Visitas no Almoço (11h15-12h45)' conta as visitas com chegada registrada nesse intervalo — o horário oficial de almoço é 11h15 às 12h45, JÁ COM 15 MINUTOS DE TOLERÂNCIA em cada borda (visitas entre 11h-11h15 ou 12h45-13h não são tratadas como violação, só como 'fora do expediente' genérico) — use para checar se o agente está trabalhando no horário de almoço ou se há erro de lançamento. Essas visitas ficam de fora do cálculo de 'Início/Fim Manhã' e 'Início/Fim Tarde', que usam a primeira chegada e a última saída de cada dia (não a média de todos os horários), para refletir melhor o início e o fim reais do expediente.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
+          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
           <t>ℹ️ Visitas com duração NEGATIVA (saída antes da chegada — provável bug do sistema) foram excluídas do cálculo de Média/Mediana e estão detalhadas na aba 'Visitas Negativas', para investigação junto ao suporte do e-Visita.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AC4"/>
+  <autoFilter ref="A2:AC5"/>
   <mergeCells count="13">
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:AC1"/>
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A17:C17"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A20:C20"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1297,7 +1394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1424,42 +1521,60 @@
       <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
-        <is>
-          <t>TOTAL GERAL</t>
-        </is>
-      </c>
-      <c r="B5" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C5" s="29" t="n">
-        <v>23</v>
-      </c>
-      <c r="D5" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="29" t="n">
-        <v>27</v>
-      </c>
-      <c r="G5" s="29" t="n">
-        <v>14.81</v>
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="n">
+        <v>19</v>
+      </c>
+      <c r="D5" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="28" t="n">
+        <v>19</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>0</v>
       </c>
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>TOTAL GERAL</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="n">
+        <v>42</v>
+      </c>
+      <c r="D6" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="29" t="n">
+        <v>46</v>
+      </c>
+      <c r="G6" s="29" t="n">
+        <v>8.699999999999999</v>
+      </c>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
     </row>
@@ -1475,11 +1590,7 @@
       <c r="I7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
-        <is>
-          <t>DETALHE — IMÓVEIS COM VISITA RECUSADA PELO MORADOR</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="n"/>
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n"/>
@@ -1490,47 +1601,62 @@
       <c r="I8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>DETALHE — IMÓVEIS COM VISITA RECUSADA PELO MORADOR</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t>ID Visita</t>
         </is>
       </c>
-      <c r="D9" s="31" t="inlineStr">
+      <c r="D10" s="31" t="inlineStr">
         <is>
           <t>Área</t>
         </is>
       </c>
-      <c r="E9" s="31" t="inlineStr">
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t>Quarteirão</t>
         </is>
       </c>
-      <c r="F9" s="31" t="inlineStr">
+      <c r="F10" s="31" t="inlineStr">
         <is>
           <t>Logradouro</t>
         </is>
       </c>
-      <c r="G9" s="31" t="inlineStr">
+      <c r="G10" s="31" t="inlineStr">
         <is>
           <t>Imóvel</t>
         </is>
       </c>
-      <c r="H9" s="31" t="inlineStr">
+      <c r="H10" s="31" t="inlineStr">
         <is>
           <t>Data Chegada</t>
         </is>
       </c>
-      <c r="I9" s="31" t="inlineStr">
+      <c r="I10" s="31" t="inlineStr">
         <is>
           <t>Data Saída</t>
         </is>
@@ -1538,7 +1664,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="A9:I9"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1551,7 +1677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1608,16 +1734,16 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>101.2</v>
+        <v>104</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1632,30 +1758,46 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>🟢 EXCELENTE</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
           <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D5" s="4" t="n">
         <v>93.8</v>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
@@ -1667,11 +1809,7 @@
       <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="inlineStr">
-        <is>
-          <t>DETALHAMENTO — TODOS OS CRITÉRIOS APLICADOS POR AGENTE</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="n"/>
       <c r="B7" s="2" t="n"/>
       <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="n"/>
@@ -1679,87 +1817,73 @@
       <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>DETALHAMENTO — TODOS OS CRITÉRIOS APLICADOS POR AGENTE</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Critério</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Quantidade</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Peso (pontos/ocorrência)</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Pontos Aplicados</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="33" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C9" s="33" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
-      <c r="D9" s="33" t="n">
+      <c r="D10" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="33" t="n">
+      <c r="E10" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="33" t="n">
+      <c r="F10" s="33" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="34" t="inlineStr">
-        <is>
-          <t>Evelyn Santana Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="B10" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C10" s="34" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D10" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F10" s="34" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="11">
@@ -1775,17 +1899,17 @@
       </c>
       <c r="C11" s="34" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D11" s="34" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12">
@@ -1801,7 +1925,7 @@
       </c>
       <c r="C12" s="34" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D12" s="34" t="n">
@@ -1827,180 +1951,310 @@
       </c>
       <c r="C13" s="34" t="inlineStr">
         <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D13" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F13" s="34" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t>Evelyn Santana Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="inlineStr">
+        <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D13" s="34" t="n">
+      <c r="D14" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="34" t="n">
+      <c r="E14" s="34" t="n">
         <v>1.5</v>
       </c>
-      <c r="F13" s="34" t="n">
+      <c r="F14" s="34" t="n">
         <v>-9</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="33" t="inlineStr">
-        <is>
-          <t>Rozentina Matos de Oliveira</t>
-        </is>
-      </c>
-      <c r="B14" s="33" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C14" s="33" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D14" s="33" t="n">
+    <row r="15">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="33" t="n">
+      <c r="E15" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="33" t="n">
+      <c r="F15" s="33" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="34" t="inlineStr">
-        <is>
-          <t>Rozentina Matos de Oliveira</t>
-        </is>
-      </c>
-      <c r="B15" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C15" s="34" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D15" s="34" t="n">
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>Bônus: pontualidade perfeita no período</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F15" s="34" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="34" t="inlineStr">
-        <is>
-          <t>Rozentina Matos de Oliveira</t>
-        </is>
-      </c>
-      <c r="B16" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C16" s="34" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D16" s="34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="34" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F16" s="34" t="n">
-        <v>-0.6</v>
+      <c r="E16" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="34" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D17" s="34" t="n">
         <v>1</v>
       </c>
       <c r="E17" s="34" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F17" s="34" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="34" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B18" s="34" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C18" s="34" t="inlineStr">
         <is>
-          <t>Visita fora do expediente/fim de semana</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D18" s="34" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F18" s="34" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="33" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="34" t="inlineStr">
+        <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B20" s="34" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="inlineStr">
+        <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D20" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="34" t="n">
         <v>0.5</v>
       </c>
-      <c r="F18" s="34" t="n">
+      <c r="F20" s="34" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="34" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="B19" s="34" t="inlineStr">
+      <c r="B21" s="34" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C19" s="34" t="inlineStr">
+      <c r="C21" s="34" t="inlineStr">
+        <is>
+          <t>Fim tarde antes de 16h00</t>
+        </is>
+      </c>
+      <c r="D21" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F21" s="34" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="34" t="inlineStr">
+        <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B22" s="34" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C22" s="34" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D22" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F22" s="34" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="34" t="inlineStr">
+        <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B23" s="34" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="inlineStr">
+        <is>
+          <t>Visita fora do expediente/fim de semana</t>
+        </is>
+      </c>
+      <c r="D23" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F23" s="34" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="34" t="inlineStr">
+        <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B24" s="34" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="inlineStr">
         <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D19" s="34" t="n">
+      <c r="D24" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="34" t="n">
+      <c r="E24" s="34" t="n">
         <v>0.3</v>
       </c>
-      <c r="F19" s="34" t="n">
+      <c r="F24" s="34" t="n">
         <v>-0.6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E4"/>
+  <autoFilter ref="A2:E5"/>
   <mergeCells count="2">
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2012,7 +2266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2231,122 +2485,176 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>425 - JARDIM ESTORIL</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Q030, Q031, Q032</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>% Rápidas até 10%</t>
         </is>
       </c>
-      <c r="C8" s="8" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="C9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>% Rápidas entre 11% e 20%</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="C10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>% Rápidas acima de 20%</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="C11" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>⚠️ SEQUÊNCIA SUSPEITA</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Duas ou mais visitas consecutivas do mesmo agente registradas no MESMO MINUTO de chegada são marcadas como suspeitas (o e-Visita não registra segundos, então o critério de negócio de 50s de diferença equivale, na prática, a 'mesmo minuto') — sugere lançamento em lote no sistema, não visita real de campo. Colunas: 'Visitas em Sequência Suspeita' (total de visitas envolvidas) e 'Maior Sequência Suspeita' (maior número de visitas seguidas nessa condição). Na aba 'Visitas Suspeitas', a coluna 'Diferença p/ Anterior (s)*' fica em branco quando o alerta da linha veio do par com a visita SEGUINTE (não da anterior).</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>🍽️ VISITAS NO HORÁRIO DE ALMOÇO</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="70" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Coluna 'Visitas no Almoço (11h15-12h45)' conta as visitas com chegada registrada nesse intervalo — o horário oficial de almoço é 11h15 às 12h45, JÁ COM 15 MINUTOS DE TOLERÂNCIA em cada borda (visitas entre 11h-11h15 ou 12h45-13h não são tratadas como violação, só como 'fora do expediente' genérico) — use para checar se o agente está trabalhando no horário de almoço ou se há erro de lançamento. Essas visitas ficam de fora do cálculo de 'Início/Fim Manhã' e 'Início/Fim Tarde', que usam a primeira chegada e a última saída de cada dia (não a média de todos os horários), para refletir melhor o início e o fim reais do expediente.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
+          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
           <t>ℹ️ Visitas com duração NEGATIVA (saída antes da chegada — provável bug do sistema) foram excluídas do cálculo de Média/Mediana e estão detalhadas na aba 'Visitas Negativas', para investigação junto ao suporte do e-Visita.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N4"/>
+  <autoFilter ref="A2:N5"/>
   <mergeCells count="13">
     <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A17:C17"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="A20:C20"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -3250,7 +3558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3265,7 +3573,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (3 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
+          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (4 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3417,8 +3725,43 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="26" t="n">
+        <v>2721</v>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="F6" s="26" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:G5"/>
+  <autoFilter ref="A2:G6"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/data/historico/semana_319.xlsx
+++ b/data/historico/semana_319.xlsx
@@ -21,17 +21,17 @@
     <sheet name="Ranking" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo Geral'!$A$2:$AC$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por Área'!$A$2:$N$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo Geral'!$A$2:$AC$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por Área'!$A$2:$N$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Visitas Duplicadas'!$A$2:$J$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Visitas Suspeitas'!$A$2:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Visitas Negativas'!$A$2:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 15min'!$A$2:$J$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ranking'!$A$2:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ranking'!$A$2:$E$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -76,12 +76,17 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="26">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFB3B3"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -101,11 +106,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF9B0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFB3B3"/>
       </patternFill>
     </fill>
     <fill>
@@ -165,6 +165,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E0D6F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="002E5C8A"/>
       </patternFill>
     </fill>
@@ -185,12 +195,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0FFE0"/>
+        <fgColor rgb="00FFE0E0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE0E0"/>
+        <fgColor rgb="00E0FFE0"/>
       </patternFill>
     </fill>
   </fills>
@@ -233,32 +243,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -309,24 +322,30 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -694,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -913,7 +932,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Carlos Alberto Albiero</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -923,410 +942,604 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>🟢 NORMAL</t>
+          <t>🔴 CRÍTICO</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>R$ 6631,36</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AB3" s="4" t="n"/>
+      <c r="AC3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Evelyn Santana Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="E4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="G4" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="I3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" s="4" t="n">
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="U3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="4" t="n">
+      <c r="U4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5" t="n">
         <v>0.33</v>
       </c>
-      <c r="W3" s="4" t="n">
+      <c r="W4" s="5" t="n">
         <v>0.33</v>
       </c>
-      <c r="X3" s="4" t="n">
+      <c r="X4" s="5" t="n">
         <v>0.27</v>
       </c>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="Y4" s="5" t="inlineStr">
         <is>
           <t>R$ 828,92</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="n"/>
-      <c r="AA3" s="4" t="n"/>
-      <c r="AB3" s="4" t="inlineStr">
+      <c r="Z4" s="5" t="n"/>
+      <c r="AA4" s="5" t="n"/>
+      <c r="AB4" s="5" t="inlineStr">
         <is>
           <t>15:27</t>
         </is>
       </c>
-      <c r="AC3" s="4" t="inlineStr">
+      <c r="AC4" s="5" t="inlineStr">
         <is>
           <t>15:47</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G5" s="5" t="n">
         <v>4.26</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="J5" s="5" t="n">
         <v>5.26</v>
       </c>
-      <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="4" t="n">
+      <c r="K5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="R5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="S4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="4" t="n">
+      <c r="S5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="U4" s="4" t="n">
+      <c r="U5" s="5" t="n">
         <v>17.39</v>
       </c>
-      <c r="V4" s="4" t="n">
+      <c r="V5" s="5" t="n">
         <v>2.05</v>
       </c>
-      <c r="W4" s="4" t="n">
+      <c r="W5" s="5" t="n">
         <v>2.05</v>
       </c>
-      <c r="X4" s="4" t="n">
+      <c r="X5" s="5" t="n">
         <v>1.35</v>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Y5" s="5" t="inlineStr">
         <is>
           <t>R$ 163,74</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="Z5" s="5" t="inlineStr">
         <is>
           <t>09:56</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AA5" s="5" t="inlineStr">
         <is>
           <t>10:59</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr">
+      <c r="AB5" s="5" t="inlineStr">
         <is>
           <t>12:55</t>
         </is>
       </c>
-      <c r="AC4" s="4" t="inlineStr">
+      <c r="AC5" s="5" t="inlineStr">
         <is>
           <t>13:29</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" s="4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>R$ 340,07</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AB6" s="4" t="n"/>
+      <c r="AC6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D7" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F7" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G7" s="5" t="n">
         <v>5.42</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="I5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="4" t="n">
+      <c r="I7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="U5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4" t="n">
+      <c r="U7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="5" t="n">
         <v>2.22</v>
       </c>
-      <c r="W5" s="4" t="n">
+      <c r="W7" s="5" t="n">
         <v>2.22</v>
       </c>
-      <c r="X5" s="4" t="n">
+      <c r="X7" s="5" t="n">
         <v>1.72</v>
       </c>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="Y7" s="5" t="inlineStr">
         <is>
           <t>R$ 128,76</t>
         </is>
       </c>
-      <c r="Z5" s="4" t="n"/>
-      <c r="AA5" s="4" t="n"/>
-      <c r="AB5" s="4" t="inlineStr">
+      <c r="Z7" s="5" t="n"/>
+      <c r="AA7" s="5" t="n"/>
+      <c r="AB7" s="5" t="inlineStr">
         <is>
           <t>13:52</t>
         </is>
       </c>
-      <c r="AC5" s="4" t="inlineStr">
+      <c r="AC7" s="5" t="inlineStr">
         <is>
           <t>16:05</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>% Rápidas até 10%</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="C11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>% Rápidas entre 11% e 20%</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>% Rápidas acima de 20%</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="n"/>
+      <c r="C12" s="9" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>% Rápidas acima de 20%</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
           <t>⚠️ SEQUÊNCIA SUSPEITA</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Duas ou mais visitas consecutivas do mesmo agente registradas no MESMO MINUTO de chegada são marcadas como suspeitas (o e-Visita não registra segundos, então o critério de negócio de 50s de diferença equivale, na prática, a 'mesmo minuto') — sugere lançamento em lote no sistema, não visita real de campo. Colunas: 'Visitas em Sequência Suspeita' (total de visitas envolvidas) e 'Maior Sequência Suspeita' (maior número de visitas seguidas nessa condição). Na aba 'Visitas Suspeitas', a coluna 'Diferença p/ Anterior (s)*' fica em branco quando o alerta da linha veio do par com a visita SEGUINTE (não da anterior).</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>🍽️ VISITAS NO HORÁRIO DE ALMOÇO</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="70" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="19" ht="70" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Coluna 'Visitas no Almoço (11h15-12h45)' conta as visitas com chegada registrada nesse intervalo — o horário oficial de almoço é 11h15 às 12h45, JÁ COM 15 MINUTOS DE TOLERÂNCIA em cada borda (visitas entre 11h-11h15 ou 12h45-13h não são tratadas como violação, só como 'fora do expediente' genérico) — use para checar se o agente está trabalhando no horário de almoço ou se há erro de lançamento. Essas visitas ficam de fora do cálculo de 'Início/Fim Manhã' e 'Início/Fim Tarde', que usam a primeira chegada e a última saída de cada dia (não a média de todos os horários), para refletir melhor o início e o fim reais do expediente.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>ℹ️ Visitas com duração NEGATIVA (saída antes da chegada — provável bug do sistema) foram excluídas do cálculo de Média/Mediana e estão detalhadas na aba 'Visitas Negativas', para investigação junto ao suporte do e-Visita.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AC5"/>
+  <autoFilter ref="A2:AC7"/>
   <mergeCells count="13">
-    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:AC1"/>
-    <mergeCell ref="A19:C19"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="B10:C10"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A16:C16"/>
+    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1338,19 +1551,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (0 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (32 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1358,29 +1571,733 @@
       <c r="D1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="27" t="inlineStr">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>Dia Início</t>
         </is>
       </c>
-      <c r="B2" s="27" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>Dia Fim</t>
         </is>
       </c>
-      <c r="C2" s="27" t="inlineStr">
+      <c r="C2" s="28" t="inlineStr">
         <is>
           <t>Motivo</t>
         </is>
       </c>
-      <c r="D2" s="27" t="inlineStr">
+      <c r="D2" s="28" t="inlineStr">
         <is>
           <t>Quem</t>
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>23/07/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D3" s="29" t="inlineStr">
+        <is>
+          <t>Agente_3035</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D4" s="29" t="inlineStr">
+        <is>
+          <t>Agente_2951</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D5" s="29" t="inlineStr">
+        <is>
+          <t>Agente_125</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="inlineStr">
+        <is>
+          <t>Agente_81</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D7" s="30" t="inlineStr">
+        <is>
+          <t>Agente_99</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>Agente_115</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="inlineStr">
+        <is>
+          <t>Agente_134</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="inlineStr">
+        <is>
+          <t>Agente_142</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="30" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>Agente_151</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="inlineStr">
+        <is>
+          <t>Agente_465</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D14" s="30" t="inlineStr">
+        <is>
+          <t>Agente_2917</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D15" s="30" t="inlineStr">
+        <is>
+          <t>Agente_3127</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D16" s="30" t="inlineStr">
+        <is>
+          <t>Agente_113</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="inlineStr">
+        <is>
+          <t>Agente_120</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C18" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D18" s="30" t="inlineStr">
+        <is>
+          <t>Agente_1936</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D19" s="30" t="inlineStr">
+        <is>
+          <t>Agente_1938</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D20" s="30" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D21" s="30" t="inlineStr">
+        <is>
+          <t>Agente_2918</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C22" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D22" s="30" t="inlineStr">
+        <is>
+          <t>Agente_3038</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C23" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D23" s="30" t="inlineStr">
+        <is>
+          <t>Agente_3128</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C24" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D24" s="30" t="inlineStr">
+        <is>
+          <t>Agente_80</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C25" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D25" s="30" t="inlineStr">
+        <is>
+          <t>Agente_86</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C26" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D26" s="30" t="inlineStr">
+        <is>
+          <t>Agente_110</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C27" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D27" s="30" t="inlineStr">
+        <is>
+          <t>Agente_124</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C28" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D28" s="30" t="inlineStr">
+        <is>
+          <t>Agente_149</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C29" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D29" s="30" t="inlineStr">
+        <is>
+          <t>Agente_157</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C30" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D30" s="30" t="inlineStr">
+        <is>
+          <t>Agente_161</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C31" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D31" s="30" t="inlineStr">
+        <is>
+          <t>Agente_1942</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C32" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D32" s="30" t="inlineStr">
+        <is>
+          <t>Agente_1943</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C33" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D33" s="30" t="inlineStr">
+        <is>
+          <t>Agente_1996</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C34" s="30" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D34" s="30" t="inlineStr">
+        <is>
+          <t>Agente_2789</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:D2"/>
+  <autoFilter ref="A2:D34"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -1394,7 +2311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1463,149 +2380,181 @@
       <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="inlineStr">
-        <is>
-          <t>Evelyn Santana Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="B3" s="28" t="inlineStr">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>Carlos Alberto Albiero</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C3" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" s="28" t="n">
+      <c r="C3" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="31" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
-        <is>
-          <t>Rozentina Matos de Oliveira</t>
-        </is>
-      </c>
-      <c r="B4" s="28" t="inlineStr">
+      <c r="A4" s="31" t="inlineStr">
+        <is>
+          <t>Evelyn Santana Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n">
-        <v>19</v>
-      </c>
-      <c r="D4" s="28" t="n">
+      <c r="C4" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="E4" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="28" t="n">
-        <v>23</v>
-      </c>
-      <c r="G4" s="28" t="n">
-        <v>17.39</v>
+      <c r="D4" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="31" t="n">
+        <v>0</v>
       </c>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="inlineStr">
-        <is>
-          <t>Miglidiane Maciel Ajala</t>
-        </is>
-      </c>
-      <c r="B5" s="28" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C5" s="28" t="n">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="D5" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <v>19</v>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>0</v>
+      <c r="D5" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="31" t="n">
+        <v>23</v>
+      </c>
+      <c r="G5" s="31" t="n">
+        <v>17.39</v>
       </c>
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
-        <is>
-          <t>TOTAL GERAL</t>
-        </is>
-      </c>
-      <c r="B6" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C6" s="29" t="n">
-        <v>42</v>
-      </c>
-      <c r="D6" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="29" t="n">
-        <v>46</v>
-      </c>
-      <c r="G6" s="29" t="n">
-        <v>8.699999999999999</v>
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>14</v>
+      </c>
+      <c r="D6" s="31" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="31" t="n">
+        <v>28</v>
+      </c>
+      <c r="G6" s="31" t="n">
+        <v>50</v>
       </c>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>19</v>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="31" t="n">
+        <v>19</v>
+      </c>
+      <c r="G7" s="31" t="n">
+        <v>0</v>
+      </c>
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL GERAL</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="n">
+        <v>57</v>
+      </c>
+      <c r="D8" s="32" t="n">
+        <v>18</v>
+      </c>
+      <c r="E8" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="32" t="n">
+        <v>75</v>
+      </c>
+      <c r="G8" s="32" t="n">
+        <v>24</v>
+      </c>
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="inlineStr">
-        <is>
-          <t>DETALHE — IMÓVEIS COM VISITA RECUSADA PELO MORADOR</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="n"/>
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
@@ -1616,47 +2565,73 @@
       <c r="I9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>DETALHE — IMÓVEIS COM VISITA RECUSADA PELO MORADOR</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="B10" s="31" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>ID Visita</t>
         </is>
       </c>
-      <c r="D10" s="31" t="inlineStr">
+      <c r="D12" s="34" t="inlineStr">
         <is>
           <t>Área</t>
         </is>
       </c>
-      <c r="E10" s="31" t="inlineStr">
+      <c r="E12" s="34" t="inlineStr">
         <is>
           <t>Quarteirão</t>
         </is>
       </c>
-      <c r="F10" s="31" t="inlineStr">
+      <c r="F12" s="34" t="inlineStr">
         <is>
           <t>Logradouro</t>
         </is>
       </c>
-      <c r="G10" s="31" t="inlineStr">
+      <c r="G12" s="34" t="inlineStr">
         <is>
           <t>Imóvel</t>
         </is>
       </c>
-      <c r="H10" s="31" t="inlineStr">
+      <c r="H12" s="34" t="inlineStr">
         <is>
           <t>Data Chegada</t>
         </is>
       </c>
-      <c r="I10" s="31" t="inlineStr">
+      <c r="I12" s="34" t="inlineStr">
         <is>
           <t>Data Saída</t>
         </is>
@@ -1664,8 +2639,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:I9"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A11:I11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1677,7 +2652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1729,23 +2704,23 @@
       <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="5" t="n">
         <v>104</v>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -1753,23 +2728,23 @@
       <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>101.2</v>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -1777,51 +2752,79 @@
       <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Carlos Alberto Albiero</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>🟢 EXCELENTE</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <v>93.8</v>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
+      <c r="A7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>🟢 EXCELENTE</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
-        <is>
-          <t>DETALHAMENTO — TODOS OS CRITÉRIOS APLICADOS POR AGENTE</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="n"/>
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n"/>
@@ -1829,432 +2832,660 @@
       <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="inlineStr">
+        <is>
+          <t>DETALHAMENTO — TODOS OS CRITÉRIOS APLICADOS POR AGENTE</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Critério</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Quantidade</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Peso (pontos/ocorrência)</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Pontos Aplicados</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="33" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="36" t="inlineStr">
+        <is>
+          <t>Carlos Alberto Albiero</t>
+        </is>
+      </c>
+      <c r="B12" s="36" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="inlineStr">
+        <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D12" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F12" s="36" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="36" t="inlineStr">
+        <is>
+          <t>Carlos Alberto Albiero</t>
+        </is>
+      </c>
+      <c r="B13" s="36" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D13" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F13" s="36" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="36" t="inlineStr">
+        <is>
+          <t>Carlos Alberto Albiero</t>
+        </is>
+      </c>
+      <c r="B14" s="36" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C14" s="36" t="inlineStr">
+        <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D14" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F14" s="36" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="36" t="inlineStr">
+        <is>
+          <t>Carlos Alberto Albiero</t>
+        </is>
+      </c>
+      <c r="B15" s="36" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C15" s="36" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D15" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F15" s="36" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="37" t="inlineStr">
         <is>
           <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
-      <c r="B10" s="33" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C10" s="33" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
-      <c r="D10" s="33" t="n">
+      <c r="D16" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="33" t="n">
+      <c r="E16" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="33" t="n">
+      <c r="F16" s="37" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C17" s="36" t="inlineStr">
         <is>
           <t>Dia sem bater a meta diária</t>
         </is>
       </c>
-      <c r="D11" s="34" t="n">
+      <c r="D17" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="34" t="n">
+      <c r="E17" s="36" t="n">
         <v>0.5</v>
       </c>
-      <c r="F11" s="34" t="n">
+      <c r="F17" s="36" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C18" s="36" t="inlineStr">
         <is>
           <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
-      <c r="D12" s="34" t="n">
+      <c r="D18" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="34" t="n">
+      <c r="E18" s="36" t="n">
         <v>0.3</v>
       </c>
-      <c r="F12" s="34" t="n">
+      <c r="F18" s="36" t="n">
         <v>-0.6</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C19" s="36" t="inlineStr">
         <is>
           <t>Início tarde após 14h30</t>
         </is>
       </c>
-      <c r="D13" s="34" t="n">
+      <c r="D19" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="34" t="n">
+      <c r="E19" s="36" t="n">
         <v>0.3</v>
       </c>
-      <c r="F13" s="34" t="n">
+      <c r="F19" s="36" t="n">
         <v>-0.6</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B20" s="36" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C20" s="36" t="inlineStr">
         <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D14" s="34" t="n">
+      <c r="D20" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="34" t="n">
+      <c r="E20" s="36" t="n">
         <v>1.5</v>
       </c>
-      <c r="F14" s="34" t="n">
+      <c r="F20" s="36" t="n">
         <v>-9</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="33" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="36" t="inlineStr">
+        <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+      <c r="B21" s="36" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C21" s="36" t="inlineStr">
+        <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D21" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F21" s="36" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="36" t="inlineStr">
+        <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+      <c r="B22" s="36" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C22" s="36" t="inlineStr">
+        <is>
+          <t>Fim manhã antes de 10h00</t>
+        </is>
+      </c>
+      <c r="D22" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F22" s="36" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="36" t="inlineStr">
+        <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+      <c r="B23" s="36" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C23" s="36" t="inlineStr">
+        <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D23" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F23" s="36" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="36" t="inlineStr">
+        <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+      <c r="B24" s="36" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C24" s="36" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D24" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="E24" s="36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F24" s="36" t="n">
+        <v>-4.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="37" t="inlineStr">
         <is>
           <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
-      <c r="B15" s="33" t="inlineStr">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C15" s="33" t="inlineStr">
+      <c r="C25" s="37" t="inlineStr">
         <is>
           <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
-      <c r="D15" s="33" t="n">
+      <c r="D25" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="33" t="n">
+      <c r="E25" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="33" t="n">
+      <c r="F25" s="37" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="33" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="37" t="inlineStr">
         <is>
           <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B26" s="37" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C16" s="33" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr">
         <is>
           <t>Bônus: pontualidade perfeita no período</t>
         </is>
       </c>
-      <c r="D16" s="33" t="n">
+      <c r="D26" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="33" t="n">
+      <c r="E26" s="37" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="33" t="n">
+      <c r="F26" s="37" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
-      <c r="B17" s="34" t="inlineStr">
+      <c r="B27" s="36" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C17" s="34" t="inlineStr">
+      <c r="C27" s="36" t="inlineStr">
         <is>
           <t>Dia sem bater a meta diária</t>
         </is>
       </c>
-      <c r="D17" s="34" t="n">
+      <c r="D27" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="34" t="n">
+      <c r="E27" s="36" t="n">
         <v>0.5</v>
       </c>
-      <c r="F17" s="34" t="n">
+      <c r="F27" s="36" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B28" s="36" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C18" s="34" t="inlineStr">
+      <c r="C28" s="36" t="inlineStr">
         <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D18" s="34" t="n">
+      <c r="D28" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="34" t="n">
+      <c r="E28" s="36" t="n">
         <v>1.5</v>
       </c>
-      <c r="F18" s="34" t="n">
+      <c r="F28" s="36" t="n">
         <v>-3</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="33" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="37" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="B19" s="33" t="inlineStr">
+      <c r="B29" s="37" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C19" s="33" t="inlineStr">
+      <c r="C29" s="37" t="inlineStr">
         <is>
           <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
-      <c r="D19" s="33" t="n">
+      <c r="D29" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="33" t="n">
+      <c r="E29" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="F19" s="33" t="n">
+      <c r="F29" s="37" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="34" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="B20" s="34" t="inlineStr">
+      <c r="B30" s="36" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C20" s="34" t="inlineStr">
+      <c r="C30" s="36" t="inlineStr">
         <is>
           <t>Dia sem bater a meta diária</t>
         </is>
       </c>
-      <c r="D20" s="34" t="n">
+      <c r="D30" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="34" t="n">
+      <c r="E30" s="36" t="n">
         <v>0.5</v>
       </c>
-      <c r="F20" s="34" t="n">
+      <c r="F30" s="36" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="34" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="B21" s="34" t="inlineStr">
+      <c r="B31" s="36" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C21" s="34" t="inlineStr">
+      <c r="C31" s="36" t="inlineStr">
         <is>
           <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
-      <c r="D21" s="34" t="n">
+      <c r="D31" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="34" t="n">
+      <c r="E31" s="36" t="n">
         <v>0.3</v>
       </c>
-      <c r="F21" s="34" t="n">
+      <c r="F31" s="36" t="n">
         <v>-0.6</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="34" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="B22" s="34" t="inlineStr">
+      <c r="B32" s="36" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C22" s="34" t="inlineStr">
+      <c r="C32" s="36" t="inlineStr">
         <is>
           <t>Início manhã após 08h30</t>
         </is>
       </c>
-      <c r="D22" s="34" t="n">
+      <c r="D32" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="34" t="n">
+      <c r="E32" s="36" t="n">
         <v>0.3</v>
       </c>
-      <c r="F22" s="34" t="n">
+      <c r="F32" s="36" t="n">
         <v>-0.6</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="34" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="B23" s="34" t="inlineStr">
+      <c r="B33" s="36" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C23" s="34" t="inlineStr">
+      <c r="C33" s="36" t="inlineStr">
         <is>
           <t>Visita fora do expediente/fim de semana</t>
         </is>
       </c>
-      <c r="D23" s="34" t="n">
+      <c r="D33" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="34" t="n">
+      <c r="E33" s="36" t="n">
         <v>0.5</v>
       </c>
-      <c r="F23" s="34" t="n">
+      <c r="F33" s="36" t="n">
         <v>-1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="34" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="B24" s="34" t="inlineStr">
+      <c r="B34" s="36" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C24" s="34" t="inlineStr">
+      <c r="C34" s="36" t="inlineStr">
         <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D24" s="34" t="n">
+      <c r="D34" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="34" t="n">
+      <c r="E34" s="36" t="n">
         <v>0.3</v>
       </c>
-      <c r="F24" s="34" t="n">
+      <c r="F34" s="36" t="n">
         <v>-0.6</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E5"/>
+  <autoFilter ref="A2:E7"/>
   <mergeCells count="2">
-    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2266,7 +3497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2282,7 +3513,7 @@
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -2306,72 +3537,72 @@
       <c r="N1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" s="17" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
+      <c r="C2" s="17" t="inlineStr">
         <is>
           <t>Área</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>Qtd Imóveis Abertos</t>
         </is>
       </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="E2" s="17" t="inlineStr">
         <is>
           <t>Tempo Médio (min)</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>Mediana (min)</t>
         </is>
       </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="G2" s="17" t="inlineStr">
         <is>
           <t>Qtd Quarteirões</t>
         </is>
       </c>
-      <c r="H2" s="16" t="inlineStr">
+      <c r="H2" s="17" t="inlineStr">
         <is>
           <t>Quarteirões</t>
         </is>
       </c>
-      <c r="I2" s="16" t="inlineStr">
+      <c r="I2" s="17" t="inlineStr">
         <is>
           <t>Rápidas</t>
         </is>
       </c>
-      <c r="J2" s="16" t="inlineStr">
+      <c r="J2" s="17" t="inlineStr">
         <is>
           <t>% Rápidas</t>
         </is>
       </c>
-      <c r="K2" s="16" t="inlineStr">
+      <c r="K2" s="17" t="inlineStr">
         <is>
           <t>Qtd Fechados</t>
         </is>
       </c>
-      <c r="L2" s="16" t="inlineStr">
+      <c r="L2" s="17" t="inlineStr">
         <is>
           <t>Qtd Recusados</t>
         </is>
       </c>
-      <c r="M2" s="16" t="inlineStr">
+      <c r="M2" s="17" t="inlineStr">
         <is>
           <t>% Pendência</t>
         </is>
       </c>
-      <c r="N2" s="16" t="inlineStr">
+      <c r="N2" s="17" t="inlineStr">
         <is>
           <t>Alerta</t>
         </is>
@@ -2380,283 +3611,391 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
+          <t>Carlos Alberto Albiero</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>409 - ANDREAZZA</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Q022</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
           <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E4" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>3.5</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Q001, Q012</t>
         </is>
       </c>
-      <c r="I3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="I4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <v>4.26</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Q019, Q034, Q035</t>
         </is>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="J5" s="5" t="n">
         <v>5.26</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="K5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="L4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="4" t="n">
+      <c r="L5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5" t="n">
         <v>17.39</v>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>415 - CENTRO 1</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Q001, Q009, Q010</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D7" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E7" s="5" t="n">
         <v>5.42</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Q030, Q031, Q032</t>
         </is>
       </c>
-      <c r="I5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="I7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>% Rápidas até 10%</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="C11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>% Rápidas entre 11% e 20%</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>% Rápidas acima de 20%</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="n"/>
+      <c r="C12" s="9" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>% Rápidas acima de 20%</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
           <t>⚠️ SEQUÊNCIA SUSPEITA</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Duas ou mais visitas consecutivas do mesmo agente registradas no MESMO MINUTO de chegada são marcadas como suspeitas (o e-Visita não registra segundos, então o critério de negócio de 50s de diferença equivale, na prática, a 'mesmo minuto') — sugere lançamento em lote no sistema, não visita real de campo. Colunas: 'Visitas em Sequência Suspeita' (total de visitas envolvidas) e 'Maior Sequência Suspeita' (maior número de visitas seguidas nessa condição). Na aba 'Visitas Suspeitas', a coluna 'Diferença p/ Anterior (s)*' fica em branco quando o alerta da linha veio do par com a visita SEGUINTE (não da anterior).</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>🍽️ VISITAS NO HORÁRIO DE ALMOÇO</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="70" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="19" ht="70" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Coluna 'Visitas no Almoço (11h15-12h45)' conta as visitas com chegada registrada nesse intervalo — o horário oficial de almoço é 11h15 às 12h45, JÁ COM 15 MINUTOS DE TOLERÂNCIA em cada borda (visitas entre 11h-11h15 ou 12h45-13h não são tratadas como violação, só como 'fora do expediente' genérico) — use para checar se o agente está trabalhando no horário de almoço ou se há erro de lançamento. Essas visitas ficam de fora do cálculo de 'Início/Fim Manhã' e 'Início/Fim Tarde', que usam a primeira chegada e a última saída de cada dia (não a média de todos os horários), para refletir melhor o início e o fim reais do expediente.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>ℹ️ Visitas com duração NEGATIVA (saída antes da chegada — provável bug do sistema) foram excluídas do cálculo de Média/Mediana e estão detalhadas na aba 'Visitas Negativas', para investigação junto ao suporte do e-Visita.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N5"/>
+  <autoFilter ref="A2:N7"/>
   <mergeCells count="13">
-    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="B10:C10"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="B12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2700,52 +4039,52 @@
       <c r="J1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
         <is>
           <t>ID Visita</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="18" t="inlineStr">
         <is>
           <t>Área</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="18" t="inlineStr">
         <is>
           <t>Quarteirão</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="18" t="inlineStr">
         <is>
           <t>Logradouro</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="G2" s="18" t="inlineStr">
         <is>
           <t>Imóvel</t>
         </is>
       </c>
-      <c r="H2" s="17" t="inlineStr">
+      <c r="H2" s="18" t="inlineStr">
         <is>
           <t>Data Chegada</t>
         </is>
       </c>
-      <c r="I2" s="17" t="inlineStr">
+      <c r="I2" s="18" t="inlineStr">
         <is>
           <t>Data Saída</t>
         </is>
       </c>
-      <c r="J2" s="17" t="inlineStr">
+      <c r="J2" s="18" t="inlineStr">
         <is>
           <t>Motivo</t>
         </is>
@@ -2800,159 +4139,159 @@
       <c r="K1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>Cadeia</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>ID Visita</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>Área</t>
         </is>
       </c>
-      <c r="F2" s="18" t="inlineStr">
+      <c r="F2" s="19" t="inlineStr">
         <is>
           <t>Quarteirão</t>
         </is>
       </c>
-      <c r="G2" s="18" t="inlineStr">
+      <c r="G2" s="19" t="inlineStr">
         <is>
           <t>Logradouro</t>
         </is>
       </c>
-      <c r="H2" s="18" t="inlineStr">
+      <c r="H2" s="19" t="inlineStr">
         <is>
           <t>Imóvel</t>
         </is>
       </c>
-      <c r="I2" s="18" t="inlineStr">
+      <c r="I2" s="19" t="inlineStr">
         <is>
           <t>Data Chegada</t>
         </is>
       </c>
-      <c r="J2" s="18" t="inlineStr">
+      <c r="J2" s="19" t="inlineStr">
         <is>
           <t>Data Saída</t>
         </is>
       </c>
-      <c r="K2" s="18" t="inlineStr">
+      <c r="K2" s="19" t="inlineStr">
         <is>
           <t>Diferença p/ Anterior (s)*</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>% Rápidas até 10%</t>
         </is>
       </c>
-      <c r="C6" s="8" t="n"/>
+      <c r="C6" s="9" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>% Rápidas entre 11% e 20%</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>% Rápidas acima de 20%</t>
         </is>
       </c>
-      <c r="C8" s="8" t="n"/>
+      <c r="C8" s="9" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>⚠️ SEQUÊNCIA SUSPEITA</t>
         </is>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Duas ou mais visitas consecutivas do mesmo agente registradas no MESMO MINUTO de chegada são marcadas como suspeitas (o e-Visita não registra segundos, então o critério de negócio de 50s de diferença equivale, na prática, a 'mesmo minuto') — sugere lançamento em lote no sistema, não visita real de campo. Colunas: 'Visitas em Sequência Suspeita' (total de visitas envolvidas) e 'Maior Sequência Suspeita' (maior número de visitas seguidas nessa condição). Na aba 'Visitas Suspeitas', a coluna 'Diferença p/ Anterior (s)*' fica em branco quando o alerta da linha veio do par com a visita SEGUINTE (não da anterior).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>🍽️ VISITAS NO HORÁRIO DE ALMOÇO</t>
         </is>
       </c>
     </row>
     <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Coluna 'Visitas no Almoço (11h15-12h45)' conta as visitas com chegada registrada nesse intervalo — o horário oficial de almoço é 11h15 às 12h45, JÁ COM 15 MINUTOS DE TOLERÂNCIA em cada borda (visitas entre 11h-11h15 ou 12h45-13h não são tratadas como violação, só como 'fora do expediente' genérico) — use para checar se o agente está trabalhando no horário de almoço ou se há erro de lançamento. Essas visitas ficam de fora do cálculo de 'Início/Fim Manhã' e 'Início/Fim Tarde', que usam a primeira chegada e a última saída de cada dia (não a média de todos os horários), para refletir melhor o início e o fim reais do expediente.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
         </is>
       </c>
     </row>
     <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>ℹ️ Visitas com duração NEGATIVA (saída antes da chegada — provável bug do sistema) foram excluídas do cálculo de Média/Mediana e estão detalhadas na aba 'Visitas Negativas', para investigação junto ao suporte do e-Visita.</t>
         </is>
@@ -3019,159 +4358,159 @@
       <c r="K1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="B2" s="19" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="C2" s="19" t="inlineStr">
+      <c r="C2" s="20" t="inlineStr">
         <is>
           <t>ID Visita</t>
         </is>
       </c>
-      <c r="D2" s="19" t="inlineStr">
+      <c r="D2" s="20" t="inlineStr">
         <is>
           <t>Área</t>
         </is>
       </c>
-      <c r="E2" s="19" t="inlineStr">
+      <c r="E2" s="20" t="inlineStr">
         <is>
           <t>Quarteirão</t>
         </is>
       </c>
-      <c r="F2" s="19" t="inlineStr">
+      <c r="F2" s="20" t="inlineStr">
         <is>
           <t>Logradouro</t>
         </is>
       </c>
-      <c r="G2" s="19" t="inlineStr">
+      <c r="G2" s="20" t="inlineStr">
         <is>
           <t>Imóvel</t>
         </is>
       </c>
-      <c r="H2" s="19" t="inlineStr">
+      <c r="H2" s="20" t="inlineStr">
         <is>
           <t>Data Chegada</t>
         </is>
       </c>
-      <c r="I2" s="19" t="inlineStr">
+      <c r="I2" s="20" t="inlineStr">
         <is>
           <t>Data Saída</t>
         </is>
       </c>
-      <c r="J2" s="19" t="inlineStr">
+      <c r="J2" s="20" t="inlineStr">
         <is>
           <t>Duração (min)</t>
         </is>
       </c>
-      <c r="K2" s="19" t="inlineStr">
+      <c r="K2" s="20" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>% Rápidas até 10%</t>
         </is>
       </c>
-      <c r="C6" s="8" t="n"/>
+      <c r="C6" s="9" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>% Rápidas entre 11% e 20%</t>
         </is>
       </c>
-      <c r="C7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>% Rápidas acima de 20%</t>
         </is>
       </c>
-      <c r="C8" s="8" t="n"/>
+      <c r="C8" s="9" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>⚠️ SEQUÊNCIA SUSPEITA</t>
         </is>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Duas ou mais visitas consecutivas do mesmo agente registradas no MESMO MINUTO de chegada são marcadas como suspeitas (o e-Visita não registra segundos, então o critério de negócio de 50s de diferença equivale, na prática, a 'mesmo minuto') — sugere lançamento em lote no sistema, não visita real de campo. Colunas: 'Visitas em Sequência Suspeita' (total de visitas envolvidas) e 'Maior Sequência Suspeita' (maior número de visitas seguidas nessa condição). Na aba 'Visitas Suspeitas', a coluna 'Diferença p/ Anterior (s)*' fica em branco quando o alerta da linha veio do par com a visita SEGUINTE (não da anterior).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>🍽️ VISITAS NO HORÁRIO DE ALMOÇO</t>
         </is>
       </c>
     </row>
     <row r="14" ht="70" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Coluna 'Visitas no Almoço (11h15-12h45)' conta as visitas com chegada registrada nesse intervalo — o horário oficial de almoço é 11h15 às 12h45, JÁ COM 15 MINUTOS DE TOLERÂNCIA em cada borda (visitas entre 11h-11h15 ou 12h45-13h não são tratadas como violação, só como 'fora do expediente' genérico) — use para checar se o agente está trabalhando no horário de almoço ou se há erro de lançamento. Essas visitas ficam de fora do cálculo de 'Início/Fim Manhã' e 'Início/Fim Tarde', que usam a primeira chegada e a última saída de cada dia (não a média de todos os horários), para refletir melhor o início e o fim reais do expediente.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
         </is>
       </c>
     </row>
     <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>ℹ️ Visitas com duração NEGATIVA (saída antes da chegada — provável bug do sistema) foram excluídas do cálculo de Média/Mediana e estão detalhadas na aba 'Visitas Negativas', para investigação junto ao suporte do e-Visita.</t>
         </is>
@@ -3236,52 +4575,52 @@
       <c r="J1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="B2" s="20" t="inlineStr">
+      <c r="B2" s="21" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="C2" s="20" t="inlineStr">
+      <c r="C2" s="21" t="inlineStr">
         <is>
           <t>ID Visita</t>
         </is>
       </c>
-      <c r="D2" s="20" t="inlineStr">
+      <c r="D2" s="21" t="inlineStr">
         <is>
           <t>Área</t>
         </is>
       </c>
-      <c r="E2" s="20" t="inlineStr">
+      <c r="E2" s="21" t="inlineStr">
         <is>
           <t>Quarteirão</t>
         </is>
       </c>
-      <c r="F2" s="20" t="inlineStr">
+      <c r="F2" s="21" t="inlineStr">
         <is>
           <t>Logradouro</t>
         </is>
       </c>
-      <c r="G2" s="20" t="inlineStr">
+      <c r="G2" s="21" t="inlineStr">
         <is>
           <t>Imóvel</t>
         </is>
       </c>
-      <c r="H2" s="20" t="inlineStr">
+      <c r="H2" s="21" t="inlineStr">
         <is>
           <t>Data Chegada</t>
         </is>
       </c>
-      <c r="I2" s="20" t="inlineStr">
+      <c r="I2" s="21" t="inlineStr">
         <is>
           <t>Data Saída</t>
         </is>
       </c>
-      <c r="J2" s="20" t="inlineStr">
+      <c r="J2" s="21" t="inlineStr">
         <is>
           <t>Duração (min)</t>
         </is>
@@ -3336,114 +4675,114 @@
       <c r="K1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="C2" s="21" t="inlineStr">
+      <c r="C2" s="22" t="inlineStr">
         <is>
           <t>ID Visita</t>
         </is>
       </c>
-      <c r="D2" s="21" t="inlineStr">
+      <c r="D2" s="22" t="inlineStr">
         <is>
           <t>Dia da Semana</t>
         </is>
       </c>
-      <c r="E2" s="21" t="inlineStr">
+      <c r="E2" s="22" t="inlineStr">
         <is>
           <t>Área</t>
         </is>
       </c>
-      <c r="F2" s="21" t="inlineStr">
+      <c r="F2" s="22" t="inlineStr">
         <is>
           <t>Quarteirão</t>
         </is>
       </c>
-      <c r="G2" s="21" t="inlineStr">
+      <c r="G2" s="22" t="inlineStr">
         <is>
           <t>Logradouro</t>
         </is>
       </c>
-      <c r="H2" s="21" t="inlineStr">
+      <c r="H2" s="22" t="inlineStr">
         <is>
           <t>Imóvel</t>
         </is>
       </c>
-      <c r="I2" s="21" t="inlineStr">
+      <c r="I2" s="22" t="inlineStr">
         <is>
           <t>Data Chegada</t>
         </is>
       </c>
-      <c r="J2" s="21" t="inlineStr">
+      <c r="J2" s="22" t="inlineStr">
         <is>
           <t>Data Saída</t>
         </is>
       </c>
-      <c r="K2" s="21" t="inlineStr">
+      <c r="K2" s="22" t="inlineStr">
         <is>
           <t>Motivo</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>16847477</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="23" t="inlineStr">
         <is>
           <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
-      <c r="F3" s="22" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t>Q019</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="23" t="inlineStr">
         <is>
           <t>Rua CORONEL PONCE</t>
         </is>
       </c>
-      <c r="H3" s="22" t="inlineStr">
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t>562 - R</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="23" t="inlineStr">
         <is>
           <t>11/08/2026 12:55</t>
         </is>
       </c>
-      <c r="J3" s="22" t="inlineStr">
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t>11/08/2026 12:58</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="23" t="inlineStr">
         <is>
           <t>Fora do expediente (próximo ao horário de almoço, dentro da tolerância de 15min)</t>
         </is>
@@ -3497,47 +4836,47 @@
       <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="B2" s="24" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="C2" s="24" t="inlineStr">
+      <c r="C2" s="25" t="inlineStr">
         <is>
           <t>ID Visita</t>
         </is>
       </c>
-      <c r="D2" s="24" t="inlineStr">
+      <c r="D2" s="25" t="inlineStr">
         <is>
           <t>Área</t>
         </is>
       </c>
-      <c r="E2" s="24" t="inlineStr">
+      <c r="E2" s="25" t="inlineStr">
         <is>
           <t>Quarteirão</t>
         </is>
       </c>
-      <c r="F2" s="24" t="inlineStr">
+      <c r="F2" s="25" t="inlineStr">
         <is>
           <t>Logradouro</t>
         </is>
       </c>
-      <c r="G2" s="24" t="inlineStr">
+      <c r="G2" s="25" t="inlineStr">
         <is>
           <t>Imóvel</t>
         </is>
       </c>
-      <c r="H2" s="24" t="inlineStr">
+      <c r="H2" s="25" t="inlineStr">
         <is>
           <t>Data Chegada</t>
         </is>
       </c>
-      <c r="I2" s="24" t="inlineStr">
+      <c r="I2" s="25" t="inlineStr">
         <is>
           <t>Data Saída</t>
         </is>
@@ -3558,7 +4897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3573,7 +4912,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (4 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
+          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (6 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3584,184 +4923,254 @@
       <c r="G1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>ID Agente</t>
         </is>
       </c>
-      <c r="B2" s="25" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="C2" s="25" t="inlineStr">
+      <c r="C2" s="26" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="D2" s="25" t="inlineStr">
+      <c r="D2" s="26" t="inlineStr">
         <is>
           <t>Dia</t>
         </is>
       </c>
-      <c r="E2" s="25" t="inlineStr">
+      <c r="E2" s="26" t="inlineStr">
         <is>
           <t>Dia da Semana</t>
         </is>
       </c>
-      <c r="F2" s="25" t="inlineStr">
+      <c r="F2" s="26" t="inlineStr">
         <is>
           <t>Turno</t>
         </is>
       </c>
-      <c r="G2" s="25" t="inlineStr">
+      <c r="G2" s="26" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="n">
+      <c r="A3" s="27" t="n">
         <v>3037</v>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="27" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D3" s="26" t="inlineStr">
+      <c r="D3" s="27" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="E3" s="26" t="inlineStr">
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t>Segunda</t>
         </is>
       </c>
-      <c r="F3" s="26" t="inlineStr">
+      <c r="F3" s="27" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G3" s="26" t="inlineStr">
+      <c r="G3" s="27" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="n">
+      <c r="A4" s="27" t="n">
         <v>3037</v>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="27" t="inlineStr">
         <is>
           <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D4" s="26" t="inlineStr">
+      <c r="D4" s="27" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E4" s="26" t="inlineStr">
+      <c r="E4" s="27" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F4" s="26" t="inlineStr">
+      <c r="F4" s="27" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="n">
+      <c r="A5" s="27" t="n">
+        <v>3101</v>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>Carlos Alberto Albiero</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G5" s="27" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="n">
         <v>3037</v>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D5" s="26" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E5" s="26" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F5" s="26" t="inlineStr">
+      <c r="F6" s="27" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="26" t="n">
+    <row r="7">
+      <c r="A7" s="27" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G7" s="27" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="27" t="n">
         <v>2721</v>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F8" s="27" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G6"/>
+  <autoFilter ref="A2:G8"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/data/historico/semana_319.xlsx
+++ b/data/historico/semana_319.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$E$28</definedName>
   </definedNames>
@@ -3767,7 +3767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3779,7 +3779,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (6 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (7 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3811,7 +3811,7 @@
     <row r="3">
       <c r="A3" s="32" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="B3" s="32" t="inlineStr">
@@ -3833,7 +3833,7 @@
     <row r="4">
       <c r="A4" s="32" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="B4" s="32" t="inlineStr">
@@ -3848,65 +3848,65 @@
       </c>
       <c r="D4" s="32" t="inlineStr">
         <is>
-          <t>Agente_2951</t>
+          <t>Agente_3035</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="32" t="inlineStr">
         <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>Agente_2951</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
           <t>03/08/2026</t>
         </is>
       </c>
-      <c r="B5" s="32" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Férias/Atestado (automático)</t>
         </is>
       </c>
-      <c r="D5" s="32" t="inlineStr">
+      <c r="D6" s="32" t="inlineStr">
         <is>
           <t>Brauher Luiz Alvarenga Gonzalez</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="33" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="33" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="C6" s="33" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D6" s="33" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="33" t="inlineStr">
         <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
       <c r="C7" s="33" t="inlineStr">
         <is>
           <t>Chuva (confirmada)</t>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="D7" s="33" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
     </row>
@@ -3936,12 +3936,34 @@
       </c>
       <c r="D8" s="33" t="inlineStr">
         <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D9" s="33" t="inlineStr">
+        <is>
           <t>Equipe 4</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D8"/>
+  <autoFilter ref="A2:D9"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/data/historico/semana_319.xlsx
+++ b/data/historico/semana_319.xlsx
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo Geral'!$A$2:$AC$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por Área'!$A$2:$N$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por Área'!$A$2:$N$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Visitas Duplicadas'!$A$2:$J$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Visitas Suspeitas'!$A$2:$K$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Visitas Negativas'!$A$2:$K$2</definedName>
@@ -2136,25 +2136,25 @@
         </is>
       </c>
       <c r="D14" s="5" t="n">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>14.67</v>
+        <v>35</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>2.7</v>
+        <v>2.21</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>47.73</v>
+        <v>62.86</v>
       </c>
       <c r="K14" s="5" t="n">
         <v>0</v>
@@ -2163,7 +2163,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
         <v>0</v>
@@ -2178,29 +2178,29 @@
         <v>0</v>
       </c>
       <c r="R14" s="5" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="S14" s="5" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>131</v>
+        <v>208</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>66.41</v>
+        <v>49.52</v>
       </c>
       <c r="V14" s="5" t="n">
-        <v>2.17</v>
+        <v>4.21</v>
       </c>
       <c r="W14" s="5" t="n">
-        <v>6.52</v>
+        <v>12.62</v>
       </c>
       <c r="X14" s="5" t="n">
-        <v>0.66</v>
+        <v>1.29</v>
       </c>
       <c r="Y14" s="5" t="inlineStr">
         <is>
-          <t>R$ 334,35</t>
+          <t>R$ 171,50</t>
         </is>
       </c>
       <c r="Z14" s="5" t="inlineStr">
@@ -2215,12 +2215,12 @@
       </c>
       <c r="AB14" s="5" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AC14" s="5" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:54</t>
         </is>
       </c>
     </row>
@@ -5106,19 +5106,19 @@
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E14" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="23" t="n">
-        <v>131</v>
+        <v>208</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>66.41</v>
+        <v>49.52</v>
       </c>
       <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="n"/>
@@ -5715,19 +5715,19 @@
         </is>
       </c>
       <c r="C35" s="35" t="n">
-        <v>1493</v>
+        <v>1554</v>
       </c>
       <c r="D35" s="35" t="n">
-        <v>576</v>
+        <v>592</v>
       </c>
       <c r="E35" s="35" t="n">
         <v>2</v>
       </c>
       <c r="F35" s="35" t="n">
-        <v>2071</v>
+        <v>2148</v>
       </c>
       <c r="G35" s="35" t="n">
-        <v>27.91</v>
+        <v>27.65</v>
       </c>
       <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="n"/>
@@ -6393,7 +6393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F206"/>
+  <dimension ref="A1:F207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7093,25 +7093,25 @@
       <c r="F29" s="2" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="6" t="n">
         <v>89</v>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>🟢 EXCELENTE</t>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
         </is>
       </c>
       <c r="F30" s="2" t="n"/>
@@ -7170,44 +7170,44 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
+          <t>Carlos Alberto Albiero</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
           <t>Mateus Falcao de Souza</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
-        <v>79.90000000000001</v>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>Carlos Alberto Albiero</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
+      <c r="D34" s="5" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
         </is>
       </c>
       <c r="F34" s="2" t="n"/>
@@ -9379,29 +9379,29 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="43" t="inlineStr">
+      <c r="A120" s="42" t="inlineStr">
         <is>
           <t>Mateus Falcao de Souza</t>
         </is>
       </c>
-      <c r="B120" s="43" t="inlineStr">
+      <c r="B120" s="42" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C120" s="43" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D120" s="43" t="n">
-        <v>3</v>
-      </c>
-      <c r="E120" s="43" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F120" s="43" t="n">
-        <v>-1.5</v>
+      <c r="C120" s="42" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D120" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -9417,17 +9417,17 @@
       </c>
       <c r="C121" s="43" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D121" s="43" t="n">
         <v>2</v>
       </c>
       <c r="E121" s="43" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F121" s="43" t="n">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="122">
@@ -9443,17 +9443,17 @@
       </c>
       <c r="C122" s="43" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D122" s="43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E122" s="43" t="n">
         <v>0.3</v>
       </c>
       <c r="F122" s="43" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="123">
@@ -9469,7 +9469,7 @@
       </c>
       <c r="C123" s="43" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D123" s="43" t="n">
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C124" s="43" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D124" s="43" t="n">
@@ -9521,17 +9521,17 @@
       </c>
       <c r="C125" s="43" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D125" s="43" t="n">
         <v>1</v>
       </c>
       <c r="E125" s="43" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F125" s="43" t="n">
-        <v>-3</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="126">
@@ -9547,43 +9547,43 @@
       </c>
       <c r="C126" s="43" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D126" s="43" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E126" s="43" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="F126" s="43" t="n">
-        <v>-12.6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="43" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="B127" s="43" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C127" s="43" t="inlineStr">
         <is>
-          <t>Dia sem bater a meta diária</t>
+          <t>Visita rápida</t>
         </is>
       </c>
       <c r="D127" s="43" t="n">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="E127" s="43" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F127" s="43" t="n">
-        <v>-1.5</v>
+        <v>-39.6</v>
       </c>
     </row>
     <row r="128">
@@ -9599,17 +9599,17 @@
       </c>
       <c r="C128" s="43" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D128" s="43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E128" s="43" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F128" s="43" t="n">
-        <v>-0.6</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="129">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="C129" s="43" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D129" s="43" t="n">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="C130" s="43" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D130" s="43" t="n">
@@ -9677,17 +9677,17 @@
       </c>
       <c r="C131" s="43" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D131" s="43" t="n">
         <v>1</v>
       </c>
       <c r="E131" s="43" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F131" s="43" t="n">
-        <v>-3</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="132">
@@ -9703,43 +9703,43 @@
       </c>
       <c r="C132" s="43" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D132" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" s="43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F132" s="43" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="43" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="B133" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C133" s="43" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D132" s="43" t="n">
+      <c r="D133" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="E132" s="43" t="n">
+      <c r="E133" s="43" t="n">
         <v>0.3</v>
       </c>
-      <c r="F132" s="43" t="n">
+      <c r="F133" s="43" t="n">
         <v>-1.8</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="42" t="inlineStr">
-        <is>
-          <t>Naime Cristina Freitas</t>
-        </is>
-      </c>
-      <c r="B133" s="42" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C133" s="42" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D133" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E133" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="F133" s="42" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="134">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="C134" s="42" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D134" s="42" t="n">
@@ -9769,29 +9769,29 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="43" t="inlineStr">
+      <c r="A135" s="42" t="inlineStr">
         <is>
           <t>Naime Cristina Freitas</t>
         </is>
       </c>
-      <c r="B135" s="43" t="inlineStr">
+      <c r="B135" s="42" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C135" s="43" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D135" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" s="43" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F135" s="43" t="n">
-        <v>-0.5</v>
+      <c r="C135" s="42" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D135" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F135" s="42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="136">
@@ -9807,43 +9807,43 @@
       </c>
       <c r="C136" s="43" t="inlineStr">
         <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D136" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" s="43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F136" s="43" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="43" t="inlineStr">
+        <is>
+          <t>Naime Cristina Freitas</t>
+        </is>
+      </c>
+      <c r="B137" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C137" s="43" t="inlineStr">
+        <is>
           <t>Início tarde após 14h30</t>
         </is>
       </c>
-      <c r="D136" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E136" s="43" t="n">
+      <c r="D137" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" s="43" t="n">
         <v>0.3</v>
       </c>
-      <c r="F136" s="43" t="n">
+      <c r="F137" s="43" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="42" t="inlineStr">
-        <is>
-          <t>Rafael Ramos Recalde</t>
-        </is>
-      </c>
-      <c r="B137" s="42" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C137" s="42" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D137" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E137" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="F137" s="42" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="138">
@@ -9859,43 +9859,43 @@
       </c>
       <c r="C138" s="42" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D138" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F138" s="42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="42" t="inlineStr">
+        <is>
+          <t>Rafael Ramos Recalde</t>
+        </is>
+      </c>
+      <c r="B139" s="42" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C139" s="42" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D138" s="42" t="n">
+      <c r="D139" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="E138" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F138" s="42" t="n">
+      <c r="E139" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" s="42" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="43" t="inlineStr">
-        <is>
-          <t>Rafael Ramos Recalde</t>
-        </is>
-      </c>
-      <c r="B139" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C139" s="43" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D139" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E139" s="43" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F139" s="43" t="n">
-        <v>-0.6</v>
       </c>
     </row>
     <row r="140">
@@ -9911,17 +9911,17 @@
       </c>
       <c r="C140" s="43" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D140" s="43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E140" s="43" t="n">
         <v>0.3</v>
       </c>
       <c r="F140" s="43" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="141">
@@ -9937,43 +9937,43 @@
       </c>
       <c r="C141" s="43" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D141" s="43" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="E141" s="43" t="n">
         <v>0.3</v>
       </c>
       <c r="F141" s="43" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="43" t="inlineStr">
+        <is>
+          <t>Rafael Ramos Recalde</t>
+        </is>
+      </c>
+      <c r="B142" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C142" s="43" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D142" s="43" t="n">
+        <v>36</v>
+      </c>
+      <c r="E142" s="43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F142" s="43" t="n">
         <v>-21.6</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="42" t="inlineStr">
-        <is>
-          <t>Raquel Ortiz dos Santos</t>
-        </is>
-      </c>
-      <c r="B142" s="42" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C142" s="42" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D142" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E142" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="F142" s="42" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="143">
@@ -9989,43 +9989,43 @@
       </c>
       <c r="C143" s="42" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D143" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F143" s="42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="42" t="inlineStr">
+        <is>
+          <t>Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B144" s="42" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C144" s="42" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D143" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E143" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F143" s="42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="43" t="inlineStr">
-        <is>
-          <t>Raquel Ortiz dos Santos</t>
-        </is>
-      </c>
-      <c r="B144" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C144" s="43" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D144" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E144" s="43" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F144" s="43" t="n">
-        <v>-0.5</v>
+      <c r="D144" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F144" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="C145" s="43" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D145" s="43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E145" s="43" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F145" s="43" t="n">
-        <v>-1.2</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="146">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="C146" s="43" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D146" s="43" t="n">
@@ -10093,17 +10093,17 @@
       </c>
       <c r="C147" s="43" t="inlineStr">
         <is>
-          <t>Visita fora do expediente/fim de semana</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D147" s="43" t="n">
         <v>2</v>
       </c>
       <c r="E147" s="43" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F147" s="43" t="n">
-        <v>-2</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="148">
@@ -10119,43 +10119,43 @@
       </c>
       <c r="C148" s="43" t="inlineStr">
         <is>
+          <t>Visita fora do expediente/fim de semana</t>
+        </is>
+      </c>
+      <c r="D148" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E148" s="43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F148" s="43" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="43" t="inlineStr">
+        <is>
+          <t>Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B149" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C149" s="43" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D148" s="43" t="n">
+      <c r="D149" s="43" t="n">
         <v>18</v>
       </c>
-      <c r="E148" s="43" t="n">
+      <c r="E149" s="43" t="n">
         <v>0.3</v>
       </c>
-      <c r="F148" s="43" t="n">
+      <c r="F149" s="43" t="n">
         <v>-10.8</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="42" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-      <c r="B149" s="42" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C149" s="42" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D149" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E149" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="F149" s="42" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="150">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="C150" s="42" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D150" s="42" t="n">
@@ -10197,43 +10197,43 @@
       </c>
       <c r="C151" s="42" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D151" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F151" s="42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="42" t="inlineStr">
+        <is>
+          <t>Rosalina Beniel Vargas</t>
+        </is>
+      </c>
+      <c r="B152" s="42" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C152" s="42" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D151" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E151" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F151" s="42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="43" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-      <c r="B152" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C152" s="43" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D152" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" s="43" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F152" s="43" t="n">
-        <v>-0.5</v>
+      <c r="D152" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F152" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -10249,17 +10249,17 @@
       </c>
       <c r="C153" s="43" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D153" s="43" t="n">
         <v>1</v>
       </c>
       <c r="E153" s="43" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F153" s="43" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="154">
@@ -10275,7 +10275,7 @@
       </c>
       <c r="C154" s="43" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D154" s="43" t="n">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="C155" s="43" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D155" s="43" t="n">
@@ -10315,29 +10315,29 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="42" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="B156" s="42" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C156" s="42" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D156" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E156" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="F156" s="42" t="n">
-        <v>5</v>
+      <c r="A156" s="43" t="inlineStr">
+        <is>
+          <t>Rosalina Beniel Vargas</t>
+        </is>
+      </c>
+      <c r="B156" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C156" s="43" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D156" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" s="43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F156" s="43" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="157">
@@ -10353,43 +10353,43 @@
       </c>
       <c r="C157" s="42" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D157" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F157" s="42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="42" t="inlineStr">
+        <is>
+          <t>Rozana Reis da Silva</t>
+        </is>
+      </c>
+      <c r="B158" s="42" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C158" s="42" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D157" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E157" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F157" s="42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="43" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="B158" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C158" s="43" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D158" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E158" s="43" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F158" s="43" t="n">
-        <v>-0.6</v>
+      <c r="D158" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="C159" s="43" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D159" s="43" t="n">
@@ -10431,43 +10431,43 @@
       </c>
       <c r="C160" s="43" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D160" s="43" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E160" s="43" t="n">
         <v>0.3</v>
       </c>
       <c r="F160" s="43" t="n">
-        <v>-9</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="43" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="B161" s="43" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C161" s="43" t="inlineStr">
         <is>
-          <t>Dia sem bater a meta diária</t>
+          <t>Visita rápida</t>
         </is>
       </c>
       <c r="D161" s="43" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E161" s="43" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F161" s="43" t="n">
-        <v>-0.5</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="162">
@@ -10483,17 +10483,17 @@
       </c>
       <c r="C162" s="43" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D162" s="43" t="n">
         <v>1</v>
       </c>
       <c r="E162" s="43" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F162" s="43" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="163">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="C163" s="43" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D163" s="43" t="n">
@@ -10535,17 +10535,17 @@
       </c>
       <c r="C164" s="43" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D164" s="43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E164" s="43" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F164" s="43" t="n">
-        <v>-6</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="165">
@@ -10561,17 +10561,17 @@
       </c>
       <c r="C165" s="43" t="inlineStr">
         <is>
-          <t>Visita fora do expediente/fim de semana</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D165" s="43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E165" s="43" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F165" s="43" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="166">
@@ -10587,43 +10587,43 @@
       </c>
       <c r="C166" s="43" t="inlineStr">
         <is>
+          <t>Visita fora do expediente/fim de semana</t>
+        </is>
+      </c>
+      <c r="D166" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" s="43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F166" s="43" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="43" t="inlineStr">
+        <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B167" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C167" s="43" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D166" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E166" s="43" t="n">
+      <c r="D167" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" s="43" t="n">
         <v>0.3</v>
       </c>
-      <c r="F166" s="43" t="n">
+      <c r="F167" s="43" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="42" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="B167" s="42" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C167" s="42" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D167" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E167" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="F167" s="42" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="168">
@@ -10639,43 +10639,43 @@
       </c>
       <c r="C168" s="42" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D168" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F168" s="42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="42" t="inlineStr">
+        <is>
+          <t>Sara Eliane Talaveira de Oliveira</t>
+        </is>
+      </c>
+      <c r="B169" s="42" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C169" s="42" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D168" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E168" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F168" s="42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="43" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="B169" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C169" s="43" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D169" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E169" s="43" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F169" s="43" t="n">
-        <v>-0.6</v>
+      <c r="D169" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F169" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="C170" s="43" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D170" s="43" t="n">
@@ -10717,43 +10717,43 @@
       </c>
       <c r="C171" s="43" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D171" s="43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E171" s="43" t="n">
         <v>0.3</v>
       </c>
       <c r="F171" s="43" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="43" t="inlineStr">
+        <is>
+          <t>Sara Eliane Talaveira de Oliveira</t>
+        </is>
+      </c>
+      <c r="B172" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C172" s="43" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D172" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E172" s="43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F172" s="43" t="n">
         <v>-6</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="42" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="B172" s="42" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C172" s="42" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D172" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E172" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="F172" s="42" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="173">
@@ -10769,7 +10769,7 @@
       </c>
       <c r="C173" s="42" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D173" s="42" t="n">
@@ -10795,69 +10795,69 @@
       </c>
       <c r="C174" s="42" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D174" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E174" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F174" s="42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="42" t="inlineStr">
+        <is>
+          <t>Selba Ramona Afonso</t>
+        </is>
+      </c>
+      <c r="B175" s="42" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C175" s="42" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D174" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E174" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F174" s="42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="43" t="inlineStr">
+      <c r="D175" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E175" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F175" s="42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="43" t="inlineStr">
         <is>
           <t>Selba Ramona Afonso</t>
         </is>
       </c>
-      <c r="B175" s="43" t="inlineStr">
+      <c r="B176" s="43" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C175" s="43" t="inlineStr">
+      <c r="C176" s="43" t="inlineStr">
         <is>
           <t>Início tarde após 14h30</t>
         </is>
       </c>
-      <c r="D175" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E175" s="43" t="n">
+      <c r="D176" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E176" s="43" t="n">
         <v>0.3</v>
       </c>
-      <c r="F175" s="43" t="n">
+      <c r="F176" s="43" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="42" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="B176" s="42" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C176" s="42" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D176" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E176" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="F176" s="42" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="177">
@@ -10873,43 +10873,43 @@
       </c>
       <c r="C177" s="42" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D177" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E177" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F177" s="42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="42" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B178" s="42" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C178" s="42" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D177" s="42" t="n">
+      <c r="D178" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="E177" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F177" s="42" t="n">
+      <c r="E178" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F178" s="42" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="43" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="B178" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C178" s="43" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D178" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E178" s="43" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F178" s="43" t="n">
-        <v>-0.6</v>
       </c>
     </row>
     <row r="179">
@@ -10925,17 +10925,17 @@
       </c>
       <c r="C179" s="43" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D179" s="43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E179" s="43" t="n">
         <v>0.3</v>
       </c>
       <c r="F179" s="43" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="180">
@@ -10951,43 +10951,43 @@
       </c>
       <c r="C180" s="43" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D180" s="43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E180" s="43" t="n">
         <v>0.3</v>
       </c>
       <c r="F180" s="43" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="43" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B181" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C181" s="43" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D181" s="43" t="n">
+        <v>4</v>
+      </c>
+      <c r="E181" s="43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F181" s="43" t="n">
         <v>-2.4</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="42" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B181" s="42" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C181" s="42" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D181" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E181" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="F181" s="42" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="182">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="C182" s="42" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D182" s="42" t="n">
@@ -11029,69 +11029,69 @@
       </c>
       <c r="C183" s="42" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D183" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F183" s="42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="42" t="inlineStr">
+        <is>
+          <t>Suely Aguiar Alves Luiz</t>
+        </is>
+      </c>
+      <c r="B184" s="42" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C184" s="42" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D183" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E183" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F183" s="42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="43" t="inlineStr">
+      <c r="D184" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" s="42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="43" t="inlineStr">
         <is>
           <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
-      <c r="B184" s="43" t="inlineStr">
+      <c r="B185" s="43" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C184" s="43" t="inlineStr">
+      <c r="C185" s="43" t="inlineStr">
         <is>
           <t>Início tarde após 14h30</t>
         </is>
       </c>
-      <c r="D184" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E184" s="43" t="n">
+      <c r="D185" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E185" s="43" t="n">
         <v>0.3</v>
       </c>
-      <c r="F184" s="43" t="n">
+      <c r="F185" s="43" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="42" t="inlineStr">
-        <is>
-          <t>Tania Maria Montania</t>
-        </is>
-      </c>
-      <c r="B185" s="42" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C185" s="42" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D185" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E185" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="F185" s="42" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="186">
@@ -11107,43 +11107,43 @@
       </c>
       <c r="C186" s="42" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D186" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E186" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F186" s="42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="42" t="inlineStr">
+        <is>
+          <t>Tania Maria Montania</t>
+        </is>
+      </c>
+      <c r="B187" s="42" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C187" s="42" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D186" s="42" t="n">
+      <c r="D187" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="E186" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F186" s="42" t="n">
+      <c r="E187" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" s="42" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="43" t="inlineStr">
-        <is>
-          <t>Tania Maria Montania</t>
-        </is>
-      </c>
-      <c r="B187" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C187" s="43" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D187" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E187" s="43" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F187" s="43" t="n">
-        <v>-0.5</v>
       </c>
     </row>
     <row r="188">
@@ -11159,17 +11159,17 @@
       </c>
       <c r="C188" s="43" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D188" s="43" t="n">
         <v>1</v>
       </c>
       <c r="E188" s="43" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F188" s="43" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="189">
@@ -11185,17 +11185,17 @@
       </c>
       <c r="C189" s="43" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D189" s="43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E189" s="43" t="n">
         <v>0.3</v>
       </c>
       <c r="F189" s="43" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="190">
@@ -11211,17 +11211,17 @@
       </c>
       <c r="C190" s="43" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D190" s="43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E190" s="43" t="n">
         <v>0.3</v>
       </c>
       <c r="F190" s="43" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="191">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="C191" s="43" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D191" s="43" t="n">
@@ -11251,55 +11251,55 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="42" t="inlineStr">
+      <c r="A192" s="43" t="inlineStr">
+        <is>
+          <t>Tania Maria Montania</t>
+        </is>
+      </c>
+      <c r="B192" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C192" s="43" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D192" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E192" s="43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F192" s="43" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="42" t="inlineStr">
         <is>
           <t>Walquiria Araujo Flores</t>
         </is>
       </c>
-      <c r="B192" s="42" t="inlineStr">
+      <c r="B193" s="42" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C192" s="42" t="inlineStr">
+      <c r="C193" s="42" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D192" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E192" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F192" s="42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="43" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="B193" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C193" s="43" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D193" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E193" s="43" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F193" s="43" t="n">
-        <v>-0.5</v>
+      <c r="D193" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E193" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F193" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -11315,17 +11315,17 @@
       </c>
       <c r="C194" s="43" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D194" s="43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E194" s="43" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F194" s="43" t="n">
-        <v>-1.2</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="195">
@@ -11341,17 +11341,17 @@
       </c>
       <c r="C195" s="43" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D195" s="43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E195" s="43" t="n">
         <v>0.3</v>
       </c>
       <c r="F195" s="43" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="196">
@@ -11367,17 +11367,17 @@
       </c>
       <c r="C196" s="43" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D196" s="43" t="n">
         <v>1</v>
       </c>
       <c r="E196" s="43" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F196" s="43" t="n">
-        <v>-3</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="197">
@@ -11393,43 +11393,43 @@
       </c>
       <c r="C197" s="43" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D197" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" s="43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F197" s="43" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="43" t="inlineStr">
+        <is>
+          <t>Walquiria Araujo Flores</t>
+        </is>
+      </c>
+      <c r="B198" s="43" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C198" s="43" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D197" s="43" t="n">
+      <c r="D198" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="E197" s="43" t="n">
+      <c r="E198" s="43" t="n">
         <v>0.3</v>
       </c>
-      <c r="F197" s="43" t="n">
+      <c r="F198" s="43" t="n">
         <v>-1.8</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="42" t="inlineStr">
-        <is>
-          <t>Wesley de Souza Leal</t>
-        </is>
-      </c>
-      <c r="B198" s="42" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C198" s="42" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D198" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E198" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="F198" s="42" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="199">
@@ -11445,43 +11445,43 @@
       </c>
       <c r="C199" s="42" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D199" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F199" s="42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="42" t="inlineStr">
+        <is>
+          <t>Wesley de Souza Leal</t>
+        </is>
+      </c>
+      <c r="B200" s="42" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C200" s="42" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D199" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E199" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F199" s="42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="43" t="inlineStr">
-        <is>
-          <t>Wesley de Souza Leal</t>
-        </is>
-      </c>
-      <c r="B200" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C200" s="43" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D200" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E200" s="43" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F200" s="43" t="n">
-        <v>-0.5</v>
+      <c r="D200" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F200" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -11497,17 +11497,17 @@
       </c>
       <c r="C201" s="43" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D201" s="43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E201" s="43" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F201" s="43" t="n">
-        <v>-1.2</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="202">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="C202" s="43" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D202" s="43" t="n">
@@ -11537,29 +11537,29 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="42" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B203" s="42" t="inlineStr">
+      <c r="A203" s="43" t="inlineStr">
+        <is>
+          <t>Wesley de Souza Leal</t>
+        </is>
+      </c>
+      <c r="B203" s="43" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C203" s="42" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D203" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E203" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="F203" s="42" t="n">
-        <v>5</v>
+      <c r="C203" s="43" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D203" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E203" s="43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F203" s="43" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="204">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="C204" s="42" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D204" s="42" t="n">
@@ -11601,42 +11601,68 @@
       </c>
       <c r="C205" s="42" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D205" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F205" s="42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="42" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B206" s="42" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C206" s="42" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D205" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E205" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F205" s="42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="43" t="inlineStr">
+      <c r="D206" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F206" s="42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="43" t="inlineStr">
         <is>
           <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
-      <c r="B206" s="43" t="inlineStr">
+      <c r="B207" s="43" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C206" s="43" t="inlineStr">
+      <c r="C207" s="43" t="inlineStr">
         <is>
           <t>Início tarde após 14h30</t>
         </is>
       </c>
-      <c r="D206" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E206" s="43" t="n">
+      <c r="D207" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E207" s="43" t="n">
         <v>0.3</v>
       </c>
-      <c r="F206" s="43" t="n">
+      <c r="F207" s="43" t="n">
         <v>-0.6</v>
       </c>
     </row>
@@ -11656,7 +11682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -12590,105 +12616,105 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
+          <t>420 - FERROVIARIA</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Q001, Q002</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>73.77</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>20.78</v>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
           <t>415 - CENTRO 1</t>
         </is>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D19" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E19" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F19" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="G19" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Q001, Q002, Q003, Q006, Q007, Q009, Q010</t>
         </is>
       </c>
-      <c r="I18" s="5" t="n">
+      <c r="I19" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="J18" s="5" t="n">
+      <c r="J19" s="5" t="n">
         <v>47.73</v>
       </c>
-      <c r="K18" s="5" t="n">
+      <c r="K19" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="L18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="5" t="n">
+      <c r="L19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5" t="n">
         <v>66.41</v>
       </c>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>Q017</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -12698,40 +12724,40 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>416 - CENTRO 2</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5.22</v>
+        <v>8.17</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>Q005, Q008, Q011</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="L20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>19.42</v>
+        <v>6.45</v>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
@@ -12742,7 +12768,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -12752,40 +12778,40 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>417 - CENTRO 3</t>
+          <t>416 - CENTRO 2</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5.17</v>
+        <v>5.22</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>5</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q005, Q008, Q011</t>
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>5.71</v>
+        <v>1.2</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>10.26</v>
+        <v>19.42</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
@@ -12796,7 +12822,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -12806,40 +12832,40 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>417 - CENTRO 3</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>8.210000000000001</v>
+        <v>5.17</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="G22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Q015</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Q011, Q025</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J22" s="4" t="n">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>40</v>
+        <v>10.26</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
@@ -12850,34 +12876,34 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>428 - JARDIM COIMBRA</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.52</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Q001, Q019, Q023, Q024</t>
+          <t>Q011, Q025</t>
         </is>
       </c>
       <c r="I23" s="4" t="n">
@@ -12887,13 +12913,13 @@
         <v>0</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="L23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>53.03</v>
+        <v>40</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
@@ -12904,7 +12930,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -12914,14 +12940,14 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>430 - VILA RENÔ</t>
+          <t>428 - JARDIM COIMBRA</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.6</v>
+        <v>5.52</v>
       </c>
       <c r="F24" s="4" t="n">
         <v>6</v>
@@ -12931,23 +12957,23 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Q008, Q018, Q032, Q033</t>
+          <t>Q001, Q019, Q023, Q024</t>
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="L24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>28.57</v>
+        <v>53.03</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
@@ -12958,7 +12984,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -12968,40 +12994,40 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>427 - JAMIL SALDANHA DERZI</t>
+          <t>430 - VILA RENÔ</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.67</v>
+        <v>5.6</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>6</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Q016, Q035, Q036, Q040, Q041, Q044, Q045, Q046</t>
+          <t>Q008, Q018, Q032, Q033</t>
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>19.44</v>
+        <v>28.57</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
@@ -13012,7 +13038,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -13022,40 +13048,40 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>427 - JAMIL SALDANHA DERZI</t>
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.35</v>
+        <v>6.67</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Q030, Q031, Q032, Q033, Q034</t>
+          <t>Q016, Q035, Q036, Q040, Q041, Q044, Q045, Q046</t>
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0</v>
+        <v>19.44</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
@@ -13066,7 +13092,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -13076,40 +13102,40 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>423 - SANTA IZABEL</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.47</v>
+        <v>5.35</v>
       </c>
       <c r="F27" s="4" t="n">
         <v>5</v>
       </c>
       <c r="G27" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Q030, Q031, Q032, Q033, Q034</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Q029, Q034, Q036</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="J27" s="4" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>40.62</v>
+        <v>0</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
@@ -13120,7 +13146,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -13130,14 +13156,14 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>424 - SÃO JOÃO</t>
+          <t>423 - SANTA IZABEL</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.69</v>
+        <v>5.47</v>
       </c>
       <c r="F28" s="4" t="n">
         <v>5</v>
@@ -13147,7 +13173,7 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Q048, Q049, Q050</t>
+          <t>Q029, Q034, Q036</t>
         </is>
       </c>
       <c r="I28" s="4" t="n">
@@ -13157,13 +13183,13 @@
         <v>0</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>42.62</v>
+        <v>40.62</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
@@ -13174,331 +13200,331 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>Rosalina Beniel Vargas</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>424 - SÃO JOÃO</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Q048, Q049, Q050</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>42.62</v>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
           <t>Selba Ramona Afonso</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>431 - PANAMBI</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D30" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E30" s="4" t="n">
         <v>6.67</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F30" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="G30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>Q026</t>
         </is>
       </c>
-      <c r="I29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="4" t="n">
+      <c r="I30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="4" t="n">
+      <c r="L30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="4" t="n">
         <v>11.76</v>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>435 - JARDIM PRIMOR</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D31" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="E31" s="6" t="n">
         <v>4.74</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="F31" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="G31" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="H30" s="6" t="inlineStr">
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>Q020, Q021</t>
         </is>
       </c>
-      <c r="I30" s="6" t="n">
+      <c r="I31" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="J31" s="6" t="n">
         <v>10.53</v>
       </c>
-      <c r="K30" s="6" t="n">
+      <c r="K31" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="L30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="6" t="n">
+      <c r="L31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="6" t="n">
         <v>29.63</v>
       </c>
-      <c r="N30" s="6" t="inlineStr">
+      <c r="N31" s="6" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Juliana Patricia Goncalves</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>445 - JARDIM IVONE</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>5.69</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Q016, Q017, Q020, Q021, Q027, Q043</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>22.86</v>
-      </c>
-      <c r="K31" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="5" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="N31" s="5" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
+          <t>Juliana Patricia Goncalves</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>445 - JARDIM IVONE</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Q016, Q017, Q020, Q021, Q027, Q043</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="5" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
           <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>435 - JARDIM PRIMOR</t>
         </is>
       </c>
-      <c r="D32" s="5" t="n">
+      <c r="D33" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E33" s="5" t="n">
         <v>3.34</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="F33" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G32" s="5" t="n">
+      <c r="G33" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Q005, Q006</t>
         </is>
       </c>
-      <c r="I32" s="5" t="n">
+      <c r="I33" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="J32" s="5" t="n">
+      <c r="J33" s="5" t="n">
         <v>44.07</v>
       </c>
-      <c r="K32" s="5" t="n">
+      <c r="K33" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="L32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="5" t="n">
+      <c r="L33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="5" t="n">
         <v>28.05</v>
       </c>
-      <c r="N32" s="5" t="inlineStr">
+      <c r="N33" s="5" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>443 - KAMEL SAAD 1</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D34" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="E34" s="6" t="n">
         <v>5.18</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="F34" s="6" t="n">
         <v>4.5</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="G34" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>Q002, Q008, Q013, Q014</t>
         </is>
       </c>
-      <c r="I33" s="6" t="n">
+      <c r="I34" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="J34" s="6" t="n">
         <v>12.5</v>
       </c>
-      <c r="K33" s="6" t="n">
+      <c r="K34" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="L33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="6" t="n">
+      <c r="L34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="6" t="n">
         <v>38.46</v>
       </c>
-      <c r="N33" s="6" t="inlineStr">
+      <c r="N34" s="6" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Rafael Ramos Recalde</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>435 - JARDIM PRIMOR</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>Q011, Q012, Q013</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="J34" s="5" t="n">
-        <v>56.25</v>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="5" t="n">
-        <v>34.02</v>
-      </c>
-      <c r="N34" s="5" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -13512,36 +13538,36 @@
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>3.49</v>
+        <v>2.81</v>
       </c>
       <c r="F35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G35" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Q025</t>
+          <t>Q011, Q012, Q013</t>
         </is>
       </c>
       <c r="I35" s="5" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>34.88</v>
+        <v>56.25</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>44.16</v>
+        <v>34.02</v>
       </c>
       <c r="N35" s="5" t="inlineStr">
         <is>
@@ -13552,7 +13578,7 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -13566,322 +13592,376 @@
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>3.31</v>
+        <v>3.49</v>
       </c>
       <c r="F36" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Q025</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>44.16</v>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Sara Eliane Talaveira de Oliveira</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>435 - JARDIM PRIMOR</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>Q001, Q002</t>
         </is>
       </c>
-      <c r="I36" s="5" t="n">
+      <c r="I37" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="J36" s="5" t="n">
+      <c r="J37" s="5" t="n">
         <v>23.81</v>
       </c>
-      <c r="K36" s="5" t="n">
+      <c r="K37" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="L36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="5" t="n">
+      <c r="L37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="5" t="n">
         <v>20.75</v>
       </c>
-      <c r="N36" s="5" t="inlineStr">
+      <c r="N37" s="5" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>434 - VILA AUREA</t>
         </is>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D38" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E38" s="4" t="n">
         <v>5.24</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="F38" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>Q025, Q040, Q041</t>
         </is>
       </c>
-      <c r="I37" s="4" t="n">
+      <c r="I38" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="J37" s="4" t="n">
+      <c r="J38" s="4" t="n">
         <v>5.97</v>
       </c>
-      <c r="K37" s="4" t="n">
+      <c r="K38" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="L37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M37" s="4" t="n">
+      <c r="L38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="4" t="n">
         <v>20.24</v>
       </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="N38" s="4" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Walquiria Araujo Flores</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>440 - JARDIM IBIRAPUERA</t>
         </is>
       </c>
-      <c r="D38" s="5" t="n">
+      <c r="D39" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E39" s="5" t="n">
         <v>2.89</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F39" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G38" s="5" t="n">
+      <c r="G39" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>Q022, Q024</t>
         </is>
       </c>
-      <c r="I38" s="5" t="n">
+      <c r="I39" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J38" s="5" t="n">
+      <c r="J39" s="5" t="n">
         <v>22.22</v>
       </c>
-      <c r="K38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="5" t="inlineStr">
+      <c r="K39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Walquiria Araujo Flores</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>435 - JARDIM PRIMOR</t>
         </is>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D40" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E40" s="4" t="n">
         <v>4.74</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="F40" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>Q008, Q009</t>
         </is>
       </c>
-      <c r="I39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="4" t="n">
+      <c r="I40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="4" t="n">
         <v>2.94</v>
       </c>
-      <c r="K39" s="4" t="n">
+      <c r="K40" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="L39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="4" t="n">
+      <c r="L40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="4" t="n">
         <v>42.37</v>
       </c>
-      <c r="N39" s="4" t="inlineStr">
+      <c r="N40" s="4" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>% Rápidas até 10%</t>
         </is>
       </c>
-      <c r="C43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="C44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>% Rápidas entre 11% e 20%</t>
         </is>
       </c>
-      <c r="C44" s="10" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="C45" s="10" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>% Rápidas acima de 20%</t>
         </is>
       </c>
-      <c r="C45" s="10" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="13" t="inlineStr">
+      <c r="C46" s="10" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>⚠️ SEQUÊNCIA SUSPEITA</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="45" customHeight="1">
-      <c r="A48" s="14" t="inlineStr">
+    <row r="49" ht="45" customHeight="1">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t>Duas ou mais visitas consecutivas do mesmo agente registradas no MESMO MINUTO de chegada são marcadas como suspeitas (o e-Visita não registra segundos, então o critério de negócio de 50s de diferença equivale, na prática, a 'mesmo minuto') — sugere lançamento em lote no sistema, não visita real de campo. Colunas: 'Visitas em Sequência Suspeita' (total de visitas envolvidas) e 'Maior Sequência Suspeita' (maior número de visitas seguidas nessa condição). Na aba 'Visitas Suspeitas', a coluna 'Diferença p/ Anterior (s)*' fica em branco quando o alerta da linha veio do par com a visita SEGUINTE (não da anterior).</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>🍽️ VISITAS NO HORÁRIO DE ALMOÇO</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="70" customHeight="1">
-      <c r="A51" s="14" t="inlineStr">
+    <row r="52" ht="70" customHeight="1">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>Coluna 'Visitas no Almoço (11h15-12h45)' conta as visitas com chegada registrada nesse intervalo — o horário oficial de almoço é 11h15 às 12h45, JÁ COM 15 MINUTOS DE TOLERÂNCIA em cada borda (visitas entre 11h-11h15 ou 12h45-13h não são tratadas como violação, só como 'fora do expediente' genérico) — use para checar se o agente está trabalhando no horário de almoço ou se há erro de lançamento. Essas visitas ficam de fora do cálculo de 'Início/Fim Manhã' e 'Início/Fim Tarde', que usam a primeira chegada e a última saída de cada dia (não a média de todos os horários), para refletir melhor o início e o fim reais do expediente.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="16" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" s="14" t="inlineStr">
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="17" t="inlineStr">
-        <is>
-          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
         <is>
+          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
           <t>ℹ️ Visitas com duração NEGATIVA (saída antes da chegada — provável bug do sistema) foram excluídas do cálculo de Média/Mediana e estão detalhadas na aba 'Visitas Negativas', para investigação junto ao suporte do e-Visita.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N39"/>
+  <autoFilter ref="A2:N40"/>
   <mergeCells count="13">
-    <mergeCell ref="A42:C42"/>
     <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A49:C49"/>
     <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A58:C58"/>
     <mergeCell ref="B45:C45"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A55:C55"/>
     <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A52:C52"/>
     <mergeCell ref="A51:C51"/>
-    <mergeCell ref="B43:C43"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/historico/semana_319.xlsx
+++ b/data/historico/semana_319.xlsx
@@ -30,8 +30,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 15min'!$A$2:$J$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$E$38</definedName>
   </definedNames>
@@ -1423,16 +1423,16 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4.98</v>
+        <v>4.97</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>5</v>
@@ -1441,7 +1441,7 @@
         <v>4</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>9.09</v>
+        <v>5.8</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -1465,49 +1465,49 @@
         <v>0</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="S7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>41.33</v>
+        <v>40.52</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>4.43</v>
+        <v>4.91</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>8.869999999999999</v>
+        <v>14.72</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="Y7" s="4" t="inlineStr">
         <is>
-          <t>R$ 121,12</t>
+          <t>R$ 116,00</t>
         </is>
       </c>
       <c r="Z7" s="4" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AA7" s="4" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AB7" s="4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AC7" s="4" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:00</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4907,7 +4907,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (11 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (10 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="B3" s="36" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="C3" s="36" t="inlineStr">
@@ -4961,7 +4961,7 @@
     <row r="4">
       <c r="A4" s="36" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="B4" s="36" t="inlineStr">
@@ -4976,19 +4976,19 @@
       </c>
       <c r="D4" s="36" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="36" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="B5" s="36" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="C5" s="36" t="inlineStr">
@@ -4998,19 +4998,19 @@
       </c>
       <c r="D5" s="36" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="36" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="B6" s="36" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="C6" s="36" t="inlineStr">
@@ -5020,14 +5020,14 @@
       </c>
       <c r="D6" s="36" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="36" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="B7" s="36" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="D7" s="36" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
     </row>
@@ -5064,36 +5064,36 @@
       </c>
       <c r="D8" s="36" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="B9" s="36" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="C9" s="36" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D9" s="36" t="inlineStr">
-        <is>
-          <t>Ramona dos Santos Oliveira</t>
+      <c r="B9" s="37" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="37" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D9" s="37" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="37" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="B10" s="37" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="D10" s="37" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
     </row>
@@ -5130,56 +5130,34 @@
       </c>
       <c r="D11" s="37" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="37" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="37" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="C12" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D12" s="37" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="38" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>13/08/2026</t>
         </is>
       </c>
-      <c r="B13" s="38" t="inlineStr">
+      <c r="B12" s="38" t="inlineStr">
         <is>
           <t>13/08/2026</t>
         </is>
       </c>
-      <c r="C13" s="38" t="inlineStr">
+      <c r="C12" s="38" t="inlineStr">
         <is>
           <t>Recolha de Ovitrampa</t>
         </is>
       </c>
-      <c r="D13" s="38" t="inlineStr">
+      <c r="D12" s="38" t="inlineStr">
         <is>
           <t>Todos os agentes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D13"/>
+  <autoFilter ref="A2:D12"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -5389,19 +5367,19 @@
         </is>
       </c>
       <c r="C7" s="27" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E7" s="27" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>41.33</v>
+        <v>40.52</v>
       </c>
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
@@ -6317,19 +6295,19 @@
         </is>
       </c>
       <c r="C39" s="24" t="n">
-        <v>2716</v>
+        <v>2741</v>
       </c>
       <c r="D39" s="24" t="n">
-        <v>1183</v>
+        <v>1199</v>
       </c>
       <c r="E39" s="24" t="n">
         <v>4</v>
       </c>
       <c r="F39" s="24" t="n">
-        <v>3903</v>
+        <v>3944</v>
       </c>
       <c r="G39" s="24" t="n">
-        <v>30.41</v>
+        <v>30.5</v>
       </c>
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="n"/>
@@ -7091,7 +7069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F259"/>
+  <dimension ref="A1:F260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7172,12 +7150,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Bianca Afonso Narbaez</t>
+          <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
@@ -7196,7 +7174,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -7220,7 +7198,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -7244,7 +7222,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -7268,7 +7246,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -7292,7 +7270,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -7316,12 +7294,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
@@ -7340,7 +7318,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -7364,7 +7342,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -7388,7 +7366,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -7412,12 +7390,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
@@ -7436,16 +7414,16 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -7460,7 +7438,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -7469,7 +7447,7 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>99.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
@@ -7484,16 +7462,16 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
@@ -7508,16 +7486,16 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>98.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
@@ -7532,16 +7510,16 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>97.8</v>
+        <v>98.3</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
@@ -7556,7 +7534,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -7565,7 +7543,7 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>96.90000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
@@ -7580,16 +7558,16 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>96.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -7604,16 +7582,16 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>96.2</v>
+        <v>96.8</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -7628,16 +7606,16 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>92.8</v>
+        <v>96.2</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
@@ -7652,16 +7630,16 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>92.7</v>
+        <v>92.8</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -7676,7 +7654,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -7685,7 +7663,7 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
-        <v>91.5</v>
+        <v>92.7</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
@@ -9145,43 +9123,43 @@
       </c>
       <c r="C84" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D84" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F84" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="46" t="inlineStr">
+        <is>
+          <t>Cris Milene Cardenas da Silva</t>
+        </is>
+      </c>
+      <c r="B85" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C85" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D84" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F84" s="46" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="47" t="inlineStr">
-        <is>
-          <t>Cris Milene Cardenas da Silva</t>
-        </is>
-      </c>
-      <c r="B85" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C85" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D85" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F85" s="47" t="n">
-        <v>-0.5</v>
+      <c r="D85" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -9197,17 +9175,17 @@
       </c>
       <c r="C86" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D86" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E86" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F86" s="47" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="87">
@@ -9223,17 +9201,17 @@
       </c>
       <c r="C87" s="47" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D87" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87" s="47" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F87" s="47" t="n">
-        <v>-6</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="88">
@@ -9249,69 +9227,69 @@
       </c>
       <c r="C88" s="47" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D88" s="47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E88" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F88" s="47" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="47" t="inlineStr">
+        <is>
+          <t>Cris Milene Cardenas da Silva</t>
+        </is>
+      </c>
+      <c r="B89" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C89" s="47" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D89" s="47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E89" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F89" s="47" t="n">
         <v>-2.4</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="46" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="46" t="inlineStr">
         <is>
           <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
-      <c r="B89" s="46" t="inlineStr">
+      <c r="B90" s="46" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C89" s="46" t="inlineStr">
+      <c r="C90" s="46" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D89" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F89" s="46" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="47" t="inlineStr">
-        <is>
-          <t>Emidio Rainer Vilhalba</t>
-        </is>
-      </c>
-      <c r="B90" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C90" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D90" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E90" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F90" s="47" t="n">
-        <v>-1</v>
+      <c r="D90" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -9327,17 +9305,17 @@
       </c>
       <c r="C91" s="47" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D91" s="47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F91" s="47" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="92">
@@ -9353,7 +9331,7 @@
       </c>
       <c r="C92" s="47" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D92" s="47" t="n">
@@ -9379,17 +9357,17 @@
       </c>
       <c r="C93" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D93" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F93" s="47" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="94">
@@ -9405,17 +9383,17 @@
       </c>
       <c r="C94" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D94" s="47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F94" s="47" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="95">
@@ -9431,17 +9409,17 @@
       </c>
       <c r="C95" s="47" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D95" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E95" s="47" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F95" s="47" t="n">
-        <v>-3</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="96">
@@ -9457,43 +9435,43 @@
       </c>
       <c r="C96" s="47" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D96" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F96" s="47" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="47" t="inlineStr">
+        <is>
+          <t>Emidio Rainer Vilhalba</t>
+        </is>
+      </c>
+      <c r="B97" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C97" s="47" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D96" s="47" t="n">
+      <c r="D97" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="E96" s="47" t="n">
+      <c r="E97" s="47" t="n">
         <v>0.3</v>
       </c>
-      <c r="F96" s="47" t="n">
+      <c r="F97" s="47" t="n">
         <v>-1.2</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="46" t="inlineStr">
-        <is>
-          <t>Evelyn Santana Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="B97" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C97" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D97" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F97" s="46" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="98">
@@ -9509,43 +9487,43 @@
       </c>
       <c r="C98" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D98" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F98" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="46" t="inlineStr">
+        <is>
+          <t>Evelyn Santana Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="B99" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C99" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D98" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F98" s="46" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="47" t="inlineStr">
-        <is>
-          <t>Evelyn Santana Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="B99" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C99" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D99" s="47" t="n">
-        <v>3</v>
-      </c>
-      <c r="E99" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F99" s="47" t="n">
-        <v>-1.5</v>
+      <c r="D99" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -9561,17 +9539,17 @@
       </c>
       <c r="C100" s="47" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D100" s="47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E100" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F100" s="47" t="n">
-        <v>-0.6</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="101">
@@ -9587,7 +9565,7 @@
       </c>
       <c r="C101" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D101" s="47" t="n">
@@ -9613,17 +9591,17 @@
       </c>
       <c r="C102" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D102" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F102" s="47" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="103">
@@ -9639,43 +9617,43 @@
       </c>
       <c r="C103" s="47" t="inlineStr">
         <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D103" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E103" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F103" s="47" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="47" t="inlineStr">
+        <is>
+          <t>Evelyn Santana Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="B104" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C104" s="47" t="inlineStr">
+        <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D103" s="47" t="n">
+      <c r="D104" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="E103" s="47" t="n">
+      <c r="E104" s="47" t="n">
         <v>1.5</v>
       </c>
-      <c r="F103" s="47" t="n">
+      <c r="F104" s="47" t="n">
         <v>-12</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="46" t="inlineStr">
-        <is>
-          <t>Fabiana de Figueredo Vieira</t>
-        </is>
-      </c>
-      <c r="B104" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C104" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D104" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F104" s="46" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="105">
@@ -9691,7 +9669,7 @@
       </c>
       <c r="C105" s="46" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D105" s="46" t="n">
@@ -9717,43 +9695,43 @@
       </c>
       <c r="C106" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D106" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F106" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="46" t="inlineStr">
+        <is>
+          <t>Fabiana de Figueredo Vieira</t>
+        </is>
+      </c>
+      <c r="B107" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C107" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D106" s="46" t="n">
+      <c r="D107" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E106" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F106" s="46" t="n">
+      <c r="E107" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="46" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="47" t="inlineStr">
-        <is>
-          <t>Fabiana de Figueredo Vieira</t>
-        </is>
-      </c>
-      <c r="B107" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C107" s="47" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D107" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E107" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F107" s="47" t="n">
-        <v>-0.6</v>
       </c>
     </row>
     <row r="108">
@@ -9769,7 +9747,7 @@
       </c>
       <c r="C108" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D108" s="47" t="n">
@@ -9795,7 +9773,7 @@
       </c>
       <c r="C109" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D109" s="47" t="n">
@@ -9809,55 +9787,55 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="46" t="inlineStr">
+      <c r="A110" s="47" t="inlineStr">
+        <is>
+          <t>Fabiana de Figueredo Vieira</t>
+        </is>
+      </c>
+      <c r="B110" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C110" s="47" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D110" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F110" s="47" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="46" t="inlineStr">
         <is>
           <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
-      <c r="B110" s="46" t="inlineStr">
+      <c r="B111" s="46" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C110" s="46" t="inlineStr">
+      <c r="C111" s="46" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D110" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F110" s="46" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="47" t="inlineStr">
-        <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
-        </is>
-      </c>
-      <c r="B111" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C111" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D111" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E111" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F111" s="47" t="n">
-        <v>-0.5</v>
+      <c r="D111" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -9873,17 +9851,17 @@
       </c>
       <c r="C112" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D112" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E112" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F112" s="47" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="113">
@@ -9899,7 +9877,7 @@
       </c>
       <c r="C113" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D113" s="47" t="n">
@@ -9925,17 +9903,17 @@
       </c>
       <c r="C114" s="47" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D114" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E114" s="47" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F114" s="47" t="n">
-        <v>-6</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="115">
@@ -9951,43 +9929,43 @@
       </c>
       <c r="C115" s="47" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D115" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E115" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F115" s="47" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="47" t="inlineStr">
+        <is>
+          <t>Gabriel Alan de Oliveira Martins</t>
+        </is>
+      </c>
+      <c r="B116" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C116" s="47" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D115" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E115" s="47" t="n">
+      <c r="D116" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="47" t="n">
         <v>0.3</v>
       </c>
-      <c r="F115" s="47" t="n">
+      <c r="F116" s="47" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="46" t="inlineStr">
-        <is>
-          <t>Geancarlos Ferreira Barrios</t>
-        </is>
-      </c>
-      <c r="B116" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C116" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D116" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F116" s="46" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="117">
@@ -10003,7 +9981,7 @@
       </c>
       <c r="C117" s="46" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D117" s="46" t="n">
@@ -10029,43 +10007,43 @@
       </c>
       <c r="C118" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D118" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F118" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="46" t="inlineStr">
+        <is>
+          <t>Geancarlos Ferreira Barrios</t>
+        </is>
+      </c>
+      <c r="B119" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C119" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D118" s="46" t="n">
+      <c r="D119" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E118" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F118" s="46" t="n">
+      <c r="E119" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="46" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="47" t="inlineStr">
-        <is>
-          <t>Geancarlos Ferreira Barrios</t>
-        </is>
-      </c>
-      <c r="B119" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C119" s="47" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D119" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E119" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F119" s="47" t="n">
-        <v>-0.6</v>
       </c>
     </row>
     <row r="120">
@@ -10081,7 +10059,7 @@
       </c>
       <c r="C120" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D120" s="47" t="n">
@@ -10107,7 +10085,7 @@
       </c>
       <c r="C121" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D121" s="47" t="n">
@@ -10121,29 +10099,29 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="46" t="inlineStr">
-        <is>
-          <t>Gilmar Bitencourt Luiz</t>
-        </is>
-      </c>
-      <c r="B122" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C122" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: pontualidade perfeita no período</t>
-        </is>
-      </c>
-      <c r="D122" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E122" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="F122" s="46" t="n">
-        <v>3</v>
+      <c r="A122" s="47" t="inlineStr">
+        <is>
+          <t>Geancarlos Ferreira Barrios</t>
+        </is>
+      </c>
+      <c r="B122" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C122" s="47" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D122" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F122" s="47" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="123">
@@ -10159,43 +10137,43 @@
       </c>
       <c r="C123" s="46" t="inlineStr">
         <is>
+          <t>Bônus: pontualidade perfeita no período</t>
+        </is>
+      </c>
+      <c r="D123" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="F123" s="46" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="46" t="inlineStr">
+        <is>
+          <t>Gilmar Bitencourt Luiz</t>
+        </is>
+      </c>
+      <c r="B124" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C124" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D123" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E123" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F123" s="46" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="47" t="inlineStr">
-        <is>
-          <t>Gilmar Bitencourt Luiz</t>
-        </is>
-      </c>
-      <c r="B124" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C124" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D124" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F124" s="47" t="n">
-        <v>-0.5</v>
+      <c r="D124" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -10211,17 +10189,17 @@
       </c>
       <c r="C125" s="47" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D125" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125" s="47" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="F125" s="47" t="n">
-        <v>-6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="126">
@@ -10237,43 +10215,43 @@
       </c>
       <c r="C126" s="47" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D126" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E126" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F126" s="47" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="47" t="inlineStr">
+        <is>
+          <t>Gilmar Bitencourt Luiz</t>
+        </is>
+      </c>
+      <c r="B127" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C127" s="47" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D126" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" s="47" t="n">
+      <c r="D127" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" s="47" t="n">
         <v>0.3</v>
       </c>
-      <c r="F126" s="47" t="n">
+      <c r="F127" s="47" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="46" t="inlineStr">
-        <is>
-          <t>Gisele Lopes Justiniano</t>
-        </is>
-      </c>
-      <c r="B127" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C127" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D127" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E127" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F127" s="46" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="128">
@@ -10289,43 +10267,43 @@
       </c>
       <c r="C128" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D128" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F128" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="46" t="inlineStr">
+        <is>
+          <t>Gisele Lopes Justiniano</t>
+        </is>
+      </c>
+      <c r="B129" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C129" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D128" s="46" t="n">
+      <c r="D129" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E128" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F128" s="46" t="n">
+      <c r="E129" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="46" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="47" t="inlineStr">
-        <is>
-          <t>Gisele Lopes Justiniano</t>
-        </is>
-      </c>
-      <c r="B129" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C129" s="47" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D129" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E129" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F129" s="47" t="n">
-        <v>-0.6</v>
       </c>
     </row>
     <row r="130">
@@ -10341,7 +10319,7 @@
       </c>
       <c r="C130" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D130" s="47" t="n">
@@ -10367,17 +10345,17 @@
       </c>
       <c r="C131" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D131" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E131" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F131" s="47" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="132">
@@ -10393,17 +10371,17 @@
       </c>
       <c r="C132" s="47" t="inlineStr">
         <is>
-          <t>Visita em sequência suspeita</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D132" s="47" t="n">
         <v>2</v>
       </c>
       <c r="E132" s="47" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="F132" s="47" t="n">
-        <v>-4</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="133">
@@ -10419,43 +10397,43 @@
       </c>
       <c r="C133" s="47" t="inlineStr">
         <is>
+          <t>Visita em sequência suspeita</t>
+        </is>
+      </c>
+      <c r="D133" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E133" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" s="47" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="47" t="inlineStr">
+        <is>
+          <t>Gisele Lopes Justiniano</t>
+        </is>
+      </c>
+      <c r="B134" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C134" s="47" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D133" s="47" t="n">
+      <c r="D134" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="E133" s="47" t="n">
+      <c r="E134" s="47" t="n">
         <v>0.3</v>
       </c>
-      <c r="F133" s="47" t="n">
+      <c r="F134" s="47" t="n">
         <v>-5.4</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="46" t="inlineStr">
-        <is>
-          <t>Gisele Olimpia Torres</t>
-        </is>
-      </c>
-      <c r="B134" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C134" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D134" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E134" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F134" s="46" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="135">
@@ -10471,43 +10449,43 @@
       </c>
       <c r="C135" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D135" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F135" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="46" t="inlineStr">
+        <is>
+          <t>Gisele Olimpia Torres</t>
+        </is>
+      </c>
+      <c r="B136" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C136" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D135" s="46" t="n">
+      <c r="D136" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E135" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F135" s="46" t="n">
+      <c r="E136" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" s="46" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="47" t="inlineStr">
-        <is>
-          <t>Gisele Olimpia Torres</t>
-        </is>
-      </c>
-      <c r="B136" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C136" s="47" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D136" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E136" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F136" s="47" t="n">
-        <v>-1.2</v>
       </c>
     </row>
     <row r="137">
@@ -10523,17 +10501,17 @@
       </c>
       <c r="C137" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D137" s="47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E137" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F137" s="47" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="138">
@@ -10549,69 +10527,69 @@
       </c>
       <c r="C138" s="47" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D138" s="47" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E138" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F138" s="47" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="47" t="inlineStr">
+        <is>
+          <t>Gisele Olimpia Torres</t>
+        </is>
+      </c>
+      <c r="B139" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C139" s="47" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D139" s="47" t="n">
+        <v>14</v>
+      </c>
+      <c r="E139" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F139" s="47" t="n">
         <v>-8.4</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="46" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="46" t="inlineStr">
         <is>
           <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
-      <c r="B139" s="46" t="inlineStr">
+      <c r="B140" s="46" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C139" s="46" t="inlineStr">
+      <c r="C140" s="46" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D139" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E139" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F139" s="46" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="47" t="inlineStr">
-        <is>
-          <t>Juliana Patricia Goncalves</t>
-        </is>
-      </c>
-      <c r="B140" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C140" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D140" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E140" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F140" s="47" t="n">
-        <v>-0.5</v>
+      <c r="D140" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" s="46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -10627,17 +10605,17 @@
       </c>
       <c r="C141" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D141" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E141" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F141" s="47" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="142">
@@ -10653,17 +10631,17 @@
       </c>
       <c r="C142" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D142" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F142" s="47" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="143">
@@ -10679,17 +10657,17 @@
       </c>
       <c r="C143" s="47" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D143" s="47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E143" s="47" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F143" s="47" t="n">
-        <v>-9</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="144">
@@ -10705,43 +10683,43 @@
       </c>
       <c r="C144" s="47" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D144" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="E144" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F144" s="47" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="47" t="inlineStr">
+        <is>
+          <t>Juliana Patricia Goncalves</t>
+        </is>
+      </c>
+      <c r="B145" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C145" s="47" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D144" s="47" t="n">
+      <c r="D145" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="E144" s="47" t="n">
+      <c r="E145" s="47" t="n">
         <v>0.3</v>
       </c>
-      <c r="F144" s="47" t="n">
+      <c r="F145" s="47" t="n">
         <v>-4.8</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="46" t="inlineStr">
-        <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
-        </is>
-      </c>
-      <c r="B145" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C145" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D145" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E145" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F145" s="46" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="146">
@@ -10757,43 +10735,43 @@
       </c>
       <c r="C146" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D146" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F146" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="46" t="inlineStr">
+        <is>
+          <t>Kariele Jackeline Rodrigues Silva</t>
+        </is>
+      </c>
+      <c r="B147" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C147" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D146" s="46" t="n">
+      <c r="D147" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E146" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F146" s="46" t="n">
+      <c r="E147" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" s="46" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="47" t="inlineStr">
-        <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
-        </is>
-      </c>
-      <c r="B147" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C147" s="47" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D147" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E147" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F147" s="47" t="n">
-        <v>-1.2</v>
       </c>
     </row>
     <row r="148">
@@ -10809,7 +10787,7 @@
       </c>
       <c r="C148" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D148" s="47" t="n">
@@ -10835,7 +10813,7 @@
       </c>
       <c r="C149" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D149" s="47" t="n">
@@ -10861,43 +10839,43 @@
       </c>
       <c r="C150" s="47" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D150" s="47" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="E150" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F150" s="47" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="47" t="inlineStr">
+        <is>
+          <t>Kariele Jackeline Rodrigues Silva</t>
+        </is>
+      </c>
+      <c r="B151" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C151" s="47" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D151" s="47" t="n">
+        <v>37</v>
+      </c>
+      <c r="E151" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F151" s="47" t="n">
         <v>-22.2</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="46" t="inlineStr">
-        <is>
-          <t>Kátia Cilene Silveira Machado</t>
-        </is>
-      </c>
-      <c r="B151" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C151" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D151" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E151" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F151" s="46" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="152">
@@ -10913,43 +10891,43 @@
       </c>
       <c r="C152" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D152" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F152" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="46" t="inlineStr">
+        <is>
+          <t>Kátia Cilene Silveira Machado</t>
+        </is>
+      </c>
+      <c r="B153" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C153" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D152" s="46" t="n">
+      <c r="D153" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="E152" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F152" s="46" t="n">
+      <c r="E153" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" s="46" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="47" t="inlineStr">
-        <is>
-          <t>Kátia Cilene Silveira Machado</t>
-        </is>
-      </c>
-      <c r="B153" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C153" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D153" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E153" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F153" s="47" t="n">
-        <v>-0.5</v>
       </c>
     </row>
     <row r="154">
@@ -10965,17 +10943,17 @@
       </c>
       <c r="C154" s="47" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D154" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E154" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F154" s="47" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="155">
@@ -10991,17 +10969,17 @@
       </c>
       <c r="C155" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D155" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E155" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F155" s="47" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="156">
@@ -11017,17 +10995,17 @@
       </c>
       <c r="C156" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D156" s="47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E156" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F156" s="47" t="n">
-        <v>-1.8</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="157">
@@ -11043,17 +11021,17 @@
       </c>
       <c r="C157" s="47" t="inlineStr">
         <is>
-          <t>Visita fora do expediente/fim de semana</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D157" s="47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E157" s="47" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F157" s="47" t="n">
-        <v>-1</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="158">
@@ -11069,43 +11047,43 @@
       </c>
       <c r="C158" s="47" t="inlineStr">
         <is>
+          <t>Visita fora do expediente/fim de semana</t>
+        </is>
+      </c>
+      <c r="D158" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F158" s="47" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="47" t="inlineStr">
+        <is>
+          <t>Kátia Cilene Silveira Machado</t>
+        </is>
+      </c>
+      <c r="B159" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C159" s="47" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D158" s="47" t="n">
+      <c r="D159" s="47" t="n">
         <v>6</v>
       </c>
-      <c r="E158" s="47" t="n">
+      <c r="E159" s="47" t="n">
         <v>0.3</v>
       </c>
-      <c r="F158" s="47" t="n">
+      <c r="F159" s="47" t="n">
         <v>-3.6</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="46" t="inlineStr">
-        <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
-        </is>
-      </c>
-      <c r="B159" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C159" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D159" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E159" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F159" s="46" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="160">
@@ -11121,7 +11099,7 @@
       </c>
       <c r="C160" s="46" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D160" s="46" t="n">
@@ -11147,43 +11125,43 @@
       </c>
       <c r="C161" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D161" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F161" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="46" t="inlineStr">
+        <is>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
+        </is>
+      </c>
+      <c r="B162" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C162" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D161" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E161" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F161" s="46" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="47" t="inlineStr">
-        <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
-        </is>
-      </c>
-      <c r="B162" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C162" s="47" t="inlineStr">
-        <is>
-          <t>Fim manhã antes de 10h00</t>
-        </is>
-      </c>
-      <c r="D162" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E162" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F162" s="47" t="n">
-        <v>-0.6</v>
+      <c r="D162" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" s="46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -11199,7 +11177,7 @@
       </c>
       <c r="C163" s="47" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D163" s="47" t="n">
@@ -11213,55 +11191,55 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="46" t="inlineStr">
+      <c r="A164" s="47" t="inlineStr">
+        <is>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
+        </is>
+      </c>
+      <c r="B164" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C164" s="47" t="inlineStr">
+        <is>
+          <t>Fim tarde antes de 16h00</t>
+        </is>
+      </c>
+      <c r="D164" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F164" s="47" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="46" t="inlineStr">
         <is>
           <t>Mateus Falcao de Souza</t>
         </is>
       </c>
-      <c r="B164" s="46" t="inlineStr">
+      <c r="B165" s="46" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C164" s="46" t="inlineStr">
+      <c r="C165" s="46" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D164" s="46" t="n">
+      <c r="D165" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="E164" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F164" s="46" t="n">
+      <c r="E165" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F165" s="46" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="47" t="inlineStr">
-        <is>
-          <t>Mateus Falcao de Souza</t>
-        </is>
-      </c>
-      <c r="B165" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C165" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D165" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E165" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F165" s="47" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="166">
@@ -11277,17 +11255,17 @@
       </c>
       <c r="C166" s="47" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D166" s="47" t="n">
         <v>2</v>
       </c>
       <c r="E166" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F166" s="47" t="n">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="167">
@@ -11303,17 +11281,17 @@
       </c>
       <c r="C167" s="47" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D167" s="47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E167" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F167" s="47" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="168">
@@ -11329,7 +11307,7 @@
       </c>
       <c r="C168" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D168" s="47" t="n">
@@ -11355,7 +11333,7 @@
       </c>
       <c r="C169" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D169" s="47" t="n">
@@ -11381,17 +11359,17 @@
       </c>
       <c r="C170" s="47" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D170" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E170" s="47" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F170" s="47" t="n">
-        <v>-3</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="171">
@@ -11407,69 +11385,69 @@
       </c>
       <c r="C171" s="47" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D171" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F171" s="47" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="47" t="inlineStr">
+        <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+      <c r="B172" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C172" s="47" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D171" s="47" t="n">
+      <c r="D172" s="47" t="n">
         <v>79</v>
       </c>
-      <c r="E171" s="47" t="n">
+      <c r="E172" s="47" t="n">
         <v>0.3</v>
       </c>
-      <c r="F171" s="47" t="n">
+      <c r="F172" s="47" t="n">
         <v>-47.4</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="46" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="46" t="inlineStr">
         <is>
           <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
-      <c r="B172" s="46" t="inlineStr">
+      <c r="B173" s="46" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C172" s="46" t="inlineStr">
+      <c r="C173" s="46" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D172" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E172" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F172" s="46" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="47" t="inlineStr">
-        <is>
-          <t>Miglidiane Maciel Ajala</t>
-        </is>
-      </c>
-      <c r="B173" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C173" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D173" s="47" t="n">
-        <v>3</v>
-      </c>
-      <c r="E173" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F173" s="47" t="n">
-        <v>-1.5</v>
+      <c r="D173" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E173" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" s="46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -11485,17 +11463,17 @@
       </c>
       <c r="C174" s="47" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D174" s="47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E174" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F174" s="47" t="n">
-        <v>-1.2</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="175">
@@ -11511,7 +11489,7 @@
       </c>
       <c r="C175" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D175" s="47" t="n">
@@ -11537,17 +11515,17 @@
       </c>
       <c r="C176" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D176" s="47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E176" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F176" s="47" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="177">
@@ -11563,17 +11541,17 @@
       </c>
       <c r="C177" s="47" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D177" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E177" s="47" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F177" s="47" t="n">
-        <v>-3</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="178">
@@ -11589,69 +11567,69 @@
       </c>
       <c r="C178" s="47" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D178" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F178" s="47" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="47" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="B179" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C179" s="47" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D178" s="47" t="n">
+      <c r="D179" s="47" t="n">
         <v>17</v>
       </c>
-      <c r="E178" s="47" t="n">
+      <c r="E179" s="47" t="n">
         <v>0.3</v>
       </c>
-      <c r="F178" s="47" t="n">
+      <c r="F179" s="47" t="n">
         <v>-10.2</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="46" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="46" t="inlineStr">
         <is>
           <t>Naime Cristina Freitas</t>
         </is>
       </c>
-      <c r="B179" s="46" t="inlineStr">
+      <c r="B180" s="46" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C179" s="46" t="inlineStr">
+      <c r="C180" s="46" t="inlineStr">
         <is>
           <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
-      <c r="D179" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E179" s="46" t="n">
+      <c r="D180" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="F179" s="46" t="n">
+      <c r="F180" s="46" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="47" t="inlineStr">
-        <is>
-          <t>Naime Cristina Freitas</t>
-        </is>
-      </c>
-      <c r="B180" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C180" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D180" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E180" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F180" s="47" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="181">
@@ -11667,17 +11645,17 @@
       </c>
       <c r="C181" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D181" s="47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E181" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F181" s="47" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="182">
@@ -11693,7 +11671,7 @@
       </c>
       <c r="C182" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D182" s="47" t="n">
@@ -11719,43 +11697,43 @@
       </c>
       <c r="C183" s="47" t="inlineStr">
         <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D183" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F183" s="47" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="47" t="inlineStr">
+        <is>
+          <t>Naime Cristina Freitas</t>
+        </is>
+      </c>
+      <c r="B184" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C184" s="47" t="inlineStr">
+        <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D183" s="47" t="n">
+      <c r="D184" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="E183" s="47" t="n">
+      <c r="E184" s="47" t="n">
         <v>1.5</v>
       </c>
-      <c r="F183" s="47" t="n">
+      <c r="F184" s="47" t="n">
         <v>-6</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="46" t="inlineStr">
-        <is>
-          <t>Rafael Ramos Recalde</t>
-        </is>
-      </c>
-      <c r="B184" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C184" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D184" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E184" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F184" s="46" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="185">
@@ -11771,43 +11749,43 @@
       </c>
       <c r="C185" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D185" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E185" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F185" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="46" t="inlineStr">
+        <is>
+          <t>Rafael Ramos Recalde</t>
+        </is>
+      </c>
+      <c r="B186" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C186" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D185" s="46" t="n">
+      <c r="D186" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E185" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F185" s="46" t="n">
+      <c r="E186" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F186" s="46" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="47" t="inlineStr">
-        <is>
-          <t>Rafael Ramos Recalde</t>
-        </is>
-      </c>
-      <c r="B186" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C186" s="47" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D186" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E186" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F186" s="47" t="n">
-        <v>-1.2</v>
       </c>
     </row>
     <row r="187">
@@ -11823,7 +11801,7 @@
       </c>
       <c r="C187" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D187" s="47" t="n">
@@ -11849,43 +11827,43 @@
       </c>
       <c r="C188" s="47" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D188" s="47" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E188" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F188" s="47" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="47" t="inlineStr">
+        <is>
+          <t>Rafael Ramos Recalde</t>
+        </is>
+      </c>
+      <c r="B189" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C189" s="47" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D189" s="47" t="n">
+        <v>50</v>
+      </c>
+      <c r="E189" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F189" s="47" t="n">
         <v>-30</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="46" t="inlineStr">
-        <is>
-          <t>Raquel Ortiz dos Santos</t>
-        </is>
-      </c>
-      <c r="B189" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C189" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D189" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E189" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F189" s="46" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="190">
@@ -11901,43 +11879,43 @@
       </c>
       <c r="C190" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D190" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E190" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F190" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="46" t="inlineStr">
+        <is>
+          <t>Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B191" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C191" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D190" s="46" t="n">
+      <c r="D191" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="E190" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F190" s="46" t="n">
+      <c r="E191" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F191" s="46" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="47" t="inlineStr">
-        <is>
-          <t>Raquel Ortiz dos Santos</t>
-        </is>
-      </c>
-      <c r="B191" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C191" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D191" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E191" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F191" s="47" t="n">
-        <v>-0.5</v>
       </c>
     </row>
     <row r="192">
@@ -11953,17 +11931,17 @@
       </c>
       <c r="C192" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D192" s="47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E192" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F192" s="47" t="n">
-        <v>-1.8</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="193">
@@ -11979,17 +11957,17 @@
       </c>
       <c r="C193" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D193" s="47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E193" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F193" s="47" t="n">
-        <v>-1.2</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="194">
@@ -12005,17 +11983,17 @@
       </c>
       <c r="C194" s="47" t="inlineStr">
         <is>
-          <t>Visita fora do expediente/fim de semana</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D194" s="47" t="n">
         <v>2</v>
       </c>
       <c r="E194" s="47" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F194" s="47" t="n">
-        <v>-2</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="195">
@@ -12031,43 +12009,43 @@
       </c>
       <c r="C195" s="47" t="inlineStr">
         <is>
+          <t>Visita fora do expediente/fim de semana</t>
+        </is>
+      </c>
+      <c r="D195" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E195" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F195" s="47" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="47" t="inlineStr">
+        <is>
+          <t>Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B196" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C196" s="47" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D195" s="47" t="n">
+      <c r="D196" s="47" t="n">
         <v>32</v>
       </c>
-      <c r="E195" s="47" t="n">
+      <c r="E196" s="47" t="n">
         <v>0.3</v>
       </c>
-      <c r="F195" s="47" t="n">
+      <c r="F196" s="47" t="n">
         <v>-19.2</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="46" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-      <c r="B196" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C196" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D196" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E196" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F196" s="46" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="197">
@@ -12083,7 +12061,7 @@
       </c>
       <c r="C197" s="46" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D197" s="46" t="n">
@@ -12109,43 +12087,43 @@
       </c>
       <c r="C198" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D198" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F198" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="46" t="inlineStr">
+        <is>
+          <t>Rosalina Beniel Vargas</t>
+        </is>
+      </c>
+      <c r="B199" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C199" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D198" s="46" t="n">
+      <c r="D199" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="E198" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F198" s="46" t="n">
+      <c r="E199" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" s="46" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="47" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-      <c r="B199" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C199" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D199" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E199" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F199" s="47" t="n">
-        <v>-0.5</v>
       </c>
     </row>
     <row r="200">
@@ -12161,17 +12139,17 @@
       </c>
       <c r="C200" s="47" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D200" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E200" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F200" s="47" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="201">
@@ -12187,7 +12165,7 @@
       </c>
       <c r="C201" s="47" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D201" s="47" t="n">
@@ -12213,7 +12191,7 @@
       </c>
       <c r="C202" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D202" s="47" t="n">
@@ -12239,7 +12217,7 @@
       </c>
       <c r="C203" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D203" s="47" t="n">
@@ -12253,55 +12231,55 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="46" t="inlineStr">
+      <c r="A204" s="47" t="inlineStr">
+        <is>
+          <t>Rosalina Beniel Vargas</t>
+        </is>
+      </c>
+      <c r="B204" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C204" s="47" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D204" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E204" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F204" s="47" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="46" t="inlineStr">
         <is>
           <t>Rozana Reis da Silva</t>
         </is>
       </c>
-      <c r="B204" s="46" t="inlineStr">
+      <c r="B205" s="46" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C204" s="46" t="inlineStr">
+      <c r="C205" s="46" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D204" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E204" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F204" s="46" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="47" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="B205" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C205" s="47" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D205" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E205" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F205" s="47" t="n">
-        <v>-0.6</v>
+      <c r="D205" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F205" s="46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="206">
@@ -12317,7 +12295,7 @@
       </c>
       <c r="C206" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D206" s="47" t="n">
@@ -12343,17 +12321,17 @@
       </c>
       <c r="C207" s="47" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D207" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E207" s="47" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F207" s="47" t="n">
-        <v>-6</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="208">
@@ -12369,43 +12347,43 @@
       </c>
       <c r="C208" s="47" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D208" s="47" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E208" s="47" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="F208" s="47" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="47" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="B209" s="47" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C209" s="47" t="inlineStr">
         <is>
-          <t>Dia sem bater a meta diária</t>
+          <t>Visita rápida</t>
         </is>
       </c>
       <c r="D209" s="47" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E209" s="47" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F209" s="47" t="n">
-        <v>-0.5</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="210">
@@ -12421,17 +12399,17 @@
       </c>
       <c r="C210" s="47" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D210" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E210" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F210" s="47" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="211">
@@ -12447,7 +12425,7 @@
       </c>
       <c r="C211" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D211" s="47" t="n">
@@ -12473,17 +12451,17 @@
       </c>
       <c r="C212" s="47" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D212" s="47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E212" s="47" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F212" s="47" t="n">
-        <v>-12</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="213">
@@ -12499,17 +12477,17 @@
       </c>
       <c r="C213" s="47" t="inlineStr">
         <is>
-          <t>Visita fora do expediente/fim de semana</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D213" s="47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E213" s="47" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F213" s="47" t="n">
-        <v>-1</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="214">
@@ -12525,69 +12503,69 @@
       </c>
       <c r="C214" s="47" t="inlineStr">
         <is>
+          <t>Visita fora do expediente/fim de semana</t>
+        </is>
+      </c>
+      <c r="D214" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E214" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F214" s="47" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="47" t="inlineStr">
+        <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B215" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C215" s="47" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D214" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E214" s="47" t="n">
+      <c r="D215" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E215" s="47" t="n">
         <v>0.3</v>
       </c>
-      <c r="F214" s="47" t="n">
+      <c r="F215" s="47" t="n">
         <v>-0.6</v>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="46" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="46" t="inlineStr">
         <is>
           <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
-      <c r="B215" s="46" t="inlineStr">
+      <c r="B216" s="46" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C215" s="46" t="inlineStr">
+      <c r="C216" s="46" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D215" s="46" t="n">
+      <c r="D216" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="E215" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F215" s="46" t="n">
+      <c r="E216" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F216" s="46" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="47" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="B216" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C216" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D216" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E216" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F216" s="47" t="n">
-        <v>-0.5</v>
       </c>
     </row>
     <row r="217">
@@ -12603,17 +12581,17 @@
       </c>
       <c r="C217" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D217" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E217" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F217" s="47" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="218">
@@ -12629,17 +12607,17 @@
       </c>
       <c r="C218" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D218" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E218" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F218" s="47" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="219">
@@ -12655,17 +12633,17 @@
       </c>
       <c r="C219" s="47" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D219" s="47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E219" s="47" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F219" s="47" t="n">
-        <v>-3</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="220">
@@ -12681,43 +12659,43 @@
       </c>
       <c r="C220" s="47" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D220" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E220" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F220" s="47" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="47" t="inlineStr">
+        <is>
+          <t>Sara Eliane Talaveira de Oliveira</t>
+        </is>
+      </c>
+      <c r="B221" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C221" s="47" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D220" s="47" t="n">
+      <c r="D221" s="47" t="n">
         <v>11</v>
       </c>
-      <c r="E220" s="47" t="n">
+      <c r="E221" s="47" t="n">
         <v>0.3</v>
       </c>
-      <c r="F220" s="47" t="n">
+      <c r="F221" s="47" t="n">
         <v>-6.6</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="46" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="B221" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C221" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D221" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E221" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F221" s="46" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="222">
@@ -12733,43 +12711,43 @@
       </c>
       <c r="C222" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D222" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E222" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F222" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="46" t="inlineStr">
+        <is>
+          <t>Selba Ramona Afonso</t>
+        </is>
+      </c>
+      <c r="B223" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C223" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D222" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E222" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F222" s="46" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="47" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="B223" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C223" s="47" t="inlineStr">
-        <is>
-          <t>Início tarde após 14h30</t>
-        </is>
-      </c>
-      <c r="D223" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E223" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F223" s="47" t="n">
-        <v>-0.6</v>
+      <c r="D223" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E223" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F223" s="46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="224">
@@ -12785,43 +12763,43 @@
       </c>
       <c r="C224" s="47" t="inlineStr">
         <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D224" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E224" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F224" s="47" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="47" t="inlineStr">
+        <is>
+          <t>Selba Ramona Afonso</t>
+        </is>
+      </c>
+      <c r="B225" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C225" s="47" t="inlineStr">
+        <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D224" s="47" t="n">
+      <c r="D225" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="E224" s="47" t="n">
+      <c r="E225" s="47" t="n">
         <v>1.5</v>
       </c>
-      <c r="F224" s="47" t="n">
+      <c r="F225" s="47" t="n">
         <v>-6</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="46" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="B225" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C225" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D225" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E225" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F225" s="46" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="226">
@@ -12837,43 +12815,43 @@
       </c>
       <c r="C226" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D226" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E226" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F226" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="46" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B227" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C227" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D226" s="46" t="n">
+      <c r="D227" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E226" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F226" s="46" t="n">
+      <c r="E227" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F227" s="46" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="47" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="B227" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C227" s="47" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D227" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E227" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F227" s="47" t="n">
-        <v>-1.2</v>
       </c>
     </row>
     <row r="228">
@@ -12889,7 +12867,7 @@
       </c>
       <c r="C228" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D228" s="47" t="n">
@@ -12915,43 +12893,43 @@
       </c>
       <c r="C229" s="47" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D229" s="47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E229" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F229" s="47" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="47" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B230" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C230" s="47" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D230" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="E230" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F230" s="47" t="n">
         <v>-3</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="46" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B230" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C230" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D230" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E230" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F230" s="46" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="231">
@@ -12967,7 +12945,7 @@
       </c>
       <c r="C231" s="46" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D231" s="46" t="n">
@@ -12993,43 +12971,43 @@
       </c>
       <c r="C232" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D232" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E232" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F232" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="46" t="inlineStr">
+        <is>
+          <t>Suely Aguiar Alves Luiz</t>
+        </is>
+      </c>
+      <c r="B233" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C233" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D232" s="46" t="n">
+      <c r="D233" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E232" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F232" s="46" t="n">
+      <c r="E233" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F233" s="46" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="47" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B233" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C233" s="47" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D233" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E233" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F233" s="47" t="n">
-        <v>-0.6</v>
       </c>
     </row>
     <row r="234">
@@ -13045,7 +13023,7 @@
       </c>
       <c r="C234" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D234" s="47" t="n">
@@ -13071,43 +13049,43 @@
       </c>
       <c r="C235" s="47" t="inlineStr">
         <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D235" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E235" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F235" s="47" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="47" t="inlineStr">
+        <is>
+          <t>Suely Aguiar Alves Luiz</t>
+        </is>
+      </c>
+      <c r="B236" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C236" s="47" t="inlineStr">
+        <is>
           <t>Visita em sequência suspeita</t>
         </is>
       </c>
-      <c r="D235" s="47" t="n">
+      <c r="D236" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="E235" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="F235" s="47" t="n">
+      <c r="E236" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F236" s="47" t="n">
         <v>-4</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="46" t="inlineStr">
-        <is>
-          <t>Tania Maria Montania</t>
-        </is>
-      </c>
-      <c r="B236" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C236" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D236" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E236" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F236" s="46" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="237">
@@ -13123,43 +13101,43 @@
       </c>
       <c r="C237" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D237" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F237" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="46" t="inlineStr">
+        <is>
+          <t>Tania Maria Montania</t>
+        </is>
+      </c>
+      <c r="B238" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C238" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D237" s="46" t="n">
+      <c r="D238" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E237" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F237" s="46" t="n">
+      <c r="E238" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F238" s="46" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="47" t="inlineStr">
-        <is>
-          <t>Tania Maria Montania</t>
-        </is>
-      </c>
-      <c r="B238" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C238" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D238" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E238" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F238" s="47" t="n">
-        <v>-0.5</v>
       </c>
     </row>
     <row r="239">
@@ -13175,17 +13153,17 @@
       </c>
       <c r="C239" s="47" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D239" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E239" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F239" s="47" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="240">
@@ -13201,17 +13179,17 @@
       </c>
       <c r="C240" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D240" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E240" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F240" s="47" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="241">
@@ -13227,17 +13205,17 @@
       </c>
       <c r="C241" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D241" s="47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E241" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F241" s="47" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="242">
@@ -13253,7 +13231,7 @@
       </c>
       <c r="C242" s="47" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D242" s="47" t="n">
@@ -13267,55 +13245,55 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="46" t="inlineStr">
+      <c r="A243" s="47" t="inlineStr">
+        <is>
+          <t>Tania Maria Montania</t>
+        </is>
+      </c>
+      <c r="B243" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C243" s="47" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D243" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E243" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F243" s="47" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="46" t="inlineStr">
         <is>
           <t>Walquiria Araujo Flores</t>
         </is>
       </c>
-      <c r="B243" s="46" t="inlineStr">
+      <c r="B244" s="46" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C243" s="46" t="inlineStr">
+      <c r="C244" s="46" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D243" s="46" t="n">
+      <c r="D244" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="E243" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F243" s="46" t="n">
+      <c r="E244" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F244" s="46" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="47" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="B244" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C244" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D244" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E244" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F244" s="47" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="245">
@@ -13331,17 +13309,17 @@
       </c>
       <c r="C245" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D245" s="47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E245" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F245" s="47" t="n">
-        <v>-2.4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="246">
@@ -13357,17 +13335,17 @@
       </c>
       <c r="C246" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D246" s="47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E246" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F246" s="47" t="n">
-        <v>-1.2</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="247">
@@ -13383,17 +13361,17 @@
       </c>
       <c r="C247" s="47" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D247" s="47" t="n">
         <v>2</v>
       </c>
       <c r="E247" s="47" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F247" s="47" t="n">
-        <v>-6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="248">
@@ -13409,43 +13387,43 @@
       </c>
       <c r="C248" s="47" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D248" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E248" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F248" s="47" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="47" t="inlineStr">
+        <is>
+          <t>Walquiria Araujo Flores</t>
+        </is>
+      </c>
+      <c r="B249" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C249" s="47" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D248" s="47" t="n">
+      <c r="D249" s="47" t="n">
         <v>11</v>
       </c>
-      <c r="E248" s="47" t="n">
+      <c r="E249" s="47" t="n">
         <v>0.3</v>
       </c>
-      <c r="F248" s="47" t="n">
+      <c r="F249" s="47" t="n">
         <v>-6.6</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="46" t="inlineStr">
-        <is>
-          <t>Wesley de Souza Leal</t>
-        </is>
-      </c>
-      <c r="B249" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C249" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D249" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E249" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F249" s="46" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="250">
@@ -13461,43 +13439,43 @@
       </c>
       <c r="C250" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D250" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E250" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F250" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="46" t="inlineStr">
+        <is>
+          <t>Wesley de Souza Leal</t>
+        </is>
+      </c>
+      <c r="B251" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C251" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D250" s="46" t="n">
+      <c r="D251" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="E250" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F250" s="46" t="n">
+      <c r="E251" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F251" s="46" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="47" t="inlineStr">
-        <is>
-          <t>Wesley de Souza Leal</t>
-        </is>
-      </c>
-      <c r="B251" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C251" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D251" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E251" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F251" s="47" t="n">
-        <v>-0.5</v>
       </c>
     </row>
     <row r="252">
@@ -13513,17 +13491,17 @@
       </c>
       <c r="C252" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D252" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E252" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F252" s="47" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="253">
@@ -13539,17 +13517,17 @@
       </c>
       <c r="C253" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D253" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E253" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F253" s="47" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="254">
@@ -13565,7 +13543,7 @@
       </c>
       <c r="C254" s="47" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D254" s="47" t="n">
@@ -13579,29 +13557,29 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="46" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B255" s="46" t="inlineStr">
+      <c r="A255" s="47" t="inlineStr">
+        <is>
+          <t>Wesley de Souza Leal</t>
+        </is>
+      </c>
+      <c r="B255" s="47" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C255" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D255" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E255" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F255" s="46" t="n">
-        <v>5</v>
+      <c r="C255" s="47" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D255" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E255" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F255" s="47" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="256">
@@ -13617,7 +13595,7 @@
       </c>
       <c r="C256" s="46" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D256" s="46" t="n">
@@ -13643,43 +13621,43 @@
       </c>
       <c r="C257" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D257" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E257" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F257" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="46" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B258" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C258" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D257" s="46" t="n">
+      <c r="D258" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E257" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F257" s="46" t="n">
+      <c r="E258" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F258" s="46" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="47" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B258" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C258" s="47" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D258" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E258" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F258" s="47" t="n">
-        <v>-0.6</v>
       </c>
     </row>
     <row r="259">
@@ -13695,16 +13673,42 @@
       </c>
       <c r="C259" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D259" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E259" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F259" s="47" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="47" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B260" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C260" s="47" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D260" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E260" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F260" s="47" t="n">
         <v>-1.2</v>
       </c>
     </row>
@@ -14268,56 +14272,56 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>410 - SALGADO FILHO</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F11" s="6" t="n">
+      <c r="D11" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Q010, Q011, Q012</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Q011, Q012</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>15.38</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>25.71</v>
-      </c>
-      <c r="N11" s="6" t="inlineStr">
-        <is>
-          <t>🟡 ATENÇÃO</t>
+      <c r="J11" s="4" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>32.89</v>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
@@ -19733,7 +19737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -19748,7 +19752,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (32 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
+          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (30 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -20077,11 +20081,11 @@
     </row>
     <row r="11">
       <c r="A11" s="34" t="n">
-        <v>470</v>
+        <v>1935</v>
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="C11" s="34" t="inlineStr">
@@ -20112,11 +20116,11 @@
     </row>
     <row r="12">
       <c r="A12" s="34" t="n">
-        <v>1935</v>
+        <v>30</v>
       </c>
       <c r="B12" s="34" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="C12" s="34" t="inlineStr">
@@ -20147,11 +20151,11 @@
     </row>
     <row r="13">
       <c r="A13" s="34" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="C13" s="34" t="inlineStr">
@@ -20171,7 +20175,7 @@
       </c>
       <c r="F13" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G13" s="34" t="inlineStr">
@@ -20182,11 +20186,11 @@
     </row>
     <row r="14">
       <c r="A14" s="34" t="n">
-        <v>73</v>
+        <v>1935</v>
       </c>
       <c r="B14" s="34" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="C14" s="34" t="inlineStr">
@@ -20217,11 +20221,11 @@
     </row>
     <row r="15">
       <c r="A15" s="34" t="n">
-        <v>470</v>
+        <v>30</v>
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="C15" s="34" t="inlineStr">
@@ -20252,26 +20256,26 @@
     </row>
     <row r="16">
       <c r="A16" s="34" t="n">
-        <v>1935</v>
+        <v>2030</v>
       </c>
       <c r="B16" s="34" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="C16" s="34" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D16" s="34" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E16" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F16" s="34" t="inlineStr">
@@ -20287,16 +20291,16 @@
     </row>
     <row r="17">
       <c r="A17" s="34" t="n">
-        <v>30</v>
+        <v>151</v>
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D17" s="34" t="inlineStr">
@@ -20311,7 +20315,7 @@
       </c>
       <c r="F17" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G17" s="34" t="inlineStr">
@@ -20322,11 +20326,11 @@
     </row>
     <row r="18">
       <c r="A18" s="34" t="n">
-        <v>2030</v>
+        <v>151</v>
       </c>
       <c r="B18" s="34" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C18" s="34" t="inlineStr">
@@ -20336,12 +20340,12 @@
       </c>
       <c r="D18" s="34" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E18" s="34" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F18" s="34" t="inlineStr">
@@ -20357,26 +20361,26 @@
     </row>
     <row r="19">
       <c r="A19" s="34" t="n">
-        <v>151</v>
+        <v>2721</v>
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C19" s="34" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D19" s="34" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E19" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F19" s="34" t="inlineStr">
@@ -20392,26 +20396,26 @@
     </row>
     <row r="20">
       <c r="A20" s="34" t="n">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="B20" s="34" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C20" s="34" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D20" s="34" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E20" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F20" s="34" t="inlineStr">
@@ -20427,11 +20431,11 @@
     </row>
     <row r="21">
       <c r="A21" s="34" t="n">
-        <v>2721</v>
+        <v>3038</v>
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C21" s="34" t="inlineStr">
@@ -20441,12 +20445,12 @@
       </c>
       <c r="D21" s="34" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E21" s="34" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F21" s="34" t="inlineStr">
@@ -20462,11 +20466,11 @@
     </row>
     <row r="22">
       <c r="A22" s="34" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B22" s="34" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C22" s="34" t="inlineStr">
@@ -20476,17 +20480,17 @@
       </c>
       <c r="D22" s="34" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E22" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F22" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G22" s="34" t="inlineStr">
@@ -20521,7 +20525,7 @@
       </c>
       <c r="F23" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G23" s="34" t="inlineStr">
@@ -20556,7 +20560,7 @@
       </c>
       <c r="F24" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G24" s="34" t="inlineStr">
@@ -20567,26 +20571,26 @@
     </row>
     <row r="25">
       <c r="A25" s="34" t="n">
-        <v>3038</v>
+        <v>157</v>
       </c>
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C25" s="34" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D25" s="34" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E25" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F25" s="34" t="inlineStr">
@@ -20602,31 +20606,31 @@
     </row>
     <row r="26">
       <c r="A26" s="34" t="n">
-        <v>113</v>
+        <v>1943</v>
       </c>
       <c r="B26" s="34" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C26" s="34" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D26" s="34" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E26" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F26" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G26" s="34" t="inlineStr">
@@ -20637,11 +20641,11 @@
     </row>
     <row r="27">
       <c r="A27" s="34" t="n">
-        <v>157</v>
+        <v>1943</v>
       </c>
       <c r="B27" s="34" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C27" s="34" t="inlineStr">
@@ -20651,17 +20655,17 @@
       </c>
       <c r="D27" s="34" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E27" s="34" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F27" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G27" s="34" t="inlineStr">
@@ -20672,11 +20676,11 @@
     </row>
     <row r="28">
       <c r="A28" s="34" t="n">
-        <v>1943</v>
+        <v>161</v>
       </c>
       <c r="B28" s="34" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C28" s="34" t="inlineStr">
@@ -20686,12 +20690,12 @@
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E28" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F28" s="34" t="inlineStr">
@@ -20731,7 +20735,7 @@
       </c>
       <c r="F29" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G29" s="34" t="inlineStr">
@@ -20766,7 +20770,7 @@
       </c>
       <c r="F30" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G30" s="34" t="inlineStr">
@@ -20777,11 +20781,11 @@
     </row>
     <row r="31">
       <c r="A31" s="34" t="n">
-        <v>1943</v>
+        <v>1996</v>
       </c>
       <c r="B31" s="34" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C31" s="34" t="inlineStr">
@@ -20812,11 +20816,11 @@
     </row>
     <row r="32">
       <c r="A32" s="34" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B32" s="34" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C32" s="34" t="inlineStr">
@@ -20845,78 +20849,8 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="34" t="n">
-        <v>1996</v>
-      </c>
-      <c r="B33" s="34" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="C33" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D33" s="34" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="E33" s="34" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F33" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G33" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="34" t="n">
-        <v>157</v>
-      </c>
-      <c r="B34" s="34" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="C34" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D34" s="34" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="E34" s="34" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F34" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G34" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G34"/>
+  <autoFilter ref="A2:G32"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/data/historico/semana_319.xlsx
+++ b/data/historico/semana_319.xlsx
@@ -18608,47 +18608,47 @@
     <row r="11">
       <c r="A11" s="27" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>16935897</t>
+          <t>16910075</t>
         </is>
       </c>
       <c r="D11" s="27" t="inlineStr">
         <is>
-          <t>417 - CENTRO 3</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E11" s="27" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="F11" s="27" t="inlineStr">
         <is>
-          <t>Avenida PRESIDENTE VARGAS</t>
+          <t>Rua CATANDUVA</t>
         </is>
       </c>
       <c r="G11" s="27" t="inlineStr">
         <is>
-          <t>725 - OU</t>
+          <t>490 - R</t>
         </is>
       </c>
       <c r="H11" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 09:40</t>
+          <t>13/08/2026 15:31</t>
         </is>
       </c>
       <c r="I11" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 09:58</t>
+          <t>13/08/2026 15:49</t>
         </is>
       </c>
       <c r="J11" s="27" t="n">
@@ -18658,47 +18658,47 @@
     <row r="12">
       <c r="A12" s="27" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>16910075</t>
+          <t>16935897</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>417 - CENTRO 3</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F12" s="27" t="inlineStr">
         <is>
-          <t>Rua CATANDUVA</t>
+          <t>Avenida PRESIDENTE VARGAS</t>
         </is>
       </c>
       <c r="G12" s="27" t="inlineStr">
         <is>
-          <t>490 - R</t>
+          <t>725 - OU</t>
         </is>
       </c>
       <c r="H12" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:31</t>
+          <t>14/08/2026 09:40</t>
         </is>
       </c>
       <c r="I12" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:49</t>
+          <t>14/08/2026 09:58</t>
         </is>
       </c>
       <c r="J12" s="27" t="n">
@@ -18708,47 +18708,47 @@
     <row r="13">
       <c r="A13" s="27" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="B13" s="27" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>16932380</t>
+          <t>16881755</t>
         </is>
       </c>
       <c r="D13" s="27" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>406 - JARDIM PRIMAVERA</t>
         </is>
       </c>
       <c r="E13" s="27" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="F13" s="27" t="inlineStr">
         <is>
-          <t>Rua CURITIBA</t>
+          <t>Rua ELOAH VIEIRA DA SILVA</t>
         </is>
       </c>
       <c r="G13" s="27" t="inlineStr">
         <is>
-          <t>01 - TB</t>
+          <t>26 - 2 - TB</t>
         </is>
       </c>
       <c r="H13" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 15:51</t>
+          <t>12/08/2026 16:12</t>
         </is>
       </c>
       <c r="I13" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 16:08</t>
+          <t>12/08/2026 16:29</t>
         </is>
       </c>
       <c r="J13" s="27" t="n">
@@ -18758,47 +18758,47 @@
     <row r="14">
       <c r="A14" s="27" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B14" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t>16910076</t>
+          <t>16932380</t>
         </is>
       </c>
       <c r="D14" s="27" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E14" s="27" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="F14" s="27" t="inlineStr">
         <is>
-          <t>Rua CATANDUVA</t>
+          <t>Rua CURITIBA</t>
         </is>
       </c>
       <c r="G14" s="27" t="inlineStr">
         <is>
-          <t>166 - R</t>
+          <t>01 - TB</t>
         </is>
       </c>
       <c r="H14" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:49</t>
+          <t>14/08/2026 15:51</t>
         </is>
       </c>
       <c r="I14" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 16:06</t>
+          <t>14/08/2026 16:08</t>
         </is>
       </c>
       <c r="J14" s="27" t="n">
@@ -18808,47 +18808,47 @@
     <row r="15">
       <c r="A15" s="27" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>16904092</t>
+          <t>16910076</t>
         </is>
       </c>
       <c r="D15" s="27" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E15" s="27" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="F15" s="27" t="inlineStr">
         <is>
-          <t>Rua SÃO JOÃO DEL REI</t>
+          <t>Rua CATANDUVA</t>
         </is>
       </c>
       <c r="G15" s="27" t="inlineStr">
         <is>
-          <t>300 - R</t>
+          <t>166 - R</t>
         </is>
       </c>
       <c r="H15" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:14</t>
+          <t>13/08/2026 15:49</t>
         </is>
       </c>
       <c r="I15" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:31</t>
+          <t>13/08/2026 16:06</t>
         </is>
       </c>
       <c r="J15" s="27" t="n">
@@ -18858,47 +18858,47 @@
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>Raquel Ortiz dos Santos</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C16" s="28" t="inlineStr">
         <is>
-          <t>16881755</t>
+          <t>16904092</t>
         </is>
       </c>
       <c r="D16" s="27" t="inlineStr">
         <is>
-          <t>406 - JARDIM PRIMAVERA</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E16" s="27" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="F16" s="27" t="inlineStr">
         <is>
-          <t>Rua ELOAH VIEIRA DA SILVA</t>
+          <t>Rua SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="G16" s="27" t="inlineStr">
         <is>
-          <t>26 - 2 - TB</t>
+          <t>300 - R</t>
         </is>
       </c>
       <c r="H16" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 16:12</t>
+          <t>13/08/2026 15:14</t>
         </is>
       </c>
       <c r="I16" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 16:29</t>
+          <t>13/08/2026 15:31</t>
         </is>
       </c>
       <c r="J16" s="27" t="n">
@@ -18958,7 +18958,7 @@
     <row r="18">
       <c r="A18" s="27" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B18" s="27" t="inlineStr">
@@ -18968,37 +18968,37 @@
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>16929550</t>
+          <t>16932420</t>
         </is>
       </c>
       <c r="D18" s="27" t="inlineStr">
         <is>
-          <t>420 - FERROVIARIA</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E18" s="27" t="inlineStr">
         <is>
-          <t>Q003</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F18" s="27" t="inlineStr">
         <is>
-          <t>Rua ALAMEDA DOS TROLLES</t>
+          <t>Rua 18 DE JULHO</t>
         </is>
       </c>
       <c r="G18" s="27" t="inlineStr">
         <is>
-          <t>190 - R</t>
+          <t>187 - R</t>
         </is>
       </c>
       <c r="H18" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:31</t>
+          <t>14/08/2026 14:52</t>
         </is>
       </c>
       <c r="I18" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:47</t>
+          <t>14/08/2026 15:08</t>
         </is>
       </c>
       <c r="J18" s="27" t="n">
@@ -19008,7 +19008,7 @@
     <row r="19">
       <c r="A19" s="27" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B19" s="27" t="inlineStr">
@@ -19018,37 +19018,37 @@
       </c>
       <c r="C19" s="28" t="inlineStr">
         <is>
-          <t>16928880</t>
+          <t>16932419</t>
         </is>
       </c>
       <c r="D19" s="27" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E19" s="27" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F19" s="27" t="inlineStr">
         <is>
-          <t>Rua CALOGERAS</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="G19" s="27" t="inlineStr">
         <is>
-          <t>1325 - C</t>
+          <t>451 - R</t>
         </is>
       </c>
       <c r="H19" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 13:48</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="I19" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 14:04</t>
+          <t>14/08/2026 14:49</t>
         </is>
       </c>
       <c r="J19" s="27" t="n">
@@ -19058,7 +19058,7 @@
     <row r="20">
       <c r="A20" s="27" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="B20" s="27" t="inlineStr">
@@ -19068,37 +19068,37 @@
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>16932419</t>
+          <t>16929550</t>
         </is>
       </c>
       <c r="D20" s="27" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>420 - FERROVIARIA</t>
         </is>
       </c>
       <c r="E20" s="27" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="F20" s="27" t="inlineStr">
         <is>
-          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
+          <t>Rua ALAMEDA DOS TROLLES</t>
         </is>
       </c>
       <c r="G20" s="27" t="inlineStr">
         <is>
-          <t>451 - R</t>
+          <t>190 - R</t>
         </is>
       </c>
       <c r="H20" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>14/08/2026 14:31</t>
         </is>
       </c>
       <c r="I20" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:49</t>
+          <t>14/08/2026 14:47</t>
         </is>
       </c>
       <c r="J20" s="27" t="n">
@@ -19108,7 +19108,7 @@
     <row r="21">
       <c r="A21" s="27" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B21" s="27" t="inlineStr">
@@ -19118,37 +19118,37 @@
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>16932420</t>
+          <t>16928880</t>
         </is>
       </c>
       <c r="D21" s="27" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E21" s="27" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="F21" s="27" t="inlineStr">
         <is>
-          <t>Rua 18 DE JULHO</t>
+          <t>Rua CALOGERAS</t>
         </is>
       </c>
       <c r="G21" s="27" t="inlineStr">
         <is>
-          <t>187 - R</t>
+          <t>1325 - C</t>
         </is>
       </c>
       <c r="H21" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:52</t>
+          <t>12/08/2026 13:48</t>
         </is>
       </c>
       <c r="I21" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 15:08</t>
+          <t>12/08/2026 14:04</t>
         </is>
       </c>
       <c r="J21" s="27" t="n">

--- a/data/historico/semana_319.xlsx
+++ b/data/historico/semana_319.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$E$38</definedName>
   </definedNames>
@@ -4895,7 +4895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4907,7 +4907,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (10 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (8 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4939,7 +4939,7 @@
     <row r="3">
       <c r="A3" s="36" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="B3" s="36" t="inlineStr">
@@ -5025,53 +5025,53 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="C7" s="36" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D7" s="36" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
+      <c r="B7" s="37" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="37" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="36" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="36" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="C8" s="36" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D8" s="36" t="inlineStr">
-        <is>
-          <t>Ramona dos Santos Oliveira</t>
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C8" s="37" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="37" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="B9" s="37" t="inlineStr">
@@ -5086,78 +5086,34 @@
       </c>
       <c r="D9" s="37" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="37" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="37" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="C10" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D10" s="37" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="37" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="37" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="C11" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D11" s="37" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>13/08/2026</t>
         </is>
       </c>
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B10" s="38" t="inlineStr">
         <is>
           <t>13/08/2026</t>
         </is>
       </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="C10" s="38" t="inlineStr">
         <is>
           <t>Recolha de Ovitrampa</t>
         </is>
       </c>
-      <c r="D12" s="38" t="inlineStr">
+      <c r="D10" s="38" t="inlineStr">
         <is>
           <t>Todos os agentes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D12"/>
+  <autoFilter ref="A2:D10"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>

--- a/data/historico/semana_319.xlsx
+++ b/data/historico/semana_319.xlsx
@@ -18564,47 +18564,47 @@
     <row r="11">
       <c r="A11" s="27" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="B11" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>16910075</t>
+          <t>16935897</t>
         </is>
       </c>
       <c r="D11" s="27" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>417 - CENTRO 3</t>
         </is>
       </c>
       <c r="E11" s="27" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F11" s="27" t="inlineStr">
         <is>
-          <t>Rua CATANDUVA</t>
+          <t>Avenida PRESIDENTE VARGAS</t>
         </is>
       </c>
       <c r="G11" s="27" t="inlineStr">
         <is>
-          <t>490 - R</t>
+          <t>725 - OU</t>
         </is>
       </c>
       <c r="H11" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:31</t>
+          <t>14/08/2026 09:40</t>
         </is>
       </c>
       <c r="I11" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:49</t>
+          <t>14/08/2026 09:58</t>
         </is>
       </c>
       <c r="J11" s="27" t="n">
@@ -18614,47 +18614,47 @@
     <row r="12">
       <c r="A12" s="27" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>16935897</t>
+          <t>16910075</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>417 - CENTRO 3</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="F12" s="27" t="inlineStr">
         <is>
-          <t>Avenida PRESIDENTE VARGAS</t>
+          <t>Rua CATANDUVA</t>
         </is>
       </c>
       <c r="G12" s="27" t="inlineStr">
         <is>
-          <t>725 - OU</t>
+          <t>490 - R</t>
         </is>
       </c>
       <c r="H12" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 09:40</t>
+          <t>13/08/2026 15:31</t>
         </is>
       </c>
       <c r="I12" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 09:58</t>
+          <t>13/08/2026 15:49</t>
         </is>
       </c>
       <c r="J12" s="27" t="n">
@@ -18664,47 +18664,47 @@
     <row r="13">
       <c r="A13" s="27" t="inlineStr">
         <is>
-          <t>Raquel Ortiz dos Santos</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B13" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>16881755</t>
+          <t>16932380</t>
         </is>
       </c>
       <c r="D13" s="27" t="inlineStr">
         <is>
-          <t>406 - JARDIM PRIMAVERA</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E13" s="27" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="F13" s="27" t="inlineStr">
         <is>
-          <t>Rua ELOAH VIEIRA DA SILVA</t>
+          <t>Rua CURITIBA</t>
         </is>
       </c>
       <c r="G13" s="27" t="inlineStr">
         <is>
-          <t>26 - 2 - TB</t>
+          <t>01 - TB</t>
         </is>
       </c>
       <c r="H13" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 16:12</t>
+          <t>14/08/2026 15:51</t>
         </is>
       </c>
       <c r="I13" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 16:29</t>
+          <t>14/08/2026 16:08</t>
         </is>
       </c>
       <c r="J13" s="27" t="n">
@@ -18714,47 +18714,47 @@
     <row r="14">
       <c r="A14" s="27" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B14" s="27" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t>16932380</t>
+          <t>16910076</t>
         </is>
       </c>
       <c r="D14" s="27" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E14" s="27" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="F14" s="27" t="inlineStr">
         <is>
-          <t>Rua CURITIBA</t>
+          <t>Rua CATANDUVA</t>
         </is>
       </c>
       <c r="G14" s="27" t="inlineStr">
         <is>
-          <t>01 - TB</t>
+          <t>166 - R</t>
         </is>
       </c>
       <c r="H14" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 15:51</t>
+          <t>13/08/2026 15:49</t>
         </is>
       </c>
       <c r="I14" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 16:08</t>
+          <t>13/08/2026 16:06</t>
         </is>
       </c>
       <c r="J14" s="27" t="n">
@@ -18764,47 +18764,47 @@
     <row r="15">
       <c r="A15" s="27" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>16910076</t>
+          <t>16904092</t>
         </is>
       </c>
       <c r="D15" s="27" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E15" s="27" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="F15" s="27" t="inlineStr">
         <is>
-          <t>Rua CATANDUVA</t>
+          <t>Rua SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="G15" s="27" t="inlineStr">
         <is>
-          <t>166 - R</t>
+          <t>300 - R</t>
         </is>
       </c>
       <c r="H15" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:49</t>
+          <t>13/08/2026 15:14</t>
         </is>
       </c>
       <c r="I15" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 16:06</t>
+          <t>13/08/2026 15:31</t>
         </is>
       </c>
       <c r="J15" s="27" t="n">
@@ -18814,47 +18814,47 @@
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C16" s="28" t="inlineStr">
         <is>
-          <t>16904092</t>
+          <t>16881755</t>
         </is>
       </c>
       <c r="D16" s="27" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>406 - JARDIM PRIMAVERA</t>
         </is>
       </c>
       <c r="E16" s="27" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="F16" s="27" t="inlineStr">
         <is>
-          <t>Rua SÃO JOÃO DEL REI</t>
+          <t>Rua ELOAH VIEIRA DA SILVA</t>
         </is>
       </c>
       <c r="G16" s="27" t="inlineStr">
         <is>
-          <t>300 - R</t>
+          <t>26 - 2 - TB</t>
         </is>
       </c>
       <c r="H16" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:14</t>
+          <t>12/08/2026 16:12</t>
         </is>
       </c>
       <c r="I16" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:31</t>
+          <t>12/08/2026 16:29</t>
         </is>
       </c>
       <c r="J16" s="27" t="n">
@@ -18914,7 +18914,7 @@
     <row r="18">
       <c r="A18" s="27" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="B18" s="27" t="inlineStr">
@@ -18924,37 +18924,37 @@
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>16932420</t>
+          <t>16929550</t>
         </is>
       </c>
       <c r="D18" s="27" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>420 - FERROVIARIA</t>
         </is>
       </c>
       <c r="E18" s="27" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="F18" s="27" t="inlineStr">
         <is>
-          <t>Rua 18 DE JULHO</t>
+          <t>Rua ALAMEDA DOS TROLLES</t>
         </is>
       </c>
       <c r="G18" s="27" t="inlineStr">
         <is>
-          <t>187 - R</t>
+          <t>190 - R</t>
         </is>
       </c>
       <c r="H18" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:52</t>
+          <t>14/08/2026 14:31</t>
         </is>
       </c>
       <c r="I18" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 15:08</t>
+          <t>14/08/2026 14:47</t>
         </is>
       </c>
       <c r="J18" s="27" t="n">
@@ -18964,7 +18964,7 @@
     <row r="19">
       <c r="A19" s="27" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B19" s="27" t="inlineStr">
@@ -18974,37 +18974,37 @@
       </c>
       <c r="C19" s="28" t="inlineStr">
         <is>
-          <t>16932419</t>
+          <t>16928880</t>
         </is>
       </c>
       <c r="D19" s="27" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E19" s="27" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="F19" s="27" t="inlineStr">
         <is>
-          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
+          <t>Rua CALOGERAS</t>
         </is>
       </c>
       <c r="G19" s="27" t="inlineStr">
         <is>
-          <t>451 - R</t>
+          <t>1325 - C</t>
         </is>
       </c>
       <c r="H19" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>12/08/2026 13:48</t>
         </is>
       </c>
       <c r="I19" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:49</t>
+          <t>12/08/2026 14:04</t>
         </is>
       </c>
       <c r="J19" s="27" t="n">
@@ -19014,7 +19014,7 @@
     <row r="20">
       <c r="A20" s="27" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B20" s="27" t="inlineStr">
@@ -19024,37 +19024,37 @@
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>16929550</t>
+          <t>16932419</t>
         </is>
       </c>
       <c r="D20" s="27" t="inlineStr">
         <is>
-          <t>420 - FERROVIARIA</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E20" s="27" t="inlineStr">
         <is>
-          <t>Q003</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F20" s="27" t="inlineStr">
         <is>
-          <t>Rua ALAMEDA DOS TROLLES</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="G20" s="27" t="inlineStr">
         <is>
-          <t>190 - R</t>
+          <t>451 - R</t>
         </is>
       </c>
       <c r="H20" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:31</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="I20" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:47</t>
+          <t>14/08/2026 14:49</t>
         </is>
       </c>
       <c r="J20" s="27" t="n">
@@ -19064,7 +19064,7 @@
     <row r="21">
       <c r="A21" s="27" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B21" s="27" t="inlineStr">
@@ -19074,37 +19074,37 @@
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>16928880</t>
+          <t>16932420</t>
         </is>
       </c>
       <c r="D21" s="27" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E21" s="27" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F21" s="27" t="inlineStr">
         <is>
-          <t>Rua CALOGERAS</t>
+          <t>Rua 18 DE JULHO</t>
         </is>
       </c>
       <c r="G21" s="27" t="inlineStr">
         <is>
-          <t>1325 - C</t>
+          <t>187 - R</t>
         </is>
       </c>
       <c r="H21" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 13:48</t>
+          <t>14/08/2026 14:52</t>
         </is>
       </c>
       <c r="I21" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 14:04</t>
+          <t>14/08/2026 15:08</t>
         </is>
       </c>
       <c r="J21" s="27" t="n">

--- a/data/historico/semana_319.xlsx
+++ b/data/historico/semana_319.xlsx
@@ -23,15 +23,15 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo Geral'!$A$2:$AC$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por Área'!$A$2:$N$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por Área'!$A$2:$N$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Visitas Duplicadas'!$A$2:$J$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Visitas Suspeitas'!$A$2:$K$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Visitas Negativas'!$A$2:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 15min'!$A$2:$J$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 15min'!$A$2:$J$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$E$39</definedName>
   </definedNames>
@@ -3250,16 +3250,16 @@
         <v>0</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>41.54</v>
+        <v>40.62</v>
       </c>
       <c r="V24" s="4" t="n">
         <v>4.43</v>
@@ -3628,16 +3628,16 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>18</v>
+        <v>19.67</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>5.56</v>
+        <v>5.64</v>
       </c>
       <c r="H28" s="4" t="n">
         <v>5</v>
@@ -3655,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0</v>
@@ -3670,49 +3670,49 @@
         <v>0</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="S28" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>49.3</v>
+        <v>42.72</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>5.94</v>
+        <v>5.63</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>11.88</v>
+        <v>16.88</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="Y28" s="4" t="inlineStr">
         <is>
-          <t>R$ 132,63</t>
+          <t>R$ 119,48</t>
         </is>
       </c>
       <c r="Z28" s="4" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA28" s="4" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AB28" s="4" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC28" s="4" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:57</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5012,7 +5012,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (8 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (9 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="B3" s="36" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="C3" s="36" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="B4" s="36" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="C4" s="36" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="B6" s="36" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="C6" s="36" t="inlineStr">
@@ -5130,38 +5130,38 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="B7" s="37" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="C7" s="37" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D7" s="37" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>17/08/2026</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D7" s="36" t="inlineStr">
+        <is>
+          <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="37" t="inlineStr">
         <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="B8" s="37" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
       <c r="C8" s="37" t="inlineStr">
         <is>
           <t>Chuva (confirmada)</t>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="D8" s="37" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
     </row>
@@ -5191,34 +5191,56 @@
       </c>
       <c r="D9" s="37" t="inlineStr">
         <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="37" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="inlineStr">
+        <is>
           <t>Equipe 4</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="38" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>13/08/2026</t>
         </is>
       </c>
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
         <is>
           <t>13/08/2026</t>
         </is>
       </c>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="C11" s="38" t="inlineStr">
         <is>
           <t>Recolha de Ovitrampa</t>
         </is>
       </c>
-      <c r="D10" s="38" t="inlineStr">
+      <c r="D11" s="38" t="inlineStr">
         <is>
           <t>Todos os agentes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D10"/>
+  <autoFilter ref="A2:D11"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -5924,16 +5946,16 @@
         <v>38</v>
       </c>
       <c r="D24" s="27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E24" s="27" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G24" s="27" t="n">
-        <v>41.54</v>
+        <v>40.62</v>
       </c>
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="n"/>
@@ -6037,19 +6059,19 @@
         </is>
       </c>
       <c r="C28" s="27" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="D28" s="27" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E28" s="27" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>71</v>
+        <v>103</v>
       </c>
       <c r="G28" s="27" t="n">
-        <v>49.3</v>
+        <v>42.72</v>
       </c>
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="n"/>
@@ -6385,19 +6407,19 @@
         </is>
       </c>
       <c r="C40" s="24" t="n">
-        <v>2878</v>
+        <v>2901</v>
       </c>
       <c r="D40" s="24" t="n">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="E40" s="24" t="n">
         <v>4</v>
       </c>
       <c r="F40" s="24" t="n">
-        <v>4115</v>
+        <v>4146</v>
       </c>
       <c r="G40" s="24" t="n">
-        <v>30.06</v>
+        <v>30.03</v>
       </c>
       <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="n"/>
@@ -7159,7 +7181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F269"/>
+  <dimension ref="A1:F271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7528,7 +7550,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -7552,12 +7574,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
@@ -7576,16 +7598,16 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
@@ -7600,7 +7622,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -7609,7 +7631,7 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>99.59999999999999</v>
+        <v>99.8</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
@@ -7624,16 +7646,16 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>99.40000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
@@ -7648,16 +7670,16 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>99</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -7672,7 +7694,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -7681,7 +7703,7 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>98.3</v>
+        <v>99</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -7696,16 +7718,16 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>97.8</v>
+        <v>98.3</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
@@ -7720,16 +7742,16 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -11733,7 +11755,7 @@
       </c>
       <c r="C181" s="46" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D181" s="46" t="n">
@@ -11747,55 +11769,55 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="47" t="inlineStr">
+      <c r="A182" s="46" t="inlineStr">
         <is>
           <t>Naime Cristina Freitas</t>
         </is>
       </c>
-      <c r="B182" s="47" t="inlineStr">
+      <c r="B182" s="46" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C182" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D182" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E182" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F182" s="47" t="n">
-        <v>-1</v>
+      <c r="C182" s="46" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D182" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E182" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F182" s="46" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="47" t="inlineStr">
+      <c r="A183" s="46" t="inlineStr">
         <is>
           <t>Naime Cristina Freitas</t>
         </is>
       </c>
-      <c r="B183" s="47" t="inlineStr">
+      <c r="B183" s="46" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C183" s="47" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D183" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E183" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F183" s="47" t="n">
-        <v>-0.6</v>
+      <c r="C183" s="46" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D183" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" s="46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -11811,17 +11833,17 @@
       </c>
       <c r="C184" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D184" s="47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E184" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F184" s="47" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="185">
@@ -11837,121 +11859,121 @@
       </c>
       <c r="C185" s="47" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D185" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E185" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F185" s="47" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="47" t="inlineStr">
+        <is>
+          <t>Naime Cristina Freitas</t>
+        </is>
+      </c>
+      <c r="B186" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C186" s="47" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D186" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="E185" s="47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F185" s="47" t="n">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="46" t="inlineStr">
+      <c r="E186" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F186" s="47" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="47" t="inlineStr">
+        <is>
+          <t>Naime Cristina Freitas</t>
+        </is>
+      </c>
+      <c r="B187" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C187" s="47" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D187" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E187" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F187" s="47" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="46" t="inlineStr">
         <is>
           <t>Rafael Ramos Recalde</t>
         </is>
       </c>
-      <c r="B186" s="46" t="inlineStr">
+      <c r="B188" s="46" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C186" s="46" t="inlineStr">
+      <c r="C188" s="46" t="inlineStr">
         <is>
           <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
-      <c r="D186" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E186" s="46" t="n">
+      <c r="D188" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E188" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="F186" s="46" t="n">
+      <c r="F188" s="46" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="46" t="inlineStr">
+    <row r="189">
+      <c r="A189" s="46" t="inlineStr">
         <is>
           <t>Rafael Ramos Recalde</t>
         </is>
       </c>
-      <c r="B187" s="46" t="inlineStr">
+      <c r="B189" s="46" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C187" s="46" t="inlineStr">
+      <c r="C189" s="46" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D187" s="46" t="n">
+      <c r="D189" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E187" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F187" s="46" t="n">
+      <c r="E189" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F189" s="46" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="47" t="inlineStr">
-        <is>
-          <t>Rafael Ramos Recalde</t>
-        </is>
-      </c>
-      <c r="B188" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C188" s="47" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D188" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E188" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F188" s="47" t="n">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="47" t="inlineStr">
-        <is>
-          <t>Rafael Ramos Recalde</t>
-        </is>
-      </c>
-      <c r="B189" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C189" s="47" t="inlineStr">
-        <is>
-          <t>Início tarde após 14h30</t>
-        </is>
-      </c>
-      <c r="D189" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E189" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F189" s="47" t="n">
-        <v>-1.2</v>
       </c>
     </row>
     <row r="190">
@@ -11967,121 +11989,121 @@
       </c>
       <c r="C190" s="47" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D190" s="47" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E190" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F190" s="47" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="47" t="inlineStr">
+        <is>
+          <t>Rafael Ramos Recalde</t>
+        </is>
+      </c>
+      <c r="B191" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C191" s="47" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D191" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E191" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F191" s="47" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="47" t="inlineStr">
+        <is>
+          <t>Rafael Ramos Recalde</t>
+        </is>
+      </c>
+      <c r="B192" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C192" s="47" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D192" s="47" t="n">
+        <v>50</v>
+      </c>
+      <c r="E192" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F192" s="47" t="n">
         <v>-30</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="46" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="46" t="inlineStr">
         <is>
           <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
-      <c r="B191" s="46" t="inlineStr">
+      <c r="B193" s="46" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C191" s="46" t="inlineStr">
+      <c r="C193" s="46" t="inlineStr">
         <is>
           <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
-      <c r="D191" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E191" s="46" t="n">
+      <c r="D193" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E193" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="F191" s="46" t="n">
+      <c r="F193" s="46" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="46" t="inlineStr">
+    <row r="194">
+      <c r="A194" s="46" t="inlineStr">
         <is>
           <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
-      <c r="B192" s="46" t="inlineStr">
+      <c r="B194" s="46" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C192" s="46" t="inlineStr">
+      <c r="C194" s="46" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D192" s="46" t="n">
+      <c r="D194" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="E192" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F192" s="46" t="n">
+      <c r="E194" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" s="46" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="47" t="inlineStr">
-        <is>
-          <t>Raquel Ortiz dos Santos</t>
-        </is>
-      </c>
-      <c r="B193" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C193" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D193" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E193" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F193" s="47" t="n">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="47" t="inlineStr">
-        <is>
-          <t>Raquel Ortiz dos Santos</t>
-        </is>
-      </c>
-      <c r="B194" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C194" s="47" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D194" s="47" t="n">
-        <v>3</v>
-      </c>
-      <c r="E194" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F194" s="47" t="n">
-        <v>-1.8</v>
       </c>
     </row>
     <row r="195">
@@ -12097,17 +12119,17 @@
       </c>
       <c r="C195" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D195" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E195" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F195" s="47" t="n">
-        <v>-1.2</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="196">
@@ -12123,17 +12145,17 @@
       </c>
       <c r="C196" s="47" t="inlineStr">
         <is>
-          <t>Visita fora do expediente/fim de semana</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D196" s="47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E196" s="47" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F196" s="47" t="n">
-        <v>-2</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="197">
@@ -12149,69 +12171,69 @@
       </c>
       <c r="C197" s="47" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D197" s="47" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E197" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F197" s="47" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="47" t="inlineStr">
+        <is>
+          <t>Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B198" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C198" s="47" t="inlineStr">
+        <is>
+          <t>Visita fora do expediente/fim de semana</t>
+        </is>
+      </c>
+      <c r="D198" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E198" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F198" s="47" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="47" t="inlineStr">
+        <is>
+          <t>Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B199" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C199" s="47" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D199" s="47" t="n">
+        <v>32</v>
+      </c>
+      <c r="E199" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F199" s="47" t="n">
         <v>-19.2</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="46" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-      <c r="B198" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C198" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D198" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E198" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F198" s="46" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="46" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-      <c r="B199" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C199" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D199" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E199" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F199" s="46" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="200">
@@ -12227,69 +12249,69 @@
       </c>
       <c r="C200" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D200" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F200" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="46" t="inlineStr">
+        <is>
+          <t>Rosalina Beniel Vargas</t>
+        </is>
+      </c>
+      <c r="B201" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C201" s="46" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D201" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F201" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="46" t="inlineStr">
+        <is>
+          <t>Rosalina Beniel Vargas</t>
+        </is>
+      </c>
+      <c r="B202" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C202" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D200" s="46" t="n">
+      <c r="D202" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="E200" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F200" s="46" t="n">
+      <c r="E202" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F202" s="46" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="47" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-      <c r="B201" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C201" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D201" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E201" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F201" s="47" t="n">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="47" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-      <c r="B202" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C202" s="47" t="inlineStr">
-        <is>
-          <t>Fim manhã antes de 10h00</t>
-        </is>
-      </c>
-      <c r="D202" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E202" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F202" s="47" t="n">
-        <v>-0.6</v>
       </c>
     </row>
     <row r="203">
@@ -12305,17 +12327,17 @@
       </c>
       <c r="C203" s="47" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D203" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E203" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F203" s="47" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="204">
@@ -12331,7 +12353,7 @@
       </c>
       <c r="C204" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D204" s="47" t="n">
@@ -12357,7 +12379,7 @@
       </c>
       <c r="C205" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D205" s="47" t="n">
@@ -12371,45 +12393,45 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="46" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="B206" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C206" s="46" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D206" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E206" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F206" s="46" t="n">
-        <v>1</v>
+      <c r="A206" s="47" t="inlineStr">
+        <is>
+          <t>Rosalina Beniel Vargas</t>
+        </is>
+      </c>
+      <c r="B206" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C206" s="47" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D206" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F206" s="47" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="47" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="B207" s="47" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C207" s="47" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D207" s="47" t="n">
@@ -12423,29 +12445,29 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="47" t="inlineStr">
+      <c r="A208" s="46" t="inlineStr">
         <is>
           <t>Rozana Reis da Silva</t>
         </is>
       </c>
-      <c r="B208" s="47" t="inlineStr">
+      <c r="B208" s="46" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C208" s="47" t="inlineStr">
-        <is>
-          <t>Início tarde após 14h30</t>
-        </is>
-      </c>
-      <c r="D208" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E208" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F208" s="47" t="n">
-        <v>-0.6</v>
+      <c r="C208" s="46" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D208" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E208" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F208" s="46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -12461,17 +12483,17 @@
       </c>
       <c r="C209" s="47" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D209" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E209" s="47" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F209" s="47" t="n">
-        <v>-6</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="210">
@@ -12487,69 +12509,69 @@
       </c>
       <c r="C210" s="47" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D210" s="47" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E210" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F210" s="47" t="n">
-        <v>-9</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="47" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="B211" s="47" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C211" s="47" t="inlineStr">
         <is>
-          <t>Dia sem bater a meta diária</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D211" s="47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E211" s="47" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F211" s="47" t="n">
-        <v>-0.5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="47" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="B212" s="47" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C212" s="47" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Visita rápida</t>
         </is>
       </c>
       <c r="D212" s="47" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E212" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F212" s="47" t="n">
-        <v>-0.6</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="213">
@@ -12565,17 +12587,17 @@
       </c>
       <c r="C213" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D213" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E213" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F213" s="47" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="214">
@@ -12591,17 +12613,17 @@
       </c>
       <c r="C214" s="47" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D214" s="47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E214" s="47" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F214" s="47" t="n">
-        <v>-12</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="215">
@@ -12617,17 +12639,17 @@
       </c>
       <c r="C215" s="47" t="inlineStr">
         <is>
-          <t>Visita fora do expediente/fim de semana</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D215" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E215" s="47" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F215" s="47" t="n">
-        <v>-1</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="216">
@@ -12643,121 +12665,121 @@
       </c>
       <c r="C216" s="47" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D216" s="47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E216" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F216" s="47" t="n">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="47" t="inlineStr">
+        <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B217" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C217" s="47" t="inlineStr">
+        <is>
+          <t>Visita fora do expediente/fim de semana</t>
+        </is>
+      </c>
+      <c r="D217" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E217" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F217" s="47" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="47" t="inlineStr">
+        <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B218" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C218" s="47" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D216" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E216" s="47" t="n">
+      <c r="D218" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E218" s="47" t="n">
         <v>0.3</v>
       </c>
-      <c r="F216" s="47" t="n">
+      <c r="F218" s="47" t="n">
         <v>-0.6</v>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="46" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="46" t="inlineStr">
         <is>
           <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
-      <c r="B217" s="46" t="inlineStr">
+      <c r="B219" s="46" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C217" s="46" t="inlineStr">
+      <c r="C219" s="46" t="inlineStr">
         <is>
           <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
-      <c r="D217" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E217" s="46" t="n">
+      <c r="D219" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E219" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="F217" s="46" t="n">
+      <c r="F219" s="46" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="46" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="46" t="inlineStr">
         <is>
           <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
-      <c r="B218" s="46" t="inlineStr">
+      <c r="B220" s="46" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C218" s="46" t="inlineStr">
+      <c r="C220" s="46" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D218" s="46" t="n">
+      <c r="D220" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E218" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F218" s="46" t="n">
+      <c r="E220" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F220" s="46" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="47" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="B219" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C219" s="47" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D219" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E219" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F219" s="47" t="n">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="47" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="B220" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C220" s="47" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D220" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E220" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F220" s="47" t="n">
-        <v>-0.6</v>
       </c>
     </row>
     <row r="221">
@@ -12773,17 +12795,17 @@
       </c>
       <c r="C221" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D221" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E221" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F221" s="47" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="222">
@@ -12799,225 +12821,225 @@
       </c>
       <c r="C222" s="47" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D222" s="47" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E222" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F222" s="47" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="47" t="inlineStr">
+        <is>
+          <t>Sara Eliane Talaveira de Oliveira</t>
+        </is>
+      </c>
+      <c r="B223" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C223" s="47" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D223" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E223" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F223" s="47" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="47" t="inlineStr">
+        <is>
+          <t>Sara Eliane Talaveira de Oliveira</t>
+        </is>
+      </c>
+      <c r="B224" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C224" s="47" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D224" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="E224" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F224" s="47" t="n">
         <v>-6.6</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="46" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="46" t="inlineStr">
         <is>
           <t>Selba Ramona Afonso</t>
         </is>
       </c>
-      <c r="B223" s="46" t="inlineStr">
+      <c r="B225" s="46" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C223" s="46" t="inlineStr">
+      <c r="C225" s="46" t="inlineStr">
         <is>
           <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
-      <c r="D223" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E223" s="46" t="n">
+      <c r="D225" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="F223" s="46" t="n">
+      <c r="F225" s="46" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="46" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="46" t="inlineStr">
         <is>
           <t>Selba Ramona Afonso</t>
         </is>
       </c>
-      <c r="B224" s="46" t="inlineStr">
+      <c r="B226" s="46" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C224" s="46" t="inlineStr">
+      <c r="C226" s="46" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D224" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E224" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F224" s="46" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="47" t="inlineStr">
+      <c r="D226" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E226" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F226" s="46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="47" t="inlineStr">
         <is>
           <t>Selba Ramona Afonso</t>
         </is>
       </c>
-      <c r="B225" s="47" t="inlineStr">
+      <c r="B227" s="47" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C225" s="47" t="inlineStr">
+      <c r="C227" s="47" t="inlineStr">
         <is>
           <t>Início tarde após 14h30</t>
         </is>
       </c>
-      <c r="D225" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E225" s="47" t="n">
+      <c r="D227" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E227" s="47" t="n">
         <v>0.3</v>
       </c>
-      <c r="F225" s="47" t="n">
+      <c r="F227" s="47" t="n">
         <v>-0.6</v>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="47" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="47" t="inlineStr">
         <is>
           <t>Selba Ramona Afonso</t>
         </is>
       </c>
-      <c r="B226" s="47" t="inlineStr">
+      <c r="B228" s="47" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C226" s="47" t="inlineStr">
+      <c r="C228" s="47" t="inlineStr">
         <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D226" s="47" t="n">
+      <c r="D228" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="E226" s="47" t="n">
+      <c r="E228" s="47" t="n">
         <v>1.5</v>
       </c>
-      <c r="F226" s="47" t="n">
+      <c r="F228" s="47" t="n">
         <v>-6</v>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="46" t="inlineStr">
+    <row r="229">
+      <c r="A229" s="46" t="inlineStr">
         <is>
           <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
-      <c r="B227" s="46" t="inlineStr">
+      <c r="B229" s="46" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C227" s="46" t="inlineStr">
+      <c r="C229" s="46" t="inlineStr">
         <is>
           <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
-      <c r="D227" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E227" s="46" t="n">
+      <c r="D229" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E229" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="F227" s="46" t="n">
+      <c r="F229" s="46" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="46" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="46" t="inlineStr">
         <is>
           <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
-      <c r="B228" s="46" t="inlineStr">
+      <c r="B230" s="46" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C228" s="46" t="inlineStr">
+      <c r="C230" s="46" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D228" s="46" t="n">
+      <c r="D230" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E228" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F228" s="46" t="n">
+      <c r="E230" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F230" s="46" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="47" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="B229" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C229" s="47" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D229" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E229" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F229" s="47" t="n">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="47" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="B230" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C230" s="47" t="inlineStr">
-        <is>
-          <t>Início tarde após 14h30</t>
-        </is>
-      </c>
-      <c r="D230" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E230" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F230" s="47" t="n">
-        <v>-1.2</v>
       </c>
     </row>
     <row r="231">
@@ -13033,69 +13055,69 @@
       </c>
       <c r="C231" s="47" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D231" s="47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E231" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F231" s="47" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="47" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B232" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C232" s="47" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D232" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E232" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F232" s="47" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="47" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B233" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C233" s="47" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D233" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="E233" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F233" s="47" t="n">
         <v>-3</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="46" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B232" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C232" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D232" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E232" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F232" s="46" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="46" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B233" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C233" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D233" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E233" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F233" s="46" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="234">
@@ -13111,69 +13133,69 @@
       </c>
       <c r="C234" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D234" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E234" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F234" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="46" t="inlineStr">
+        <is>
+          <t>Suely Aguiar Alves Luiz</t>
+        </is>
+      </c>
+      <c r="B235" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C235" s="46" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D235" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E235" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F235" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="46" t="inlineStr">
+        <is>
+          <t>Suely Aguiar Alves Luiz</t>
+        </is>
+      </c>
+      <c r="B236" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C236" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D234" s="46" t="n">
+      <c r="D236" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E234" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F234" s="46" t="n">
+      <c r="E236" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F236" s="46" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="47" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B235" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C235" s="47" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D235" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E235" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F235" s="47" t="n">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="47" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B236" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C236" s="47" t="inlineStr">
-        <is>
-          <t>Início tarde após 14h30</t>
-        </is>
-      </c>
-      <c r="D236" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E236" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F236" s="47" t="n">
-        <v>-0.6</v>
       </c>
     </row>
     <row r="237">
@@ -13189,121 +13211,121 @@
       </c>
       <c r="C237" s="47" t="inlineStr">
         <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D237" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E237" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F237" s="47" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="47" t="inlineStr">
+        <is>
+          <t>Suely Aguiar Alves Luiz</t>
+        </is>
+      </c>
+      <c r="B238" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C238" s="47" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D238" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E238" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F238" s="47" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="47" t="inlineStr">
+        <is>
+          <t>Suely Aguiar Alves Luiz</t>
+        </is>
+      </c>
+      <c r="B239" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C239" s="47" t="inlineStr">
+        <is>
           <t>Visita em sequência suspeita</t>
         </is>
       </c>
-      <c r="D237" s="47" t="n">
+      <c r="D239" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="E237" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="F237" s="47" t="n">
+      <c r="E239" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F239" s="47" t="n">
         <v>-4</v>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="46" t="inlineStr">
+    <row r="240">
+      <c r="A240" s="46" t="inlineStr">
         <is>
           <t>Tania Maria Montania</t>
         </is>
       </c>
-      <c r="B238" s="46" t="inlineStr">
+      <c r="B240" s="46" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C238" s="46" t="inlineStr">
+      <c r="C240" s="46" t="inlineStr">
         <is>
           <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
-      <c r="D238" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E238" s="46" t="n">
+      <c r="D240" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E240" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="F238" s="46" t="n">
+      <c r="F240" s="46" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="46" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="46" t="inlineStr">
         <is>
           <t>Tania Maria Montania</t>
         </is>
       </c>
-      <c r="B239" s="46" t="inlineStr">
+      <c r="B241" s="46" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C239" s="46" t="inlineStr">
+      <c r="C241" s="46" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D239" s="46" t="n">
+      <c r="D241" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E239" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F239" s="46" t="n">
+      <c r="E241" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F241" s="46" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="47" t="inlineStr">
-        <is>
-          <t>Tania Maria Montania</t>
-        </is>
-      </c>
-      <c r="B240" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C240" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D240" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E240" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F240" s="47" t="n">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="47" t="inlineStr">
-        <is>
-          <t>Tania Maria Montania</t>
-        </is>
-      </c>
-      <c r="B241" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C241" s="47" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D241" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E241" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F241" s="47" t="n">
-        <v>-0.6</v>
       </c>
     </row>
     <row r="242">
@@ -13319,17 +13341,17 @@
       </c>
       <c r="C242" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D242" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E242" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F242" s="47" t="n">
-        <v>-1.2</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="243">
@@ -13345,7 +13367,7 @@
       </c>
       <c r="C243" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D243" s="47" t="n">
@@ -13371,95 +13393,95 @@
       </c>
       <c r="C244" s="47" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D244" s="47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E244" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F244" s="47" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="47" t="inlineStr">
+        <is>
+          <t>Tania Maria Montania</t>
+        </is>
+      </c>
+      <c r="B245" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C245" s="47" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D245" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E245" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F245" s="47" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="46" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
-        </is>
-      </c>
-      <c r="B245" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C245" s="46" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D245" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E245" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F245" s="46" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="47" t="inlineStr">
         <is>
+          <t>Tania Maria Montania</t>
+        </is>
+      </c>
+      <c r="B246" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C246" s="47" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D246" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E246" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F246" s="47" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="46" t="inlineStr">
+        <is>
           <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
-      <c r="B246" s="47" t="inlineStr">
+      <c r="B247" s="46" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C246" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D246" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E246" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F246" s="47" t="n">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="47" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
-        </is>
-      </c>
-      <c r="B247" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C247" s="47" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D247" s="47" t="n">
+      <c r="C247" s="46" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D247" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="E247" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F247" s="47" t="n">
-        <v>-1.2</v>
+      <c r="E247" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F247" s="46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="248">
@@ -13475,17 +13497,17 @@
       </c>
       <c r="C248" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D248" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E248" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F248" s="47" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="249">
@@ -13501,17 +13523,17 @@
       </c>
       <c r="C249" s="47" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D249" s="47" t="n">
         <v>2</v>
       </c>
       <c r="E249" s="47" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F249" s="47" t="n">
-        <v>-6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="250">
@@ -13527,17 +13549,17 @@
       </c>
       <c r="C250" s="47" t="inlineStr">
         <is>
-          <t>Visita fora do expediente/fim de semana</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D250" s="47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E250" s="47" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F250" s="47" t="n">
-        <v>-4</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="251">
@@ -13553,95 +13575,95 @@
       </c>
       <c r="C251" s="47" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D251" s="47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E251" s="47" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="F251" s="47" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="46" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="B252" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C252" s="46" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D252" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="E252" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F252" s="46" t="n">
-        <v>3</v>
+      <c r="A252" s="47" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="B252" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C252" s="47" t="inlineStr">
+        <is>
+          <t>Visita fora do expediente/fim de semana</t>
+        </is>
+      </c>
+      <c r="D252" s="47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E252" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F252" s="47" t="n">
+        <v>-4</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="47" t="inlineStr">
         <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="B253" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C253" s="47" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D253" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="E253" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F253" s="47" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="46" t="inlineStr">
+        <is>
           <t>Walquiria Araujo Flores</t>
         </is>
       </c>
-      <c r="B253" s="47" t="inlineStr">
+      <c r="B254" s="46" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C253" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D253" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E253" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F253" s="47" t="n">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="47" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="B254" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C254" s="47" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D254" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E254" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F254" s="47" t="n">
-        <v>-0.6</v>
+      <c r="C254" s="46" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D254" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E254" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F254" s="46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="255">
@@ -13657,17 +13679,17 @@
       </c>
       <c r="C255" s="47" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D255" s="47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E255" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F255" s="47" t="n">
-        <v>-2.4</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="256">
@@ -13683,17 +13705,17 @@
       </c>
       <c r="C256" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D256" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E256" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F256" s="47" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="257">
@@ -13709,17 +13731,17 @@
       </c>
       <c r="C257" s="47" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D257" s="47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E257" s="47" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F257" s="47" t="n">
-        <v>-3</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="258">
@@ -13735,121 +13757,121 @@
       </c>
       <c r="C258" s="47" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D258" s="47" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E258" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F258" s="47" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="47" t="inlineStr">
+        <is>
+          <t>Walquiria Araujo Flores</t>
+        </is>
+      </c>
+      <c r="B259" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C259" s="47" t="inlineStr">
+        <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D259" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E259" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F259" s="47" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="47" t="inlineStr">
+        <is>
+          <t>Walquiria Araujo Flores</t>
+        </is>
+      </c>
+      <c r="B260" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C260" s="47" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D260" s="47" t="n">
+        <v>11</v>
+      </c>
+      <c r="E260" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F260" s="47" t="n">
         <v>-6.6</v>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="46" t="inlineStr">
+    <row r="261">
+      <c r="A261" s="46" t="inlineStr">
         <is>
           <t>Wesley de Souza Leal</t>
         </is>
       </c>
-      <c r="B259" s="46" t="inlineStr">
+      <c r="B261" s="46" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C259" s="46" t="inlineStr">
+      <c r="C261" s="46" t="inlineStr">
         <is>
           <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
-      <c r="D259" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E259" s="46" t="n">
+      <c r="D261" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E261" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="F259" s="46" t="n">
+      <c r="F261" s="46" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="46" t="inlineStr">
+    <row r="262">
+      <c r="A262" s="46" t="inlineStr">
         <is>
           <t>Wesley de Souza Leal</t>
         </is>
       </c>
-      <c r="B260" s="46" t="inlineStr">
+      <c r="B262" s="46" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C260" s="46" t="inlineStr">
+      <c r="C262" s="46" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D260" s="46" t="n">
+      <c r="D262" s="46" t="n">
         <v>2</v>
       </c>
-      <c r="E260" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F260" s="46" t="n">
+      <c r="E262" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F262" s="46" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="47" t="inlineStr">
-        <is>
-          <t>Wesley de Souza Leal</t>
-        </is>
-      </c>
-      <c r="B261" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C261" s="47" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D261" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E261" s="47" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F261" s="47" t="n">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="47" t="inlineStr">
-        <is>
-          <t>Wesley de Souza Leal</t>
-        </is>
-      </c>
-      <c r="B262" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C262" s="47" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D262" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E262" s="47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F262" s="47" t="n">
-        <v>-0.6</v>
       </c>
     </row>
     <row r="263">
@@ -13865,17 +13887,17 @@
       </c>
       <c r="C263" s="47" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D263" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E263" s="47" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F263" s="47" t="n">
-        <v>-1.2</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="264">
@@ -13891,69 +13913,69 @@
       </c>
       <c r="C264" s="47" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D264" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E264" s="47" t="n">
         <v>0.3</v>
       </c>
       <c r="F264" s="47" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="47" t="inlineStr">
+        <is>
+          <t>Wesley de Souza Leal</t>
+        </is>
+      </c>
+      <c r="B265" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C265" s="47" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D265" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E265" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F265" s="47" t="n">
         <v>-1.2</v>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" s="46" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B265" s="46" t="inlineStr">
+    <row r="266">
+      <c r="A266" s="47" t="inlineStr">
+        <is>
+          <t>Wesley de Souza Leal</t>
+        </is>
+      </c>
+      <c r="B266" s="47" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C265" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D265" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E265" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F265" s="46" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="46" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B266" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C266" s="46" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D266" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E266" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F266" s="46" t="n">
-        <v>5</v>
+      <c r="C266" s="47" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D266" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="E266" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F266" s="47" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="267">
@@ -13969,68 +13991,120 @@
       </c>
       <c r="C267" s="46" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D267" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E267" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F267" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="46" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B268" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C268" s="46" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D268" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E268" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F268" s="46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="46" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B269" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C269" s="46" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D267" s="46" t="n">
+      <c r="D269" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E267" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F267" s="46" t="n">
+      <c r="E269" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F269" s="46" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" s="47" t="inlineStr">
+    <row r="270">
+      <c r="A270" s="47" t="inlineStr">
         <is>
           <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
-      <c r="B268" s="47" t="inlineStr">
+      <c r="B270" s="47" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C268" s="47" t="inlineStr">
+      <c r="C270" s="47" t="inlineStr">
         <is>
           <t>Início manhã após 08h30</t>
         </is>
       </c>
-      <c r="D268" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E268" s="47" t="n">
+      <c r="D270" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E270" s="47" t="n">
         <v>0.3</v>
       </c>
-      <c r="F268" s="47" t="n">
+      <c r="F270" s="47" t="n">
         <v>-0.6</v>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" s="47" t="inlineStr">
+    <row r="271">
+      <c r="A271" s="47" t="inlineStr">
         <is>
           <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
-      <c r="B269" s="47" t="inlineStr">
+      <c r="B271" s="47" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C269" s="47" t="inlineStr">
+      <c r="C271" s="47" t="inlineStr">
         <is>
           <t>Início tarde após 14h30</t>
         </is>
       </c>
-      <c r="D269" s="47" t="n">
+      <c r="D271" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="E269" s="47" t="n">
+      <c r="E271" s="47" t="n">
         <v>0.3</v>
       </c>
-      <c r="F269" s="47" t="n">
+      <c r="F271" s="47" t="n">
         <v>-1.2</v>
       </c>
     </row>
@@ -14050,7 +14124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N82"/>
+  <dimension ref="A1:N83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -16037,13 +16111,13 @@
         <v>4.35</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>47.73</v>
+        <v>46.51</v>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
@@ -16432,7 +16506,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
@@ -16446,20 +16520,20 @@
         </is>
       </c>
       <c r="D45" s="4" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>5.53</v>
+        <v>5.78</v>
       </c>
       <c r="F45" s="4" t="n">
         <v>5</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Q022, Q025, Q026</t>
+          <t>Q010, Q011</t>
         </is>
       </c>
       <c r="I45" s="4" t="n">
@@ -16469,13 +16543,13 @@
         <v>0</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" s="4" t="n">
-        <v>52.94</v>
+        <v>28.12</v>
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
@@ -16496,14 +16570,14 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>424 - SÃO JOÃO</t>
+          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>5.69</v>
+        <v>5.53</v>
       </c>
       <c r="F46" s="4" t="n">
         <v>5</v>
@@ -16513,7 +16587,7 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>Q048, Q049, Q050</t>
+          <t>Q022, Q025, Q026</t>
         </is>
       </c>
       <c r="I46" s="4" t="n">
@@ -16523,13 +16597,13 @@
         <v>0</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="L46" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>42.62</v>
+        <v>52.94</v>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
@@ -16540,223 +16614,223 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
+          <t>Rosalina Beniel Vargas</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>424 - SÃO JOÃO</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Q048, Q049, Q050</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" s="4" t="n">
+        <v>42.62</v>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
           <t>Selba Ramona Afonso</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>431 - PANAMBI</t>
         </is>
       </c>
-      <c r="D47" s="4" t="n">
+      <c r="D48" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="E47" s="4" t="n">
+      <c r="E48" s="4" t="n">
         <v>6.67</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="F48" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="G48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>Q026</t>
         </is>
       </c>
-      <c r="I47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="4" t="n">
+      <c r="I48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="L47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="4" t="n">
+      <c r="L48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="4" t="n">
         <v>11.76</v>
       </c>
-      <c r="N47" s="4" t="inlineStr">
+      <c r="N48" s="4" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>435 - JARDIM PRIMOR</t>
         </is>
       </c>
-      <c r="D48" s="6" t="n">
+      <c r="D49" s="6" t="n">
         <v>81</v>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="E49" s="6" t="n">
         <v>4.75</v>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="F49" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G48" s="6" t="n">
+      <c r="G49" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="6" t="inlineStr">
+      <c r="H49" s="6" t="inlineStr">
         <is>
           <t>Q020, Q021, Q022</t>
         </is>
       </c>
-      <c r="I48" s="6" t="n">
+      <c r="I49" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="J48" s="6" t="n">
+      <c r="J49" s="6" t="n">
         <v>11.11</v>
       </c>
-      <c r="K48" s="6" t="n">
+      <c r="K49" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="L48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="6" t="n">
+      <c r="L49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="N48" s="6" t="inlineStr">
+      <c r="N49" s="6" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>434 - VILA AUREA</t>
         </is>
       </c>
-      <c r="D49" s="4" t="n">
+      <c r="D50" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="E49" s="4" t="n">
+      <c r="E50" s="4" t="n">
         <v>5.69</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="F50" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="G50" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>Q003</t>
         </is>
       </c>
-      <c r="I49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="4" t="n">
+      <c r="I50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="L49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="4" t="n">
+      <c r="L50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="4" t="n">
         <v>55.17</v>
       </c>
-      <c r="N49" s="4" t="inlineStr">
+      <c r="N50" s="4" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>Juliana Patricia Goncalves</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>445 - JARDIM IVONE</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>5.69</v>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>Q016, Q017, Q020, Q021, Q027, Q043</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J50" s="5" t="n">
-        <v>22.86</v>
-      </c>
-      <c r="K50" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="5" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="N50" s="5" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
@@ -16766,40 +16840,40 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>445 - JARDIM IVONE</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>3.24</v>
+        <v>5.69</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q016, Q017, Q020, Q021, Q027, Q043</t>
         </is>
       </c>
       <c r="I51" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>23.53</v>
+        <v>22.86</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L51" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>15</v>
+        <v>20.45</v>
       </c>
       <c r="N51" s="5" t="inlineStr">
         <is>
@@ -16820,98 +16894,98 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>435 - JARDIM PRIMOR</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>3</v>
       </c>
       <c r="G52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>Q018</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="K52" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="L52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Kariele Jackeline Rodrigues Silva</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>435 - JARDIM PRIMOR</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>Q005, Q006, Q007</t>
         </is>
       </c>
-      <c r="I52" s="5" t="n">
+      <c r="I53" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="J52" s="5" t="n">
+      <c r="J53" s="5" t="n">
         <v>44.59</v>
       </c>
-      <c r="K52" s="5" t="n">
+      <c r="K53" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="L52" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M52" s="5" t="n">
+      <c r="L53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" s="5" t="n">
         <v>31.48</v>
       </c>
-      <c r="N52" s="5" t="inlineStr">
+      <c r="N53" s="5" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>Kátia Cilene Silveira Machado</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>434 - VILA AUREA</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E53" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="F53" s="6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G53" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>Q023</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="K53" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="L53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="6" t="n">
-        <v>52.94</v>
-      </c>
-      <c r="N53" s="6" t="inlineStr">
-        <is>
-          <t>🟡 ATENÇÃO</t>
         </is>
       </c>
     </row>
@@ -16928,98 +17002,98 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
+          <t>434 - VILA AUREA</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>Q023</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K54" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="L54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="6" t="n">
+        <v>52.94</v>
+      </c>
+      <c r="N54" s="6" t="inlineStr">
+        <is>
+          <t>🟡 ATENÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Kátia Cilene Silveira Machado</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
           <t>443 - KAMEL SAAD 1</t>
         </is>
       </c>
-      <c r="D54" s="6" t="n">
+      <c r="D55" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="E54" s="6" t="n">
+      <c r="E55" s="6" t="n">
         <v>5.33</v>
       </c>
-      <c r="F54" s="6" t="n">
+      <c r="F55" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G54" s="6" t="n">
+      <c r="G55" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="H55" s="6" t="inlineStr">
         <is>
           <t>Q002, Q008, Q013, Q014, Q015, Q016, Q017</t>
         </is>
       </c>
-      <c r="I54" s="6" t="n">
+      <c r="I55" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="J54" s="6" t="n">
+      <c r="J55" s="6" t="n">
         <v>10.42</v>
       </c>
-      <c r="K54" s="6" t="n">
+      <c r="K55" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="L54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="6" t="n">
+      <c r="L55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="6" t="n">
         <v>43.53</v>
       </c>
-      <c r="N54" s="6" t="inlineStr">
+      <c r="N55" s="6" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>Rafael Ramos Recalde</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>435 - JARDIM PRIMOR</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>Q011, Q012, Q013</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="J55" s="5" t="n">
-        <v>56.25</v>
-      </c>
-      <c r="K55" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="L55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="5" t="n">
-        <v>34.02</v>
-      </c>
-      <c r="N55" s="5" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
         </is>
       </c>
     </row>
@@ -17036,40 +17110,40 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>446 - GUY VILELA</t>
+          <t>435 - JARDIM PRIMOR</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G56" s="5" t="n">
         <v>3</v>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>Q022, Q023, Q024</t>
+          <t>Q011, Q012, Q013</t>
         </is>
       </c>
       <c r="I56" s="5" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>36.36</v>
+        <v>56.25</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="L56" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>31.25</v>
+        <v>34.02</v>
       </c>
       <c r="N56" s="5" t="inlineStr">
         <is>
@@ -17090,40 +17164,40 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>446 - GUY VILELA</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>4.12</v>
+        <v>2.91</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>Q038</t>
+          <t>Q022, Q023, Q024</t>
         </is>
       </c>
       <c r="I57" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>23.08</v>
+        <v>36.36</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L57" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>16.13</v>
+        <v>31.25</v>
       </c>
       <c r="N57" s="5" t="inlineStr">
         <is>
@@ -17134,169 +17208,169 @@
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
+          <t>Rafael Ramos Recalde</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>434 - VILA AUREA</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>23.08</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>16.13</v>
+      </c>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
           <t>Rozana Reis da Silva</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>435 - JARDIM PRIMOR</t>
         </is>
       </c>
-      <c r="D58" s="5" t="n">
+      <c r="D59" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="E58" s="5" t="n">
+      <c r="E59" s="5" t="n">
         <v>3.49</v>
       </c>
-      <c r="F58" s="5" t="n">
+      <c r="F59" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G58" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="G59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
         <is>
           <t>Q025</t>
         </is>
       </c>
-      <c r="I58" s="5" t="n">
+      <c r="I59" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="J58" s="5" t="n">
+      <c r="J59" s="5" t="n">
         <v>34.88</v>
       </c>
-      <c r="K58" s="5" t="n">
+      <c r="K59" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="L58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="5" t="n">
+      <c r="L59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="5" t="n">
         <v>44.16</v>
       </c>
-      <c r="N58" s="5" t="inlineStr">
+      <c r="N59" s="5" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>435 - JARDIM PRIMOR</t>
         </is>
       </c>
-      <c r="D59" s="6" t="n">
+      <c r="D60" s="6" t="n">
         <v>78</v>
       </c>
-      <c r="E59" s="6" t="n">
+      <c r="E60" s="6" t="n">
         <v>4.19</v>
       </c>
-      <c r="F59" s="6" t="n">
+      <c r="F60" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="G59" s="6" t="n">
+      <c r="G60" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="H59" s="6" t="inlineStr">
+      <c r="H60" s="6" t="inlineStr">
         <is>
           <t>Q001, Q002, Q003, Q004</t>
         </is>
       </c>
-      <c r="I59" s="6" t="n">
+      <c r="I60" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="J59" s="6" t="n">
+      <c r="J60" s="6" t="n">
         <v>14.1</v>
       </c>
-      <c r="K59" s="6" t="n">
+      <c r="K60" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="L59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="6" t="n">
+      <c r="L60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="6" t="n">
         <v>17.02</v>
       </c>
-      <c r="N59" s="6" t="inlineStr">
+      <c r="N60" s="6" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>434 - VILA AUREA</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="F60" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G60" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>Q013</t>
-        </is>
-      </c>
-      <c r="I60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="4" t="n">
-        <v>47.37</v>
-      </c>
-      <c r="N60" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
@@ -17310,36 +17384,36 @@
         </is>
       </c>
       <c r="D61" s="4" t="n">
-        <v>96</v>
+        <v>10</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>5.53</v>
+        <v>6.4</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>Q025, Q028, Q033, Q040, Q041, Q043</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" s="4" t="n">
-        <v>26.15</v>
+        <v>47.37</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
@@ -17350,7 +17424,7 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -17364,36 +17438,36 @@
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>4.09</v>
+        <v>5.53</v>
       </c>
       <c r="F62" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q025, Q028, Q033, Q040, Q041, Q043</t>
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>50</v>
+        <v>26.15</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
@@ -17414,218 +17488,272 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>435 - JARDIM PRIMOR</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="D63" s="4" t="n">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>4.13</v>
+        <v>4.09</v>
       </c>
       <c r="F63" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G63" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Q008</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="N63" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Walquiria Araujo Flores</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>435 - JARDIM PRIMOR</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G64" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H63" s="4" t="inlineStr">
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>Q008, Q009, Q010</t>
         </is>
       </c>
-      <c r="I63" s="4" t="n">
+      <c r="I64" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="J63" s="4" t="n">
+      <c r="J64" s="4" t="n">
         <v>7.94</v>
       </c>
-      <c r="K63" s="4" t="n">
+      <c r="K64" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="L63" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="4" t="n">
+      <c r="L64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="4" t="n">
         <v>50.39</v>
       </c>
-      <c r="N63" s="4" t="inlineStr">
+      <c r="N64" s="4" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>Walquiria Araujo Flores</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>440 - JARDIM IBIRAPUERA</t>
         </is>
       </c>
-      <c r="D64" s="5" t="n">
+      <c r="D65" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="E64" s="5" t="n">
+      <c r="E65" s="5" t="n">
         <v>4.14</v>
       </c>
-      <c r="F64" s="5" t="n">
+      <c r="F65" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G64" s="5" t="n">
+      <c r="G65" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="H65" s="5" t="inlineStr">
         <is>
           <t>Q022, Q024, Q026</t>
         </is>
       </c>
-      <c r="I64" s="5" t="n">
+      <c r="I65" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="J64" s="5" t="n">
+      <c r="J65" s="5" t="n">
         <v>20.69</v>
       </c>
-      <c r="K64" s="5" t="n">
+      <c r="K65" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="L64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="5" t="n">
+      <c r="L65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="5" t="n">
         <v>29.27</v>
       </c>
-      <c r="N64" s="5" t="inlineStr">
+      <c r="N65" s="5" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="7" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="8" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>🟢 NORMAL</t>
         </is>
       </c>
-      <c r="B68" s="9" t="inlineStr">
+      <c r="B69" s="9" t="inlineStr">
         <is>
           <t>% Rápidas até 10%</t>
         </is>
       </c>
-      <c r="C68" s="10" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="11" t="inlineStr">
+      <c r="C69" s="10" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>🟡 ATENÇÃO</t>
         </is>
       </c>
-      <c r="B69" s="9" t="inlineStr">
+      <c r="B70" s="9" t="inlineStr">
         <is>
           <t>% Rápidas entre 11% e 20%</t>
         </is>
       </c>
-      <c r="C69" s="10" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="12" t="inlineStr">
+      <c r="C70" s="10" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr">
+      <c r="B71" s="9" t="inlineStr">
         <is>
           <t>% Rápidas acima de 20%</t>
         </is>
       </c>
-      <c r="C70" s="10" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="13" t="inlineStr">
+      <c r="C71" s="10" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
         <is>
           <t>⚠️ SEQUÊNCIA SUSPEITA</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="45" customHeight="1">
-      <c r="A73" s="14" t="inlineStr">
+    <row r="74" ht="45" customHeight="1">
+      <c r="A74" s="14" t="inlineStr">
         <is>
           <t>Duas ou mais visitas consecutivas do mesmo agente registradas no MESMO MINUTO de chegada são marcadas como suspeitas (o e-Visita não registra segundos, então o critério de negócio de 50s de diferença equivale, na prática, a 'mesmo minuto') — sugere lançamento em lote no sistema, não visita real de campo. Colunas: 'Visitas em Sequência Suspeita' (total de visitas envolvidas) e 'Maior Sequência Suspeita' (maior número de visitas seguidas nessa condição). Na aba 'Visitas Suspeitas', a coluna 'Diferença p/ Anterior (s)*' fica em branco quando o alerta da linha veio do par com a visita SEGUINTE (não da anterior).</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="15" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="15" t="inlineStr">
         <is>
           <t>🍽️ VISITAS NO HORÁRIO DE ALMOÇO</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="70" customHeight="1">
-      <c r="A76" s="14" t="inlineStr">
+    <row r="77" ht="70" customHeight="1">
+      <c r="A77" s="14" t="inlineStr">
         <is>
           <t>Coluna 'Visitas no Almoço (11h15-12h45)' conta as visitas com chegada registrada nesse intervalo — o horário oficial de almoço é 11h15 às 12h45, JÁ COM 15 MINUTOS DE TOLERÂNCIA em cada borda (visitas entre 11h-11h15 ou 12h45-13h não são tratadas como violação, só como 'fora do expediente' genérico) — use para checar se o agente está trabalhando no horário de almoço ou se há erro de lançamento. Essas visitas ficam de fora do cálculo de 'Início/Fim Manhã' e 'Início/Fim Tarde', que usam a primeira chegada e a última saída de cada dia (não a média de todos os horários), para refletir melhor o início e o fim reais do expediente.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="16" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="16" t="inlineStr">
         <is>
           <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" s="14" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" s="14" t="inlineStr">
         <is>
           <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="17" t="inlineStr">
-        <is>
-          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="17" t="inlineStr">
         <is>
+          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="17" t="inlineStr">
+        <is>
           <t>ℹ️ Visitas com duração NEGATIVA (saída antes da chegada — provável bug do sistema) foram excluídas do cálculo de Média/Mediana e estão detalhadas na aba 'Visitas Negativas', para investigação junto ao suporte do e-Visita.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N64"/>
+  <autoFilter ref="A2:N65"/>
   <mergeCells count="13">
     <mergeCell ref="A82:C82"/>
     <mergeCell ref="B69:C69"/>
     <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B68:C68"/>
     <mergeCell ref="A76:C76"/>
-    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A80:C80"/>
     <mergeCell ref="A79:C79"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A78:C78"/>
-    <mergeCell ref="A81:C81"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="A77:C77"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="B71:C71"/>
     <mergeCell ref="A73:C73"/>
-    <mergeCell ref="A72:C72"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18660,13 +18788,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -18678,7 +18806,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VISITAS COM DURAÇÃO ACIMA DE 15MIN (21 registros) — AUDITORIA DE POSSÍVEL MANIPULAÇÃO DE HORÁRIO (LANÇAMENTO PELO COMPUTADOR); NO CÁLCULO DE MÉDIA/MEDIANA ENTRAM COMO 15MIN</t>
+          <t>VISITAS COM DURAÇÃO ACIMA DE 15MIN (22 registros) — AUDITORIA DE POSSÍVEL MANIPULAÇÃO DE HORÁRIO (LANÇAMENTO PELO COMPUTADOR); NO CÁLCULO DE MÉDIA/MEDIANA ENTRAM COMO 15MIN</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -18996,47 +19124,47 @@
     <row r="8">
       <c r="A8" s="27" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C8" s="28" t="inlineStr">
         <is>
-          <t>16879459</t>
+          <t>16938750</t>
         </is>
       </c>
       <c r="D8" s="27" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E8" s="27" t="inlineStr">
         <is>
-          <t>Q025</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="F8" s="27" t="inlineStr">
         <is>
-          <t>Rua EPTACIO PESSOA</t>
+          <t>Rua SAO CRISTOVAO</t>
         </is>
       </c>
       <c r="G8" s="27" t="inlineStr">
         <is>
-          <t>245 - 1 - R</t>
+          <t>14 - 1 - R</t>
         </is>
       </c>
       <c r="H8" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 10:11</t>
+          <t>14/08/2026 09:53</t>
         </is>
       </c>
       <c r="I8" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 10:31</t>
+          <t>14/08/2026 10:13</t>
         </is>
       </c>
       <c r="J8" s="27" t="n">
@@ -19046,47 +19174,47 @@
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C9" s="28" t="inlineStr">
         <is>
-          <t>16938750</t>
+          <t>16879459</t>
         </is>
       </c>
       <c r="D9" s="27" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E9" s="27" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q025</t>
         </is>
       </c>
       <c r="F9" s="27" t="inlineStr">
         <is>
-          <t>Rua SAO CRISTOVAO</t>
+          <t>Rua EPTACIO PESSOA</t>
         </is>
       </c>
       <c r="G9" s="27" t="inlineStr">
         <is>
-          <t>14 - 1 - R</t>
+          <t>245 - 1 - R</t>
         </is>
       </c>
       <c r="H9" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 09:53</t>
+          <t>12/08/2026 10:11</t>
         </is>
       </c>
       <c r="I9" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 10:13</t>
+          <t>12/08/2026 10:31</t>
         </is>
       </c>
       <c r="J9" s="27" t="n">
@@ -19096,51 +19224,51 @@
     <row r="10">
       <c r="A10" s="27" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="B10" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C10" s="28" t="inlineStr">
         <is>
-          <t>16910075</t>
+          <t>16947422</t>
         </is>
       </c>
       <c r="D10" s="27" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E10" s="27" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="F10" s="27" t="inlineStr">
         <is>
-          <t>Rua CATANDUVA</t>
+          <t>Avenida BELMIRO DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="G10" s="27" t="inlineStr">
         <is>
-          <t>490 - R</t>
+          <t>2727 - R</t>
         </is>
       </c>
       <c r="H10" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:31</t>
+          <t>14/08/2026 08:56</t>
         </is>
       </c>
       <c r="I10" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:49</t>
+          <t>14/08/2026 09:15</t>
         </is>
       </c>
       <c r="J10" s="27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -19196,47 +19324,47 @@
     <row r="12">
       <c r="A12" s="27" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>16879448</t>
+          <t>16910075</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E12" s="27" t="inlineStr">
         <is>
-          <t>Q025</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="F12" s="27" t="inlineStr">
         <is>
-          <t>Rua MODESTO DAUZACKER</t>
+          <t>Rua CATANDUVA</t>
         </is>
       </c>
       <c r="G12" s="27" t="inlineStr">
         <is>
-          <t>62 - 1 - R</t>
+          <t>490 - R</t>
         </is>
       </c>
       <c r="H12" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 09:07</t>
+          <t>13/08/2026 15:31</t>
         </is>
       </c>
       <c r="I12" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 09:25</t>
+          <t>13/08/2026 15:49</t>
         </is>
       </c>
       <c r="J12" s="27" t="n">
@@ -19246,51 +19374,51 @@
     <row r="13">
       <c r="A13" s="27" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B13" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>16910076</t>
+          <t>16879448</t>
         </is>
       </c>
       <c r="D13" s="27" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E13" s="27" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q025</t>
         </is>
       </c>
       <c r="F13" s="27" t="inlineStr">
         <is>
-          <t>Rua CATANDUVA</t>
+          <t>Rua MODESTO DAUZACKER</t>
         </is>
       </c>
       <c r="G13" s="27" t="inlineStr">
         <is>
-          <t>166 - R</t>
+          <t>62 - 1 - R</t>
         </is>
       </c>
       <c r="H13" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:49</t>
+          <t>12/08/2026 09:07</t>
         </is>
       </c>
       <c r="I13" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 16:06</t>
+          <t>12/08/2026 09:25</t>
         </is>
       </c>
       <c r="J13" s="27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -19346,7 +19474,7 @@
     <row r="15">
       <c r="A15" s="27" t="inlineStr">
         <is>
-          <t>Raquel Ortiz dos Santos</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B15" s="27" t="inlineStr">
@@ -19356,37 +19484,37 @@
       </c>
       <c r="C15" s="28" t="inlineStr">
         <is>
-          <t>16881755</t>
+          <t>16910076</t>
         </is>
       </c>
       <c r="D15" s="27" t="inlineStr">
         <is>
-          <t>406 - JARDIM PRIMAVERA</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E15" s="27" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="F15" s="27" t="inlineStr">
         <is>
-          <t>Rua ELOAH VIEIRA DA SILVA</t>
+          <t>Rua CATANDUVA</t>
         </is>
       </c>
       <c r="G15" s="27" t="inlineStr">
         <is>
-          <t>26 - 2 - TB</t>
+          <t>166 - R</t>
         </is>
       </c>
       <c r="H15" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 16:12</t>
+          <t>13/08/2026 15:49</t>
         </is>
       </c>
       <c r="I15" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 16:29</t>
+          <t>13/08/2026 16:06</t>
         </is>
       </c>
       <c r="J15" s="27" t="n">
@@ -19396,47 +19524,47 @@
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C16" s="28" t="inlineStr">
         <is>
-          <t>16904092</t>
+          <t>16881755</t>
         </is>
       </c>
       <c r="D16" s="27" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>406 - JARDIM PRIMAVERA</t>
         </is>
       </c>
       <c r="E16" s="27" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="F16" s="27" t="inlineStr">
         <is>
-          <t>Rua SÃO JOÃO DEL REI</t>
+          <t>Rua ELOAH VIEIRA DA SILVA</t>
         </is>
       </c>
       <c r="G16" s="27" t="inlineStr">
         <is>
-          <t>300 - R</t>
+          <t>26 - 2 - TB</t>
         </is>
       </c>
       <c r="H16" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:14</t>
+          <t>12/08/2026 16:12</t>
         </is>
       </c>
       <c r="I16" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:31</t>
+          <t>12/08/2026 16:29</t>
         </is>
       </c>
       <c r="J16" s="27" t="n">
@@ -19446,47 +19574,47 @@
     <row r="17">
       <c r="A17" s="27" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C17" s="28" t="inlineStr">
         <is>
-          <t>16932380</t>
+          <t>16904092</t>
         </is>
       </c>
       <c r="D17" s="27" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E17" s="27" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="F17" s="27" t="inlineStr">
         <is>
-          <t>Rua CURITIBA</t>
+          <t>Rua SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="G17" s="27" t="inlineStr">
         <is>
-          <t>01 - TB</t>
+          <t>300 - R</t>
         </is>
       </c>
       <c r="H17" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 15:51</t>
+          <t>13/08/2026 15:14</t>
         </is>
       </c>
       <c r="I17" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 16:08</t>
+          <t>13/08/2026 15:31</t>
         </is>
       </c>
       <c r="J17" s="27" t="n">
@@ -19496,97 +19624,97 @@
     <row r="18">
       <c r="A18" s="27" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>16887154</t>
+          <t>16932380</t>
         </is>
       </c>
       <c r="D18" s="27" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E18" s="27" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="F18" s="27" t="inlineStr">
         <is>
-          <t>Rua DR. MIGUEL MARCONDES ARMANDO</t>
+          <t>Rua CURITIBA</t>
         </is>
       </c>
       <c r="G18" s="27" t="inlineStr">
         <is>
-          <t>950 - R</t>
+          <t>01 - TB</t>
         </is>
       </c>
       <c r="H18" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 09:04</t>
+          <t>14/08/2026 15:51</t>
         </is>
       </c>
       <c r="I18" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 09:20</t>
+          <t>14/08/2026 16:08</t>
         </is>
       </c>
       <c r="J18" s="27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="27" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C19" s="28" t="inlineStr">
         <is>
-          <t>16929550</t>
+          <t>16887154</t>
         </is>
       </c>
       <c r="D19" s="27" t="inlineStr">
         <is>
-          <t>420 - FERROVIARIA</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E19" s="27" t="inlineStr">
         <is>
-          <t>Q003</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="F19" s="27" t="inlineStr">
         <is>
-          <t>Rua ALAMEDA DOS TROLLES</t>
+          <t>Rua DR. MIGUEL MARCONDES ARMANDO</t>
         </is>
       </c>
       <c r="G19" s="27" t="inlineStr">
         <is>
-          <t>190 - R</t>
+          <t>950 - R</t>
         </is>
       </c>
       <c r="H19" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:31</t>
+          <t>12/08/2026 09:04</t>
         </is>
       </c>
       <c r="I19" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:47</t>
+          <t>12/08/2026 09:20</t>
         </is>
       </c>
       <c r="J19" s="27" t="n">
@@ -19596,7 +19724,7 @@
     <row r="20">
       <c r="A20" s="27" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="B20" s="27" t="inlineStr">
@@ -19606,37 +19734,37 @@
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>16932420</t>
+          <t>16929550</t>
         </is>
       </c>
       <c r="D20" s="27" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>420 - FERROVIARIA</t>
         </is>
       </c>
       <c r="E20" s="27" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="F20" s="27" t="inlineStr">
         <is>
-          <t>Rua 18 DE JULHO</t>
+          <t>Rua ALAMEDA DOS TROLLES</t>
         </is>
       </c>
       <c r="G20" s="27" t="inlineStr">
         <is>
-          <t>187 - R</t>
+          <t>190 - R</t>
         </is>
       </c>
       <c r="H20" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:52</t>
+          <t>14/08/2026 14:31</t>
         </is>
       </c>
       <c r="I20" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 15:08</t>
+          <t>14/08/2026 14:47</t>
         </is>
       </c>
       <c r="J20" s="27" t="n">
@@ -19656,7 +19784,7 @@
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>16932419</t>
+          <t>16932420</t>
         </is>
       </c>
       <c r="D21" s="27" t="inlineStr">
@@ -19671,22 +19799,22 @@
       </c>
       <c r="F21" s="27" t="inlineStr">
         <is>
-          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
+          <t>Rua 18 DE JULHO</t>
         </is>
       </c>
       <c r="G21" s="27" t="inlineStr">
         <is>
-          <t>451 - R</t>
+          <t>187 - R</t>
         </is>
       </c>
       <c r="H21" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>14/08/2026 14:52</t>
         </is>
       </c>
       <c r="I21" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:49</t>
+          <t>14/08/2026 15:08</t>
         </is>
       </c>
       <c r="J21" s="27" t="n">
@@ -19696,7 +19824,7 @@
     <row r="22">
       <c r="A22" s="27" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B22" s="27" t="inlineStr">
@@ -19706,37 +19834,37 @@
       </c>
       <c r="C22" s="28" t="inlineStr">
         <is>
-          <t>16945204</t>
+          <t>16932419</t>
         </is>
       </c>
       <c r="D22" s="27" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E22" s="27" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F22" s="27" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="G22" s="27" t="inlineStr">
         <is>
-          <t>3974 - 9 - R - 150</t>
+          <t>451 - R</t>
         </is>
       </c>
       <c r="H22" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 13:23</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="I22" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 13:39</t>
+          <t>14/08/2026 14:49</t>
         </is>
       </c>
       <c r="J22" s="27" t="n">
@@ -19756,7 +19884,7 @@
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>16928880</t>
+          <t>16945204</t>
         </is>
       </c>
       <c r="D23" s="27" t="inlineStr">
@@ -19766,35 +19894,85 @@
       </c>
       <c r="E23" s="27" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F23" s="27" t="inlineStr">
         <is>
-          <t>Rua CALOGERAS</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="G23" s="27" t="inlineStr">
         <is>
-          <t>1325 - C</t>
+          <t>3974 - 9 - R - 150</t>
         </is>
       </c>
       <c r="H23" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 13:48</t>
+          <t>14/08/2026 13:23</t>
         </is>
       </c>
       <c r="I23" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 14:04</t>
+          <t>14/08/2026 13:39</t>
         </is>
       </c>
       <c r="J23" s="27" t="n">
         <v>16</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="27" t="inlineStr">
+        <is>
+          <t>Gilmar Bitencourt Luiz</t>
+        </is>
+      </c>
+      <c r="B24" s="27" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="inlineStr">
+        <is>
+          <t>16928880</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>418 - CENTRO 4</t>
+        </is>
+      </c>
+      <c r="E24" s="27" t="inlineStr">
+        <is>
+          <t>Q008</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="inlineStr">
+        <is>
+          <t>Rua CALOGERAS</t>
+        </is>
+      </c>
+      <c r="G24" s="27" t="inlineStr">
+        <is>
+          <t>1325 - C</t>
+        </is>
+      </c>
+      <c r="H24" s="27" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:48</t>
+        </is>
+      </c>
+      <c r="I24" s="27" t="inlineStr">
+        <is>
+          <t>12/08/2026 14:04</t>
+        </is>
+      </c>
+      <c r="J24" s="27" t="n">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:J23"/>
+  <autoFilter ref="A2:J24"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -19820,6 +19998,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20609,7 +20788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -20624,7 +20803,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (26 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
+          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (24 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -21233,11 +21412,11 @@
     </row>
     <row r="19">
       <c r="A19" s="34" t="n">
-        <v>3038</v>
+        <v>113</v>
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C19" s="34" t="inlineStr">
@@ -21292,7 +21471,7 @@
       </c>
       <c r="F20" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G20" s="34" t="inlineStr">
@@ -21303,26 +21482,26 @@
     </row>
     <row r="21">
       <c r="A21" s="34" t="n">
-        <v>3038</v>
+        <v>157</v>
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C21" s="34" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D21" s="34" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E21" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F21" s="34" t="inlineStr">
@@ -21338,31 +21517,31 @@
     </row>
     <row r="22">
       <c r="A22" s="34" t="n">
-        <v>113</v>
+        <v>1943</v>
       </c>
       <c r="B22" s="34" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C22" s="34" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D22" s="34" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E22" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F22" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G22" s="34" t="inlineStr">
@@ -21373,11 +21552,11 @@
     </row>
     <row r="23">
       <c r="A23" s="34" t="n">
-        <v>157</v>
+        <v>1943</v>
       </c>
       <c r="B23" s="34" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C23" s="34" t="inlineStr">
@@ -21387,17 +21566,17 @@
       </c>
       <c r="D23" s="34" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E23" s="34" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F23" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G23" s="34" t="inlineStr">
@@ -21408,11 +21587,11 @@
     </row>
     <row r="24">
       <c r="A24" s="34" t="n">
-        <v>1943</v>
+        <v>161</v>
       </c>
       <c r="B24" s="34" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C24" s="34" t="inlineStr">
@@ -21422,12 +21601,12 @@
       </c>
       <c r="D24" s="34" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E24" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F24" s="34" t="inlineStr">
@@ -21467,7 +21646,7 @@
       </c>
       <c r="F25" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G25" s="34" t="inlineStr">
@@ -21502,7 +21681,7 @@
       </c>
       <c r="F26" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G26" s="34" t="inlineStr">
@@ -21511,78 +21690,8 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="34" t="n">
-        <v>1943</v>
-      </c>
-      <c r="B27" s="34" t="inlineStr">
-        <is>
-          <t>Juliana Patricia Goncalves</t>
-        </is>
-      </c>
-      <c r="C27" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D27" s="34" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="E27" s="34" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F27" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G27" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="34" t="n">
-        <v>161</v>
-      </c>
-      <c r="B28" s="34" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="C28" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D28" s="34" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="E28" s="34" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F28" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G28" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G28"/>
+  <autoFilter ref="A2:G26"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/data/historico/semana_319.xlsx
+++ b/data/historico/semana_319.xlsx
@@ -5049,7 +5049,7 @@
       </c>
       <c r="B3" s="36" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="C3" s="36" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="B6" s="36" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="C6" s="36" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="C7" s="36" t="inlineStr">

--- a/data/historico/semana_319.xlsx
+++ b/data/historico/semana_319.xlsx
@@ -33,7 +33,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$E$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$G$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="B6" s="36" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="C6" s="36" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="C7" s="36" t="inlineStr">
@@ -7181,15 +7181,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F271"/>
+  <dimension ref="A1:G271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -7203,6 +7204,7 @@
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -7222,15 +7224,24 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>Dias Trabalhados</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Dias Úteis Esperados no Mês</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
           <t>Pontuação Final</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -7247,14 +7258,19 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F3" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -7271,14 +7287,19 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -7295,14 +7316,19 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -7319,14 +7345,19 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -7343,14 +7374,19 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -7367,14 +7403,19 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F8" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -7391,14 +7432,19 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -7415,14 +7461,19 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -7439,14 +7490,19 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F11" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -7463,14 +7519,19 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -7487,14 +7548,19 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -7511,14 +7577,19 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -7535,14 +7606,19 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -7559,14 +7635,19 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F16" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -7583,14 +7664,19 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -7607,14 +7693,19 @@
         </is>
       </c>
       <c r="D18" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F18" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -7631,14 +7722,19 @@
         </is>
       </c>
       <c r="D19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F19" s="4" t="n">
         <v>99.8</v>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -7655,14 +7751,19 @@
         </is>
       </c>
       <c r="D20" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F20" s="4" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -7679,14 +7780,19 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F21" s="4" t="n">
         <v>99.40000000000001</v>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -7703,14 +7809,19 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F22" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -7727,14 +7838,19 @@
         </is>
       </c>
       <c r="D23" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F23" s="4" t="n">
         <v>98.3</v>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -7751,14 +7867,19 @@
         </is>
       </c>
       <c r="D24" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" s="4" t="n">
         <v>97.8</v>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -7775,14 +7896,19 @@
         </is>
       </c>
       <c r="D25" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F25" s="4" t="n">
         <v>96.2</v>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -7799,14 +7925,19 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" s="4" t="n">
         <v>92.8</v>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -7823,14 +7954,19 @@
         </is>
       </c>
       <c r="D27" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="F27" s="4" t="n">
         <v>90.09999999999999</v>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
       </c>
-      <c r="F27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
@@ -7847,14 +7983,19 @@
         </is>
       </c>
       <c r="D28" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="F28" s="6" t="n">
         <v>88.7</v>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
@@ -7871,14 +8012,19 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F29" s="6" t="n">
         <v>86.7</v>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
@@ -7895,14 +8041,19 @@
         </is>
       </c>
       <c r="D30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="F30" s="6" t="n">
         <v>84.90000000000001</v>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
@@ -7919,14 +8070,19 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="F31" s="6" t="n">
         <v>84.8</v>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
@@ -7943,14 +8099,19 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F32" s="6" t="n">
         <v>84.7</v>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
@@ -7967,14 +8128,19 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" s="6" t="n">
         <v>83.3</v>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
@@ -7991,14 +8157,19 @@
         </is>
       </c>
       <c r="D34" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F34" s="6" t="n">
         <v>82.3</v>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -8015,14 +8186,19 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="F35" s="6" t="n">
         <v>82.2</v>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
@@ -8039,14 +8215,19 @@
         </is>
       </c>
       <c r="D36" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="F36" s="6" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
@@ -8063,14 +8244,19 @@
         </is>
       </c>
       <c r="D37" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="F37" s="6" t="n">
         <v>75.5</v>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
       </c>
-      <c r="F37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="44" t="n">
@@ -8087,14 +8273,19 @@
         </is>
       </c>
       <c r="D38" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" s="44" t="n">
+        <v>21</v>
+      </c>
+      <c r="F38" s="44" t="n">
         <v>64.40000000000001</v>
       </c>
-      <c r="E38" s="44" t="inlineStr">
+      <c r="G38" s="44" t="inlineStr">
         <is>
           <t>🟠 ATENÇÃO</t>
         </is>
       </c>
-      <c r="F38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
@@ -8111,14 +8302,19 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F39" s="5" t="n">
         <v>47.6</v>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>🔴 CRÍTICO</t>
         </is>
       </c>
-      <c r="F39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -8127,6 +8323,7 @@
       <c r="D40" s="2" t="n"/>
       <c r="E40" s="2" t="n"/>
       <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -8135,6 +8332,7 @@
       <c r="D41" s="2" t="n"/>
       <c r="E41" s="2" t="n"/>
       <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="45" t="inlineStr">
@@ -8147,6 +8345,7 @@
       <c r="D42" s="2" t="n"/>
       <c r="E42" s="2" t="n"/>
       <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -8179,6 +8378,7 @@
           <t>Pontos Aplicados</t>
         </is>
       </c>
+      <c r="G43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="46" t="inlineStr">
@@ -8205,6 +8405,7 @@
       <c r="F44" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="46" t="inlineStr">
@@ -8231,6 +8432,7 @@
       <c r="F45" s="46" t="n">
         <v>3</v>
       </c>
+      <c r="G45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="47" t="inlineStr">
@@ -8252,11 +8454,12 @@
         <v>1</v>
       </c>
       <c r="E46" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F46" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="47" t="inlineStr">
@@ -8278,11 +8481,12 @@
         <v>4</v>
       </c>
       <c r="E47" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F47" s="47" t="n">
         <v>-2.4</v>
       </c>
+      <c r="G47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="46" t="inlineStr">
@@ -8309,6 +8513,7 @@
       <c r="F48" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="46" t="inlineStr">
@@ -8335,6 +8540,7 @@
       <c r="F49" s="46" t="n">
         <v>3</v>
       </c>
+      <c r="G49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="47" t="inlineStr">
@@ -8356,11 +8562,12 @@
         <v>1</v>
       </c>
       <c r="E50" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F50" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="47" t="inlineStr">
@@ -8382,11 +8589,12 @@
         <v>1</v>
       </c>
       <c r="E51" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F51" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="47" t="inlineStr">
@@ -8408,11 +8616,12 @@
         <v>3</v>
       </c>
       <c r="E52" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F52" s="47" t="n">
         <v>-1.8</v>
       </c>
+      <c r="G52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="47" t="inlineStr">
@@ -8434,11 +8643,12 @@
         <v>2</v>
       </c>
       <c r="E53" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F53" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="47" t="inlineStr">
@@ -8460,11 +8670,12 @@
         <v>7</v>
       </c>
       <c r="E54" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F54" s="47" t="n">
         <v>-4.2</v>
       </c>
+      <c r="G54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="46" t="inlineStr">
@@ -8491,6 +8702,7 @@
       <c r="F55" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="46" t="inlineStr">
@@ -8517,6 +8729,7 @@
       <c r="F56" s="46" t="n">
         <v>2</v>
       </c>
+      <c r="G56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="47" t="inlineStr">
@@ -8538,11 +8751,12 @@
         <v>1</v>
       </c>
       <c r="E57" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F57" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="47" t="inlineStr">
@@ -8564,11 +8778,12 @@
         <v>1</v>
       </c>
       <c r="E58" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F58" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="47" t="inlineStr">
@@ -8590,11 +8805,12 @@
         <v>2</v>
       </c>
       <c r="E59" s="47" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F59" s="47" t="n">
         <v>-6</v>
       </c>
+      <c r="G59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="46" t="inlineStr">
@@ -8621,6 +8837,7 @@
       <c r="F60" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G60" s="2" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="46" t="inlineStr">
@@ -8647,6 +8864,7 @@
       <c r="F61" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="46" t="inlineStr">
@@ -8673,6 +8891,7 @@
       <c r="F62" s="46" t="n">
         <v>3</v>
       </c>
+      <c r="G62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="47" t="inlineStr">
@@ -8694,11 +8913,12 @@
         <v>1</v>
       </c>
       <c r="E63" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F63" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="47" t="inlineStr">
@@ -8720,11 +8940,12 @@
         <v>2</v>
       </c>
       <c r="E64" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F64" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="46" t="inlineStr">
@@ -8751,6 +8972,7 @@
       <c r="F65" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="46" t="inlineStr">
@@ -8777,6 +8999,7 @@
       <c r="F66" s="46" t="n">
         <v>3</v>
       </c>
+      <c r="G66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="47" t="inlineStr">
@@ -8798,11 +9021,12 @@
         <v>1</v>
       </c>
       <c r="E67" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F67" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="47" t="inlineStr">
@@ -8824,11 +9048,12 @@
         <v>3</v>
       </c>
       <c r="E68" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F68" s="47" t="n">
         <v>-1.8</v>
       </c>
+      <c r="G68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="47" t="inlineStr">
@@ -8850,11 +9075,12 @@
         <v>4</v>
       </c>
       <c r="E69" s="47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" s="47" t="n">
         <v>-8</v>
       </c>
+      <c r="G69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="47" t="inlineStr">
@@ -8876,11 +9102,12 @@
         <v>2</v>
       </c>
       <c r="E70" s="47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F70" s="47" t="n">
         <v>-2</v>
       </c>
+      <c r="G70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="47" t="inlineStr">
@@ -8902,11 +9129,12 @@
         <v>52</v>
       </c>
       <c r="E71" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F71" s="47" t="n">
         <v>-31.2</v>
       </c>
+      <c r="G71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="46" t="inlineStr">
@@ -8933,6 +9161,7 @@
       <c r="F72" s="46" t="n">
         <v>3</v>
       </c>
+      <c r="G72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="47" t="inlineStr">
@@ -8959,6 +9188,7 @@
       <c r="F73" s="47" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="47" t="inlineStr">
@@ -8980,11 +9210,12 @@
         <v>2</v>
       </c>
       <c r="E74" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F74" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="47" t="inlineStr">
@@ -9006,11 +9237,12 @@
         <v>1</v>
       </c>
       <c r="E75" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F75" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="47" t="inlineStr">
@@ -9032,11 +9264,12 @@
         <v>1</v>
       </c>
       <c r="E76" s="47" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F76" s="47" t="n">
         <v>-3</v>
       </c>
+      <c r="G76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="47" t="inlineStr">
@@ -9058,11 +9291,12 @@
         <v>37</v>
       </c>
       <c r="E77" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F77" s="47" t="n">
         <v>-22.2</v>
       </c>
+      <c r="G77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="46" t="inlineStr">
@@ -9089,6 +9323,7 @@
       <c r="F78" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="46" t="inlineStr">
@@ -9115,6 +9350,7 @@
       <c r="F79" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="46" t="inlineStr">
@@ -9141,6 +9377,7 @@
       <c r="F80" s="46" t="n">
         <v>1</v>
       </c>
+      <c r="G80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="47" t="inlineStr">
@@ -9167,6 +9404,7 @@
       <c r="F81" s="47" t="n">
         <v>-1</v>
       </c>
+      <c r="G81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="47" t="inlineStr">
@@ -9188,11 +9426,12 @@
         <v>2</v>
       </c>
       <c r="E82" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F82" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="47" t="inlineStr">
@@ -9214,11 +9453,12 @@
         <v>2</v>
       </c>
       <c r="E83" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F83" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="47" t="inlineStr">
@@ -9240,11 +9480,12 @@
         <v>1</v>
       </c>
       <c r="E84" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F84" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="46" t="inlineStr">
@@ -9271,6 +9512,7 @@
       <c r="F85" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G85" s="2" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="46" t="inlineStr">
@@ -9297,6 +9539,7 @@
       <c r="F86" s="46" t="n">
         <v>2</v>
       </c>
+      <c r="G86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="47" t="inlineStr">
@@ -9323,6 +9566,7 @@
       <c r="F87" s="47" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="47" t="inlineStr">
@@ -9344,11 +9588,12 @@
         <v>1</v>
       </c>
       <c r="E88" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F88" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="47" t="inlineStr">
@@ -9370,11 +9615,12 @@
         <v>1</v>
       </c>
       <c r="E89" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F89" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="47" t="inlineStr">
@@ -9396,11 +9642,12 @@
         <v>4</v>
       </c>
       <c r="E90" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F90" s="47" t="n">
         <v>-2.4</v>
       </c>
+      <c r="G90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="46" t="inlineStr">
@@ -9427,6 +9674,7 @@
       <c r="F91" s="46" t="n">
         <v>1</v>
       </c>
+      <c r="G91" s="2" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="47" t="inlineStr">
@@ -9453,6 +9701,7 @@
       <c r="F92" s="47" t="n">
         <v>-1</v>
       </c>
+      <c r="G92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="47" t="inlineStr">
@@ -9474,11 +9723,12 @@
         <v>1</v>
       </c>
       <c r="E93" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F93" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="47" t="inlineStr">
@@ -9500,11 +9750,12 @@
         <v>1</v>
       </c>
       <c r="E94" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F94" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="47" t="inlineStr">
@@ -9526,11 +9777,12 @@
         <v>2</v>
       </c>
       <c r="E95" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F95" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="47" t="inlineStr">
@@ -9552,11 +9804,12 @@
         <v>1</v>
       </c>
       <c r="E96" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F96" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="47" t="inlineStr">
@@ -9578,11 +9831,12 @@
         <v>1</v>
       </c>
       <c r="E97" s="47" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F97" s="47" t="n">
         <v>-3</v>
       </c>
+      <c r="G97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="47" t="inlineStr">
@@ -9604,11 +9858,12 @@
         <v>2</v>
       </c>
       <c r="E98" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F98" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="46" t="inlineStr">
@@ -9635,6 +9890,7 @@
       <c r="F99" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="46" t="inlineStr">
@@ -9661,6 +9917,7 @@
       <c r="F100" s="46" t="n">
         <v>1</v>
       </c>
+      <c r="G100" s="2" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="47" t="inlineStr">
@@ -9687,6 +9944,7 @@
       <c r="F101" s="47" t="n">
         <v>-1.5</v>
       </c>
+      <c r="G101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="47" t="inlineStr">
@@ -9708,11 +9966,12 @@
         <v>1</v>
       </c>
       <c r="E102" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F102" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="47" t="inlineStr">
@@ -9734,11 +9993,12 @@
         <v>1</v>
       </c>
       <c r="E103" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F103" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="47" t="inlineStr">
@@ -9760,11 +10020,12 @@
         <v>2</v>
       </c>
       <c r="E104" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F104" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="47" t="inlineStr">
@@ -9786,11 +10047,12 @@
         <v>4</v>
       </c>
       <c r="E105" s="47" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F105" s="47" t="n">
         <v>-12</v>
       </c>
+      <c r="G105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="46" t="inlineStr">
@@ -9817,6 +10079,7 @@
       <c r="F106" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="46" t="inlineStr">
@@ -9843,6 +10106,7 @@
       <c r="F107" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G107" s="2" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="46" t="inlineStr">
@@ -9869,6 +10133,7 @@
       <c r="F108" s="46" t="n">
         <v>3</v>
       </c>
+      <c r="G108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="47" t="inlineStr">
@@ -9890,11 +10155,12 @@
         <v>1</v>
       </c>
       <c r="E109" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F109" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="47" t="inlineStr">
@@ -9916,11 +10182,12 @@
         <v>1</v>
       </c>
       <c r="E110" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F110" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="47" t="inlineStr">
@@ -9942,11 +10209,12 @@
         <v>1</v>
       </c>
       <c r="E111" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F111" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="46" t="inlineStr">
@@ -9973,6 +10241,7 @@
       <c r="F112" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="46" t="inlineStr">
@@ -9999,6 +10268,7 @@
       <c r="F113" s="46" t="n">
         <v>2</v>
       </c>
+      <c r="G113" s="2" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="47" t="inlineStr">
@@ -10025,6 +10295,7 @@
       <c r="F114" s="47" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="47" t="inlineStr">
@@ -10046,11 +10317,12 @@
         <v>2</v>
       </c>
       <c r="E115" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F115" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="47" t="inlineStr">
@@ -10072,11 +10344,12 @@
         <v>2</v>
       </c>
       <c r="E116" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F116" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="47" t="inlineStr">
@@ -10098,11 +10371,12 @@
         <v>2</v>
       </c>
       <c r="E117" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F117" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G117" s="2" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="46" t="inlineStr">
@@ -10129,6 +10403,7 @@
       <c r="F118" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G118" s="2" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="46" t="inlineStr">
@@ -10155,6 +10430,7 @@
       <c r="F119" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G119" s="2" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="46" t="inlineStr">
@@ -10181,6 +10457,7 @@
       <c r="F120" s="46" t="n">
         <v>3</v>
       </c>
+      <c r="G120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="47" t="inlineStr">
@@ -10202,11 +10479,12 @@
         <v>1</v>
       </c>
       <c r="E121" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F121" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G121" s="2" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="47" t="inlineStr">
@@ -10228,11 +10506,12 @@
         <v>1</v>
       </c>
       <c r="E122" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F122" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="47" t="inlineStr">
@@ -10254,11 +10533,12 @@
         <v>1</v>
       </c>
       <c r="E123" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F123" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="46" t="inlineStr">
@@ -10285,6 +10565,7 @@
       <c r="F124" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G124" s="2" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="46" t="inlineStr">
@@ -10311,6 +10592,7 @@
       <c r="F125" s="46" t="n">
         <v>3</v>
       </c>
+      <c r="G125" s="2" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="46" t="inlineStr">
@@ -10337,6 +10619,7 @@
       <c r="F126" s="46" t="n">
         <v>2</v>
       </c>
+      <c r="G126" s="2" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="47" t="inlineStr">
@@ -10363,6 +10646,7 @@
       <c r="F127" s="47" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G127" s="2" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="47" t="inlineStr">
@@ -10384,11 +10668,12 @@
         <v>1</v>
       </c>
       <c r="E128" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F128" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G128" s="2" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="46" t="inlineStr">
@@ -10415,6 +10700,7 @@
       <c r="F129" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G129" s="2" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="46" t="inlineStr">
@@ -10441,6 +10727,7 @@
       <c r="F130" s="46" t="n">
         <v>3</v>
       </c>
+      <c r="G130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="47" t="inlineStr">
@@ -10462,11 +10749,12 @@
         <v>1</v>
       </c>
       <c r="E131" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F131" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G131" s="2" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="47" t="inlineStr">
@@ -10488,11 +10776,12 @@
         <v>1</v>
       </c>
       <c r="E132" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F132" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="47" t="inlineStr">
@@ -10514,11 +10803,12 @@
         <v>2</v>
       </c>
       <c r="E133" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F133" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="47" t="inlineStr">
@@ -10540,11 +10830,12 @@
         <v>2</v>
       </c>
       <c r="E134" s="47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F134" s="47" t="n">
         <v>-4</v>
       </c>
+      <c r="G134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="47" t="inlineStr">
@@ -10566,11 +10857,12 @@
         <v>9</v>
       </c>
       <c r="E135" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F135" s="47" t="n">
         <v>-5.4</v>
       </c>
+      <c r="G135" s="2" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="46" t="inlineStr">
@@ -10597,6 +10889,7 @@
       <c r="F136" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G136" s="2" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="46" t="inlineStr">
@@ -10623,6 +10916,7 @@
       <c r="F137" s="46" t="n">
         <v>3</v>
       </c>
+      <c r="G137" s="2" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="47" t="inlineStr">
@@ -10644,11 +10938,12 @@
         <v>2</v>
       </c>
       <c r="E138" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F138" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="47" t="inlineStr">
@@ -10670,11 +10965,12 @@
         <v>1</v>
       </c>
       <c r="E139" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F139" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G139" s="2" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="47" t="inlineStr">
@@ -10696,11 +10992,12 @@
         <v>14</v>
       </c>
       <c r="E140" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F140" s="47" t="n">
         <v>-8.4</v>
       </c>
+      <c r="G140" s="2" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="46" t="inlineStr">
@@ -10727,6 +11024,7 @@
       <c r="F141" s="46" t="n">
         <v>1</v>
       </c>
+      <c r="G141" s="2" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="47" t="inlineStr">
@@ -10753,6 +11051,7 @@
       <c r="F142" s="47" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="47" t="inlineStr">
@@ -10774,11 +11073,12 @@
         <v>1</v>
       </c>
       <c r="E143" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F143" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G143" s="2" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="47" t="inlineStr">
@@ -10800,11 +11100,12 @@
         <v>2</v>
       </c>
       <c r="E144" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F144" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="47" t="inlineStr">
@@ -10826,11 +11127,12 @@
         <v>3</v>
       </c>
       <c r="E145" s="47" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F145" s="47" t="n">
         <v>-9</v>
       </c>
+      <c r="G145" s="2" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="47" t="inlineStr">
@@ -10852,11 +11154,12 @@
         <v>8</v>
       </c>
       <c r="E146" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F146" s="47" t="n">
         <v>-4.8</v>
       </c>
+      <c r="G146" s="2" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="46" t="inlineStr">
@@ -10883,6 +11186,7 @@
       <c r="F147" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G147" s="2" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="46" t="inlineStr">
@@ -10909,6 +11213,7 @@
       <c r="F148" s="46" t="n">
         <v>3</v>
       </c>
+      <c r="G148" s="2" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="47" t="inlineStr">
@@ -10930,11 +11235,12 @@
         <v>2</v>
       </c>
       <c r="E149" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F149" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G149" s="2" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="47" t="inlineStr">
@@ -10956,11 +11262,12 @@
         <v>2</v>
       </c>
       <c r="E150" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F150" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="47" t="inlineStr">
@@ -10982,11 +11289,12 @@
         <v>2</v>
       </c>
       <c r="E151" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F151" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G151" s="2" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="47" t="inlineStr">
@@ -11008,11 +11316,12 @@
         <v>37</v>
       </c>
       <c r="E152" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F152" s="47" t="n">
         <v>-22.2</v>
       </c>
+      <c r="G152" s="2" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="46" t="inlineStr">
@@ -11039,6 +11348,7 @@
       <c r="F153" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G153" s="2" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="46" t="inlineStr">
@@ -11065,6 +11375,7 @@
       <c r="F154" s="46" t="n">
         <v>2</v>
       </c>
+      <c r="G154" s="2" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="47" t="inlineStr">
@@ -11091,6 +11402,7 @@
       <c r="F155" s="47" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G155" s="2" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="47" t="inlineStr">
@@ -11112,11 +11424,12 @@
         <v>1</v>
       </c>
       <c r="E156" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F156" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="47" t="inlineStr">
@@ -11138,11 +11451,12 @@
         <v>2</v>
       </c>
       <c r="E157" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F157" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G157" s="2" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="47" t="inlineStr">
@@ -11164,11 +11478,12 @@
         <v>3</v>
       </c>
       <c r="E158" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F158" s="47" t="n">
         <v>-1.8</v>
       </c>
+      <c r="G158" s="2" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="47" t="inlineStr">
@@ -11190,11 +11505,12 @@
         <v>1</v>
       </c>
       <c r="E159" s="47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F159" s="47" t="n">
         <v>-1</v>
       </c>
+      <c r="G159" s="2" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="47" t="inlineStr">
@@ -11216,11 +11532,12 @@
         <v>6</v>
       </c>
       <c r="E160" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F160" s="47" t="n">
         <v>-3.6</v>
       </c>
+      <c r="G160" s="2" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="46" t="inlineStr">
@@ -11247,6 +11564,7 @@
       <c r="F161" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G161" s="2" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="46" t="inlineStr">
@@ -11273,6 +11591,7 @@
       <c r="F162" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G162" s="2" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="46" t="inlineStr">
@@ -11299,6 +11618,7 @@
       <c r="F163" s="46" t="n">
         <v>1</v>
       </c>
+      <c r="G163" s="2" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="47" t="inlineStr">
@@ -11320,11 +11640,12 @@
         <v>1</v>
       </c>
       <c r="E164" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F164" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="47" t="inlineStr">
@@ -11346,11 +11667,12 @@
         <v>1</v>
       </c>
       <c r="E165" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F165" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G165" s="2" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="46" t="inlineStr">
@@ -11377,6 +11699,7 @@
       <c r="F166" s="46" t="n">
         <v>2</v>
       </c>
+      <c r="G166" s="2" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="47" t="inlineStr">
@@ -11403,6 +11726,7 @@
       <c r="F167" s="47" t="n">
         <v>-1</v>
       </c>
+      <c r="G167" s="2" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="47" t="inlineStr">
@@ -11424,11 +11748,12 @@
         <v>2</v>
       </c>
       <c r="E168" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F168" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="47" t="inlineStr">
@@ -11450,11 +11775,12 @@
         <v>1</v>
       </c>
       <c r="E169" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F169" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G169" s="2" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="47" t="inlineStr">
@@ -11476,11 +11802,12 @@
         <v>1</v>
       </c>
       <c r="E170" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F170" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="47" t="inlineStr">
@@ -11502,11 +11829,12 @@
         <v>1</v>
       </c>
       <c r="E171" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F171" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G171" s="2" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="47" t="inlineStr">
@@ -11528,11 +11856,12 @@
         <v>1</v>
       </c>
       <c r="E172" s="47" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F172" s="47" t="n">
         <v>-3</v>
       </c>
+      <c r="G172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="47" t="inlineStr">
@@ -11554,11 +11883,12 @@
         <v>79</v>
       </c>
       <c r="E173" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F173" s="47" t="n">
         <v>-47.4</v>
       </c>
+      <c r="G173" s="2" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="46" t="inlineStr">
@@ -11585,6 +11915,7 @@
       <c r="F174" s="46" t="n">
         <v>1</v>
       </c>
+      <c r="G174" s="2" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="47" t="inlineStr">
@@ -11611,6 +11942,7 @@
       <c r="F175" s="47" t="n">
         <v>-1.5</v>
       </c>
+      <c r="G175" s="2" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="47" t="inlineStr">
@@ -11632,11 +11964,12 @@
         <v>2</v>
       </c>
       <c r="E176" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F176" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="47" t="inlineStr">
@@ -11658,11 +11991,12 @@
         <v>2</v>
       </c>
       <c r="E177" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F177" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G177" s="2" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="47" t="inlineStr">
@@ -11684,11 +12018,12 @@
         <v>1</v>
       </c>
       <c r="E178" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F178" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G178" s="2" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="47" t="inlineStr">
@@ -11710,11 +12045,12 @@
         <v>1</v>
       </c>
       <c r="E179" s="47" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F179" s="47" t="n">
         <v>-3</v>
       </c>
+      <c r="G179" s="2" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="47" t="inlineStr">
@@ -11736,11 +12072,12 @@
         <v>17</v>
       </c>
       <c r="E180" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F180" s="47" t="n">
         <v>-10.2</v>
       </c>
+      <c r="G180" s="2" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="46" t="inlineStr">
@@ -11767,6 +12104,7 @@
       <c r="F181" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G181" s="2" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="46" t="inlineStr">
@@ -11793,6 +12131,7 @@
       <c r="F182" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G182" s="2" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="46" t="inlineStr">
@@ -11819,6 +12158,7 @@
       <c r="F183" s="46" t="n">
         <v>1</v>
       </c>
+      <c r="G183" s="2" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="47" t="inlineStr">
@@ -11845,6 +12185,7 @@
       <c r="F184" s="47" t="n">
         <v>-1</v>
       </c>
+      <c r="G184" s="2" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="47" t="inlineStr">
@@ -11866,11 +12207,12 @@
         <v>1</v>
       </c>
       <c r="E185" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F185" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G185" s="2" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="47" t="inlineStr">
@@ -11892,11 +12234,12 @@
         <v>2</v>
       </c>
       <c r="E186" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F186" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G186" s="2" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="47" t="inlineStr">
@@ -11918,11 +12261,12 @@
         <v>1</v>
       </c>
       <c r="E187" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F187" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G187" s="2" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="46" t="inlineStr">
@@ -11949,6 +12293,7 @@
       <c r="F188" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G188" s="2" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="46" t="inlineStr">
@@ -11975,6 +12320,7 @@
       <c r="F189" s="46" t="n">
         <v>3</v>
       </c>
+      <c r="G189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="47" t="inlineStr">
@@ -11996,11 +12342,12 @@
         <v>2</v>
       </c>
       <c r="E190" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F190" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G190" s="2" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="47" t="inlineStr">
@@ -12022,11 +12369,12 @@
         <v>2</v>
       </c>
       <c r="E191" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F191" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G191" s="2" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="47" t="inlineStr">
@@ -12048,11 +12396,12 @@
         <v>50</v>
       </c>
       <c r="E192" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F192" s="47" t="n">
         <v>-30</v>
       </c>
+      <c r="G192" s="2" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="46" t="inlineStr">
@@ -12079,6 +12428,7 @@
       <c r="F193" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G193" s="2" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="46" t="inlineStr">
@@ -12105,6 +12455,7 @@
       <c r="F194" s="46" t="n">
         <v>2</v>
       </c>
+      <c r="G194" s="2" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="47" t="inlineStr">
@@ -12131,6 +12482,7 @@
       <c r="F195" s="47" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G195" s="2" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="47" t="inlineStr">
@@ -12152,11 +12504,12 @@
         <v>3</v>
       </c>
       <c r="E196" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F196" s="47" t="n">
         <v>-1.8</v>
       </c>
+      <c r="G196" s="2" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="47" t="inlineStr">
@@ -12178,11 +12531,12 @@
         <v>2</v>
       </c>
       <c r="E197" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F197" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G197" s="2" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="47" t="inlineStr">
@@ -12204,11 +12558,12 @@
         <v>2</v>
       </c>
       <c r="E198" s="47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F198" s="47" t="n">
         <v>-2</v>
       </c>
+      <c r="G198" s="2" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="47" t="inlineStr">
@@ -12230,11 +12585,12 @@
         <v>32</v>
       </c>
       <c r="E199" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F199" s="47" t="n">
         <v>-19.2</v>
       </c>
+      <c r="G199" s="2" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="46" t="inlineStr">
@@ -12261,6 +12617,7 @@
       <c r="F200" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G200" s="2" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="46" t="inlineStr">
@@ -12287,6 +12644,7 @@
       <c r="F201" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G201" s="2" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="46" t="inlineStr">
@@ -12313,6 +12671,7 @@
       <c r="F202" s="46" t="n">
         <v>2</v>
       </c>
+      <c r="G202" s="2" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="47" t="inlineStr">
@@ -12339,6 +12698,7 @@
       <c r="F203" s="47" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G203" s="2" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="47" t="inlineStr">
@@ -12360,11 +12720,12 @@
         <v>1</v>
       </c>
       <c r="E204" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F204" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G204" s="2" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="47" t="inlineStr">
@@ -12386,11 +12747,12 @@
         <v>1</v>
       </c>
       <c r="E205" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F205" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G205" s="2" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="47" t="inlineStr">
@@ -12412,11 +12774,12 @@
         <v>1</v>
       </c>
       <c r="E206" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F206" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G206" s="2" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="47" t="inlineStr">
@@ -12438,11 +12801,12 @@
         <v>1</v>
       </c>
       <c r="E207" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F207" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G207" s="2" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="46" t="inlineStr">
@@ -12469,6 +12833,7 @@
       <c r="F208" s="46" t="n">
         <v>1</v>
       </c>
+      <c r="G208" s="2" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="47" t="inlineStr">
@@ -12490,11 +12855,12 @@
         <v>1</v>
       </c>
       <c r="E209" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F209" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G209" s="2" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="47" t="inlineStr">
@@ -12516,11 +12882,12 @@
         <v>1</v>
       </c>
       <c r="E210" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F210" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G210" s="2" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="47" t="inlineStr">
@@ -12542,11 +12909,12 @@
         <v>2</v>
       </c>
       <c r="E211" s="47" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F211" s="47" t="n">
         <v>-6</v>
       </c>
+      <c r="G211" s="2" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="47" t="inlineStr">
@@ -12568,11 +12936,12 @@
         <v>15</v>
       </c>
       <c r="E212" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F212" s="47" t="n">
         <v>-9</v>
       </c>
+      <c r="G212" s="2" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="47" t="inlineStr">
@@ -12599,6 +12968,7 @@
       <c r="F213" s="47" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G213" s="2" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="47" t="inlineStr">
@@ -12620,11 +12990,12 @@
         <v>1</v>
       </c>
       <c r="E214" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F214" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G214" s="2" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="47" t="inlineStr">
@@ -12646,11 +13017,12 @@
         <v>1</v>
       </c>
       <c r="E215" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F215" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G215" s="2" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="47" t="inlineStr">
@@ -12672,11 +13044,12 @@
         <v>4</v>
       </c>
       <c r="E216" s="47" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F216" s="47" t="n">
         <v>-12</v>
       </c>
+      <c r="G216" s="2" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="47" t="inlineStr">
@@ -12698,11 +13071,12 @@
         <v>1</v>
       </c>
       <c r="E217" s="47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F217" s="47" t="n">
         <v>-1</v>
       </c>
+      <c r="G217" s="2" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="47" t="inlineStr">
@@ -12724,11 +13098,12 @@
         <v>1</v>
       </c>
       <c r="E218" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F218" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G218" s="2" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="46" t="inlineStr">
@@ -12755,6 +13130,7 @@
       <c r="F219" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G219" s="2" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="46" t="inlineStr">
@@ -12781,6 +13157,7 @@
       <c r="F220" s="46" t="n">
         <v>3</v>
       </c>
+      <c r="G220" s="2" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="47" t="inlineStr">
@@ -12802,11 +13179,12 @@
         <v>1</v>
       </c>
       <c r="E221" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F221" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G221" s="2" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="47" t="inlineStr">
@@ -12828,11 +13206,12 @@
         <v>1</v>
       </c>
       <c r="E222" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F222" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G222" s="2" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="47" t="inlineStr">
@@ -12854,11 +13233,12 @@
         <v>2</v>
       </c>
       <c r="E223" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F223" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G223" s="2" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="47" t="inlineStr">
@@ -12880,11 +13260,12 @@
         <v>11</v>
       </c>
       <c r="E224" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F224" s="47" t="n">
         <v>-6.6</v>
       </c>
+      <c r="G224" s="2" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="46" t="inlineStr">
@@ -12911,6 +13292,7 @@
       <c r="F225" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G225" s="2" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="46" t="inlineStr">
@@ -12937,6 +13319,7 @@
       <c r="F226" s="46" t="n">
         <v>1</v>
       </c>
+      <c r="G226" s="2" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="47" t="inlineStr">
@@ -12958,11 +13341,12 @@
         <v>1</v>
       </c>
       <c r="E227" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F227" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G227" s="2" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="47" t="inlineStr">
@@ -12984,11 +13368,12 @@
         <v>2</v>
       </c>
       <c r="E228" s="47" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F228" s="47" t="n">
         <v>-6</v>
       </c>
+      <c r="G228" s="2" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="46" t="inlineStr">
@@ -13015,6 +13400,7 @@
       <c r="F229" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G229" s="2" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="46" t="inlineStr">
@@ -13041,6 +13427,7 @@
       <c r="F230" s="46" t="n">
         <v>3</v>
       </c>
+      <c r="G230" s="2" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="47" t="inlineStr">
@@ -13062,11 +13449,12 @@
         <v>2</v>
       </c>
       <c r="E231" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F231" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G231" s="2" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="47" t="inlineStr">
@@ -13088,11 +13476,12 @@
         <v>2</v>
       </c>
       <c r="E232" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F232" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G232" s="2" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="47" t="inlineStr">
@@ -13114,11 +13503,12 @@
         <v>5</v>
       </c>
       <c r="E233" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F233" s="47" t="n">
         <v>-3</v>
       </c>
+      <c r="G233" s="2" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="46" t="inlineStr">
@@ -13145,6 +13535,7 @@
       <c r="F234" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G234" s="2" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="46" t="inlineStr">
@@ -13171,6 +13562,7 @@
       <c r="F235" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G235" s="2" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="46" t="inlineStr">
@@ -13197,6 +13589,7 @@
       <c r="F236" s="46" t="n">
         <v>3</v>
       </c>
+      <c r="G236" s="2" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="47" t="inlineStr">
@@ -13218,11 +13611,12 @@
         <v>1</v>
       </c>
       <c r="E237" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F237" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G237" s="2" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="47" t="inlineStr">
@@ -13244,11 +13638,12 @@
         <v>1</v>
       </c>
       <c r="E238" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F238" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G238" s="2" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="47" t="inlineStr">
@@ -13270,11 +13665,12 @@
         <v>2</v>
       </c>
       <c r="E239" s="47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F239" s="47" t="n">
         <v>-4</v>
       </c>
+      <c r="G239" s="2" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="46" t="inlineStr">
@@ -13301,6 +13697,7 @@
       <c r="F240" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G240" s="2" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="46" t="inlineStr">
@@ -13327,6 +13724,7 @@
       <c r="F241" s="46" t="n">
         <v>3</v>
       </c>
+      <c r="G241" s="2" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="47" t="inlineStr">
@@ -13353,6 +13751,7 @@
       <c r="F242" s="47" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G242" s="2" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="47" t="inlineStr">
@@ -13374,11 +13773,12 @@
         <v>1</v>
       </c>
       <c r="E243" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F243" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G243" s="2" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="47" t="inlineStr">
@@ -13400,11 +13800,12 @@
         <v>2</v>
       </c>
       <c r="E244" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F244" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G244" s="2" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="47" t="inlineStr">
@@ -13426,11 +13827,12 @@
         <v>1</v>
       </c>
       <c r="E245" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F245" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G245" s="2" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="47" t="inlineStr">
@@ -13452,11 +13854,12 @@
         <v>1</v>
       </c>
       <c r="E246" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F246" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G246" s="2" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="46" t="inlineStr">
@@ -13483,6 +13886,7 @@
       <c r="F247" s="46" t="n">
         <v>2</v>
       </c>
+      <c r="G247" s="2" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="47" t="inlineStr">
@@ -13509,6 +13913,7 @@
       <c r="F248" s="47" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G248" s="2" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="47" t="inlineStr">
@@ -13530,11 +13935,12 @@
         <v>2</v>
       </c>
       <c r="E249" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F249" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G249" s="2" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="47" t="inlineStr">
@@ -13556,11 +13962,12 @@
         <v>1</v>
       </c>
       <c r="E250" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F250" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G250" s="2" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="47" t="inlineStr">
@@ -13582,11 +13989,12 @@
         <v>2</v>
       </c>
       <c r="E251" s="47" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F251" s="47" t="n">
         <v>-6</v>
       </c>
+      <c r="G251" s="2" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="47" t="inlineStr">
@@ -13608,11 +14016,12 @@
         <v>4</v>
       </c>
       <c r="E252" s="47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F252" s="47" t="n">
         <v>-4</v>
       </c>
+      <c r="G252" s="2" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="47" t="inlineStr">
@@ -13634,11 +14043,12 @@
         <v>5</v>
       </c>
       <c r="E253" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F253" s="47" t="n">
         <v>-3</v>
       </c>
+      <c r="G253" s="2" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="46" t="inlineStr">
@@ -13665,6 +14075,7 @@
       <c r="F254" s="46" t="n">
         <v>3</v>
       </c>
+      <c r="G254" s="2" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="47" t="inlineStr">
@@ -13691,6 +14102,7 @@
       <c r="F255" s="47" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G255" s="2" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="47" t="inlineStr">
@@ -13712,11 +14124,12 @@
         <v>1</v>
       </c>
       <c r="E256" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F256" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G256" s="2" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="47" t="inlineStr">
@@ -13738,11 +14151,12 @@
         <v>4</v>
       </c>
       <c r="E257" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F257" s="47" t="n">
         <v>-2.4</v>
       </c>
+      <c r="G257" s="2" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="47" t="inlineStr">
@@ -13764,11 +14178,12 @@
         <v>2</v>
       </c>
       <c r="E258" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F258" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G258" s="2" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="47" t="inlineStr">
@@ -13790,11 +14205,12 @@
         <v>1</v>
       </c>
       <c r="E259" s="47" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F259" s="47" t="n">
         <v>-3</v>
       </c>
+      <c r="G259" s="2" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="47" t="inlineStr">
@@ -13816,11 +14232,12 @@
         <v>11</v>
       </c>
       <c r="E260" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F260" s="47" t="n">
         <v>-6.6</v>
       </c>
+      <c r="G260" s="2" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="46" t="inlineStr">
@@ -13847,6 +14264,7 @@
       <c r="F261" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G261" s="2" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="46" t="inlineStr">
@@ -13873,6 +14291,7 @@
       <c r="F262" s="46" t="n">
         <v>2</v>
       </c>
+      <c r="G262" s="2" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="47" t="inlineStr">
@@ -13899,6 +14318,7 @@
       <c r="F263" s="47" t="n">
         <v>-0.5</v>
       </c>
+      <c r="G263" s="2" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="47" t="inlineStr">
@@ -13920,11 +14340,12 @@
         <v>1</v>
       </c>
       <c r="E264" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F264" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G264" s="2" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="47" t="inlineStr">
@@ -13946,11 +14367,12 @@
         <v>2</v>
       </c>
       <c r="E265" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F265" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G265" s="2" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="47" t="inlineStr">
@@ -13972,11 +14394,12 @@
         <v>2</v>
       </c>
       <c r="E266" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F266" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G266" s="2" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="46" t="inlineStr">
@@ -14003,6 +14426,7 @@
       <c r="F267" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G267" s="2" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="46" t="inlineStr">
@@ -14029,6 +14453,7 @@
       <c r="F268" s="46" t="n">
         <v>5</v>
       </c>
+      <c r="G268" s="2" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="46" t="inlineStr">
@@ -14055,6 +14480,7 @@
       <c r="F269" s="46" t="n">
         <v>3</v>
       </c>
+      <c r="G269" s="2" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="47" t="inlineStr">
@@ -14076,11 +14502,12 @@
         <v>1</v>
       </c>
       <c r="E270" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F270" s="47" t="n">
         <v>-0.6</v>
       </c>
+      <c r="G270" s="2" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="47" t="inlineStr">
@@ -14102,16 +14529,17 @@
         <v>2</v>
       </c>
       <c r="E271" s="47" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="F271" s="47" t="n">
         <v>-1.2</v>
       </c>
+      <c r="G271" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E39"/>
+  <autoFilter ref="A2:G39"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A42:F42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/historico/semana_319.xlsx
+++ b/data/historico/semana_319.xlsx
@@ -33,7 +33,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$G$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$H$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7181,16 +7181,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G271"/>
+  <dimension ref="A1:H271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -7205,6 +7206,7 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -7234,10 +7236,15 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>Turnos Sem Trabalhar</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>Pontuação Final</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Classificação</t>
         </is>
@@ -7261,12 +7268,15 @@
         <v>3</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7278,7 +7288,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -7290,12 +7300,15 @@
         <v>3</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7307,7 +7320,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -7319,12 +7332,15 @@
         <v>3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7336,24 +7352,27 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Bianca Afonso Narbaez</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7365,7 +7384,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -7377,12 +7396,15 @@
         <v>3</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7394,7 +7416,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -7406,12 +7428,15 @@
         <v>3</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7423,7 +7448,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -7435,12 +7460,15 @@
         <v>3</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7452,7 +7480,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Tania Maria Montania</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -7461,15 +7489,18 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7481,7 +7512,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -7493,12 +7524,15 @@
         <v>3</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7510,7 +7544,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Tania Maria Montania</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -7519,15 +7553,18 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7539,24 +7576,27 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7568,24 +7608,27 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7597,7 +7640,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -7606,15 +7649,18 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7626,7 +7672,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -7638,12 +7684,15 @@
         <v>3</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7655,7 +7704,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -7664,15 +7713,18 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7684,24 +7736,27 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7713,24 +7768,27 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7742,24 +7800,27 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7771,24 +7832,27 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>99.40000000000001</v>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7800,24 +7864,27 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7841,12 +7908,15 @@
         <v>3</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>98.3</v>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7858,24 +7928,27 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7899,12 +7972,15 @@
         <v>3</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7928,12 +8004,15 @@
         <v>3</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
         </is>
@@ -7945,55 +8024,61 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D27" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F27" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>🟢 EXCELENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Evelyn Santana Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" s="4" t="n">
         <v>90.09999999999999</v>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
         </is>
       </c>
     </row>
@@ -8003,24 +8088,27 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>86.7</v>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -8032,24 +8120,27 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -8073,12 +8164,15 @@
         <v>1</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -8090,7 +8184,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -8099,15 +8193,18 @@
         </is>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -8131,12 +8228,15 @@
         <v>4</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -8148,24 +8248,27 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Raquel Ortiz dos Santos</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D34" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F34" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E34" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="G34" s="6" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -8177,7 +8280,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -8189,12 +8292,15 @@
         <v>3</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -8206,24 +8312,27 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -8247,12 +8356,15 @@
         <v>4</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
         </is>
@@ -8276,43 +8388,49 @@
         <v>3</v>
       </c>
       <c r="E38" s="44" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F38" s="44" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="G38" s="44" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="G38" s="44" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="H38" s="44" t="inlineStr">
         <is>
           <t>🟠 ATENÇÃO</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="44" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="44" t="inlineStr">
         <is>
           <t>Mateus Falcao de Souza</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="44" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="D39" s="5" t="n">
+      <c r="D39" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="E39" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
+      <c r="E39" s="44" t="n">
+        <v>9</v>
+      </c>
+      <c r="F39" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="44" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="H39" s="44" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
         </is>
       </c>
     </row>
@@ -8324,6 +8442,7 @@
       <c r="E40" s="2" t="n"/>
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -8333,6 +8452,7 @@
       <c r="E41" s="2" t="n"/>
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="45" t="inlineStr">
@@ -8346,6 +8466,7 @@
       <c r="E42" s="2" t="n"/>
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -8370,15 +8491,24 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Peso (pontos/ocorrência)</t>
+          <t>Peso Nominal (tabela de critérios)</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
+          <t>Fator de Normalização</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Peso Efetivo (nominal × fator)</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
           <t>Pontos Aplicados</t>
         </is>
       </c>
-      <c r="G43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="46" t="inlineStr">
@@ -8403,9 +8533,14 @@
         <v>5</v>
       </c>
       <c r="F44" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="46" t="inlineStr">
@@ -8430,9 +8565,14 @@
         <v>1</v>
       </c>
       <c r="F45" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="G45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="47" t="inlineStr">
@@ -8454,12 +8594,17 @@
         <v>1</v>
       </c>
       <c r="E46" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F46" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F46" s="47" t="n">
+      <c r="H46" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="47" t="inlineStr">
@@ -8481,12 +8626,17 @@
         <v>4</v>
       </c>
       <c r="E47" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F47" s="47" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="G47" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G47" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H47" s="47" t="n">
+        <v>-1.6</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="46" t="inlineStr">
@@ -8511,9 +8661,14 @@
         <v>5</v>
       </c>
       <c r="F48" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="46" t="inlineStr">
@@ -8538,9 +8693,14 @@
         <v>1</v>
       </c>
       <c r="F49" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="G49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="47" t="inlineStr">
@@ -8562,12 +8722,17 @@
         <v>1</v>
       </c>
       <c r="E50" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F50" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F50" s="47" t="n">
+      <c r="H50" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="47" t="inlineStr">
@@ -8589,12 +8754,17 @@
         <v>1</v>
       </c>
       <c r="E51" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F51" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F51" s="47" t="n">
+      <c r="H51" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="47" t="inlineStr">
@@ -8616,12 +8786,17 @@
         <v>3</v>
       </c>
       <c r="E52" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F52" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F52" s="47" t="n">
+      <c r="H52" s="47" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="47" t="inlineStr">
@@ -8643,12 +8818,17 @@
         <v>2</v>
       </c>
       <c r="E53" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F53" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F53" s="47" t="n">
+      <c r="H53" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="47" t="inlineStr">
@@ -8670,12 +8850,17 @@
         <v>7</v>
       </c>
       <c r="E54" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F54" s="47" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="G54" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G54" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H54" s="47" t="n">
+        <v>-2.8</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="46" t="inlineStr">
@@ -8700,9 +8885,14 @@
         <v>5</v>
       </c>
       <c r="F55" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G55" s="2" t="n"/>
+      <c r="H55" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="46" t="inlineStr">
@@ -8727,9 +8917,14 @@
         <v>1</v>
       </c>
       <c r="F56" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G56" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G56" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="46" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="47" t="inlineStr">
@@ -8751,12 +8946,17 @@
         <v>1</v>
       </c>
       <c r="E57" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F57" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G57" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F57" s="47" t="n">
+      <c r="H57" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="47" t="inlineStr">
@@ -8778,12 +8978,17 @@
         <v>1</v>
       </c>
       <c r="E58" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F58" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F58" s="47" t="n">
+      <c r="H58" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="47" t="inlineStr">
@@ -8805,12 +9010,17 @@
         <v>2</v>
       </c>
       <c r="E59" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F59" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G59" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="F59" s="47" t="n">
+      <c r="H59" s="47" t="n">
         <v>-6</v>
       </c>
-      <c r="G59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="46" t="inlineStr">
@@ -8835,9 +9045,14 @@
         <v>5</v>
       </c>
       <c r="F60" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="46" t="inlineStr">
@@ -8862,9 +9077,14 @@
         <v>5</v>
       </c>
       <c r="F61" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G61" s="2" t="n"/>
+      <c r="H61" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="46" t="inlineStr">
@@ -8889,9 +9109,14 @@
         <v>1</v>
       </c>
       <c r="F62" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="G62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="47" t="inlineStr">
@@ -8913,12 +9138,17 @@
         <v>1</v>
       </c>
       <c r="E63" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F63" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G63" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F63" s="47" t="n">
+      <c r="H63" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="47" t="inlineStr">
@@ -8940,12 +9170,17 @@
         <v>2</v>
       </c>
       <c r="E64" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F64" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G64" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F64" s="47" t="n">
+      <c r="H64" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="46" t="inlineStr">
@@ -8970,9 +9205,14 @@
         <v>5</v>
       </c>
       <c r="F65" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G65" s="2" t="n"/>
+      <c r="H65" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="46" t="inlineStr">
@@ -8997,9 +9237,14 @@
         <v>1</v>
       </c>
       <c r="F66" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="G66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="47" t="inlineStr">
@@ -9021,12 +9266,17 @@
         <v>1</v>
       </c>
       <c r="E67" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F67" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G67" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F67" s="47" t="n">
+      <c r="H67" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="47" t="inlineStr">
@@ -9048,12 +9298,17 @@
         <v>3</v>
       </c>
       <c r="E68" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F68" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G68" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F68" s="47" t="n">
+      <c r="H68" s="47" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="47" t="inlineStr">
@@ -9075,12 +9330,17 @@
         <v>4</v>
       </c>
       <c r="E69" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G69" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="H69" s="47" t="n">
         <v>-8</v>
       </c>
-      <c r="G69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="47" t="inlineStr">
@@ -9102,12 +9362,17 @@
         <v>2</v>
       </c>
       <c r="E70" s="47" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F70" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G70" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="47" t="n">
         <v>-2</v>
       </c>
-      <c r="G70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="47" t="inlineStr">
@@ -9129,12 +9394,17 @@
         <v>52</v>
       </c>
       <c r="E71" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F71" s="47" t="n">
-        <v>-31.2</v>
-      </c>
-      <c r="G71" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G71" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H71" s="47" t="n">
+        <v>-20.8</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="46" t="inlineStr">
@@ -9159,9 +9429,14 @@
         <v>1</v>
       </c>
       <c r="F72" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="G72" s="2" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="47" t="inlineStr">
@@ -9186,9 +9461,14 @@
         <v>0.5</v>
       </c>
       <c r="F73" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H73" s="47" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="47" t="inlineStr">
@@ -9210,12 +9490,17 @@
         <v>2</v>
       </c>
       <c r="E74" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F74" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G74" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F74" s="47" t="n">
+      <c r="H74" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="47" t="inlineStr">
@@ -9237,12 +9522,17 @@
         <v>1</v>
       </c>
       <c r="E75" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F75" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G75" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F75" s="47" t="n">
+      <c r="H75" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="47" t="inlineStr">
@@ -9264,12 +9554,17 @@
         <v>1</v>
       </c>
       <c r="E76" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F76" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="F76" s="47" t="n">
+      <c r="H76" s="47" t="n">
         <v>-3</v>
       </c>
-      <c r="G76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="47" t="inlineStr">
@@ -9291,12 +9586,17 @@
         <v>37</v>
       </c>
       <c r="E77" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F77" s="47" t="n">
-        <v>-22.2</v>
-      </c>
-      <c r="G77" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G77" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H77" s="47" t="n">
+        <v>-14.8</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="46" t="inlineStr">
@@ -9321,9 +9621,14 @@
         <v>5</v>
       </c>
       <c r="F78" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G78" s="2" t="n"/>
+      <c r="H78" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="46" t="inlineStr">
@@ -9348,9 +9653,14 @@
         <v>5</v>
       </c>
       <c r="F79" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G79" s="2" t="n"/>
+      <c r="H79" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="46" t="inlineStr">
@@ -9377,7 +9687,12 @@
       <c r="F80" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="G80" s="2" t="n"/>
+      <c r="G80" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="47" t="inlineStr">
@@ -9402,9 +9717,14 @@
         <v>0.5</v>
       </c>
       <c r="F81" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H81" s="47" t="n">
         <v>-1</v>
       </c>
-      <c r="G81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="47" t="inlineStr">
@@ -9426,12 +9746,17 @@
         <v>2</v>
       </c>
       <c r="E82" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F82" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G82" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F82" s="47" t="n">
+      <c r="H82" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="47" t="inlineStr">
@@ -9453,12 +9778,17 @@
         <v>2</v>
       </c>
       <c r="E83" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F83" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G83" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F83" s="47" t="n">
+      <c r="H83" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="47" t="inlineStr">
@@ -9480,12 +9810,17 @@
         <v>1</v>
       </c>
       <c r="E84" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F84" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G84" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F84" s="47" t="n">
+      <c r="H84" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="46" t="inlineStr">
@@ -9510,9 +9845,14 @@
         <v>5</v>
       </c>
       <c r="F85" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G85" s="2" t="n"/>
+      <c r="H85" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="46" t="inlineStr">
@@ -9537,9 +9877,14 @@
         <v>1</v>
       </c>
       <c r="F86" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G86" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G86" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="46" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="47" t="inlineStr">
@@ -9564,9 +9909,14 @@
         <v>0.5</v>
       </c>
       <c r="F87" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H87" s="47" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="47" t="inlineStr">
@@ -9588,12 +9938,17 @@
         <v>1</v>
       </c>
       <c r="E88" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F88" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G88" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F88" s="47" t="n">
+      <c r="H88" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="47" t="inlineStr">
@@ -9615,12 +9970,17 @@
         <v>1</v>
       </c>
       <c r="E89" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F89" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G89" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F89" s="47" t="n">
+      <c r="H89" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="47" t="inlineStr">
@@ -9642,12 +10002,17 @@
         <v>4</v>
       </c>
       <c r="E90" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F90" s="47" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="G90" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G90" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H90" s="47" t="n">
+        <v>-1.6</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="46" t="inlineStr">
@@ -9674,7 +10039,12 @@
       <c r="F91" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="G91" s="2" t="n"/>
+      <c r="G91" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="47" t="inlineStr">
@@ -9699,9 +10069,14 @@
         <v>0.5</v>
       </c>
       <c r="F92" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H92" s="47" t="n">
         <v>-1</v>
       </c>
-      <c r="G92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="47" t="inlineStr">
@@ -9723,12 +10098,17 @@
         <v>1</v>
       </c>
       <c r="E93" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F93" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G93" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F93" s="47" t="n">
+      <c r="H93" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="47" t="inlineStr">
@@ -9750,12 +10130,17 @@
         <v>1</v>
       </c>
       <c r="E94" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F94" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G94" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F94" s="47" t="n">
+      <c r="H94" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="47" t="inlineStr">
@@ -9777,12 +10162,17 @@
         <v>2</v>
       </c>
       <c r="E95" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F95" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G95" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F95" s="47" t="n">
+      <c r="H95" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G95" s="2" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="47" t="inlineStr">
@@ -9804,12 +10194,17 @@
         <v>1</v>
       </c>
       <c r="E96" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F96" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G96" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F96" s="47" t="n">
+      <c r="H96" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="47" t="inlineStr">
@@ -9831,12 +10226,17 @@
         <v>1</v>
       </c>
       <c r="E97" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F97" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G97" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="F97" s="47" t="n">
+      <c r="H97" s="47" t="n">
         <v>-3</v>
       </c>
-      <c r="G97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="47" t="inlineStr">
@@ -9858,12 +10258,17 @@
         <v>2</v>
       </c>
       <c r="E98" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F98" s="47" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="G98" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G98" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H98" s="47" t="n">
+        <v>-0.8</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="46" t="inlineStr">
@@ -9888,9 +10293,14 @@
         <v>5</v>
       </c>
       <c r="F99" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G99" s="2" t="n"/>
+      <c r="H99" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="46" t="inlineStr">
@@ -9917,7 +10327,12 @@
       <c r="F100" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="G100" s="2" t="n"/>
+      <c r="G100" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" s="46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="47" t="inlineStr">
@@ -9942,9 +10357,14 @@
         <v>0.5</v>
       </c>
       <c r="F101" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H101" s="47" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="47" t="inlineStr">
@@ -9966,12 +10386,17 @@
         <v>1</v>
       </c>
       <c r="E102" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F102" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G102" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F102" s="47" t="n">
+      <c r="H102" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G102" s="2" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="47" t="inlineStr">
@@ -9993,12 +10418,17 @@
         <v>1</v>
       </c>
       <c r="E103" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F103" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G103" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F103" s="47" t="n">
+      <c r="H103" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G103" s="2" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="47" t="inlineStr">
@@ -10020,12 +10450,17 @@
         <v>2</v>
       </c>
       <c r="E104" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F104" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G104" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F104" s="47" t="n">
+      <c r="H104" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="47" t="inlineStr">
@@ -10047,12 +10482,17 @@
         <v>4</v>
       </c>
       <c r="E105" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F105" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G105" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="F105" s="47" t="n">
+      <c r="H105" s="47" t="n">
         <v>-12</v>
       </c>
-      <c r="G105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="46" t="inlineStr">
@@ -10077,9 +10517,14 @@
         <v>5</v>
       </c>
       <c r="F106" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G106" s="2" t="n"/>
+      <c r="H106" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="46" t="inlineStr">
@@ -10104,9 +10549,14 @@
         <v>5</v>
       </c>
       <c r="F107" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G107" s="2" t="n"/>
+      <c r="H107" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="46" t="inlineStr">
@@ -10131,9 +10581,14 @@
         <v>1</v>
       </c>
       <c r="F108" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="G108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="47" t="inlineStr">
@@ -10155,12 +10610,17 @@
         <v>1</v>
       </c>
       <c r="E109" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F109" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G109" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F109" s="47" t="n">
+      <c r="H109" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G109" s="2" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="47" t="inlineStr">
@@ -10182,12 +10642,17 @@
         <v>1</v>
       </c>
       <c r="E110" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F110" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G110" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F110" s="47" t="n">
+      <c r="H110" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="47" t="inlineStr">
@@ -10209,12 +10674,17 @@
         <v>1</v>
       </c>
       <c r="E111" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F111" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G111" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F111" s="47" t="n">
+      <c r="H111" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G111" s="2" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="46" t="inlineStr">
@@ -10239,9 +10709,14 @@
         <v>5</v>
       </c>
       <c r="F112" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G112" s="2" t="n"/>
+      <c r="H112" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="46" t="inlineStr">
@@ -10266,9 +10741,14 @@
         <v>1</v>
       </c>
       <c r="F113" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G113" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G113" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" s="46" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="47" t="inlineStr">
@@ -10293,9 +10773,14 @@
         <v>0.5</v>
       </c>
       <c r="F114" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H114" s="47" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G114" s="2" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="47" t="inlineStr">
@@ -10317,12 +10802,17 @@
         <v>2</v>
       </c>
       <c r="E115" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F115" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G115" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F115" s="47" t="n">
+      <c r="H115" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G115" s="2" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="47" t="inlineStr">
@@ -10344,12 +10834,17 @@
         <v>2</v>
       </c>
       <c r="E116" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F116" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G116" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F116" s="47" t="n">
+      <c r="H116" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G116" s="2" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="47" t="inlineStr">
@@ -10371,12 +10866,17 @@
         <v>2</v>
       </c>
       <c r="E117" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F117" s="47" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="G117" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G117" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H117" s="47" t="n">
+        <v>-0.8</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="46" t="inlineStr">
@@ -10401,9 +10901,14 @@
         <v>5</v>
       </c>
       <c r="F118" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G118" s="2" t="n"/>
+      <c r="H118" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="46" t="inlineStr">
@@ -10428,9 +10933,14 @@
         <v>5</v>
       </c>
       <c r="F119" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G119" s="2" t="n"/>
+      <c r="H119" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="46" t="inlineStr">
@@ -10455,9 +10965,14 @@
         <v>1</v>
       </c>
       <c r="F120" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="G120" s="2" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="47" t="inlineStr">
@@ -10479,12 +10994,17 @@
         <v>1</v>
       </c>
       <c r="E121" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F121" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G121" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F121" s="47" t="n">
+      <c r="H121" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G121" s="2" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="47" t="inlineStr">
@@ -10506,12 +11026,17 @@
         <v>1</v>
       </c>
       <c r="E122" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F122" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G122" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F122" s="47" t="n">
+      <c r="H122" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G122" s="2" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="47" t="inlineStr">
@@ -10533,12 +11058,17 @@
         <v>1</v>
       </c>
       <c r="E123" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F123" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G123" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F123" s="47" t="n">
+      <c r="H123" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G123" s="2" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="46" t="inlineStr">
@@ -10563,9 +11093,14 @@
         <v>5</v>
       </c>
       <c r="F124" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G124" s="2" t="n"/>
+      <c r="H124" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="46" t="inlineStr">
@@ -10590,9 +11125,14 @@
         <v>3</v>
       </c>
       <c r="F125" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="G125" s="2" t="n"/>
+      <c r="H125" s="46" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="46" t="inlineStr">
@@ -10617,9 +11157,14 @@
         <v>1</v>
       </c>
       <c r="F126" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G126" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G126" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" s="46" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="47" t="inlineStr">
@@ -10644,9 +11189,14 @@
         <v>0.5</v>
       </c>
       <c r="F127" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H127" s="47" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G127" s="2" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="47" t="inlineStr">
@@ -10668,12 +11218,17 @@
         <v>1</v>
       </c>
       <c r="E128" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F128" s="47" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G128" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G128" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H128" s="47" t="n">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="46" t="inlineStr">
@@ -10698,9 +11253,14 @@
         <v>5</v>
       </c>
       <c r="F129" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G129" s="2" t="n"/>
+      <c r="H129" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="46" t="inlineStr">
@@ -10725,9 +11285,14 @@
         <v>1</v>
       </c>
       <c r="F130" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="G130" s="2" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="47" t="inlineStr">
@@ -10749,12 +11314,17 @@
         <v>1</v>
       </c>
       <c r="E131" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F131" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G131" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F131" s="47" t="n">
+      <c r="H131" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G131" s="2" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="47" t="inlineStr">
@@ -10776,12 +11346,17 @@
         <v>1</v>
       </c>
       <c r="E132" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F132" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G132" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F132" s="47" t="n">
+      <c r="H132" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G132" s="2" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="47" t="inlineStr">
@@ -10803,12 +11378,17 @@
         <v>2</v>
       </c>
       <c r="E133" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F133" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G133" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F133" s="47" t="n">
+      <c r="H133" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G133" s="2" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="47" t="inlineStr">
@@ -10830,12 +11410,17 @@
         <v>2</v>
       </c>
       <c r="E134" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F134" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G134" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="H134" s="47" t="n">
         <v>-4</v>
       </c>
-      <c r="G134" s="2" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="47" t="inlineStr">
@@ -10857,12 +11442,17 @@
         <v>9</v>
       </c>
       <c r="E135" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F135" s="47" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="G135" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G135" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H135" s="47" t="n">
+        <v>-3.6</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="46" t="inlineStr">
@@ -10887,9 +11477,14 @@
         <v>5</v>
       </c>
       <c r="F136" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G136" s="2" t="n"/>
+      <c r="H136" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="46" t="inlineStr">
@@ -10914,9 +11509,14 @@
         <v>1</v>
       </c>
       <c r="F137" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="G137" s="2" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="47" t="inlineStr">
@@ -10938,12 +11538,17 @@
         <v>2</v>
       </c>
       <c r="E138" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F138" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G138" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F138" s="47" t="n">
+      <c r="H138" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G138" s="2" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="47" t="inlineStr">
@@ -10965,12 +11570,17 @@
         <v>1</v>
       </c>
       <c r="E139" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F139" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G139" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F139" s="47" t="n">
+      <c r="H139" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G139" s="2" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="47" t="inlineStr">
@@ -10992,12 +11602,17 @@
         <v>14</v>
       </c>
       <c r="E140" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F140" s="47" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="G140" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G140" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H140" s="47" t="n">
+        <v>-5.6</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="46" t="inlineStr">
@@ -11024,7 +11639,12 @@
       <c r="F141" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="G141" s="2" t="n"/>
+      <c r="G141" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" s="46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="47" t="inlineStr">
@@ -11049,9 +11669,14 @@
         <v>0.5</v>
       </c>
       <c r="F142" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H142" s="47" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G142" s="2" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="47" t="inlineStr">
@@ -11073,12 +11698,17 @@
         <v>1</v>
       </c>
       <c r="E143" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F143" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G143" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F143" s="47" t="n">
+      <c r="H143" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G143" s="2" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="47" t="inlineStr">
@@ -11100,12 +11730,17 @@
         <v>2</v>
       </c>
       <c r="E144" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F144" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G144" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F144" s="47" t="n">
+      <c r="H144" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G144" s="2" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="47" t="inlineStr">
@@ -11127,12 +11762,17 @@
         <v>3</v>
       </c>
       <c r="E145" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F145" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G145" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="F145" s="47" t="n">
+      <c r="H145" s="47" t="n">
         <v>-9</v>
       </c>
-      <c r="G145" s="2" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="47" t="inlineStr">
@@ -11154,12 +11794,17 @@
         <v>8</v>
       </c>
       <c r="E146" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F146" s="47" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="G146" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G146" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H146" s="47" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="46" t="inlineStr">
@@ -11184,9 +11829,14 @@
         <v>5</v>
       </c>
       <c r="F147" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G147" s="2" t="n"/>
+      <c r="H147" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="46" t="inlineStr">
@@ -11211,9 +11861,14 @@
         <v>1</v>
       </c>
       <c r="F148" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="G148" s="2" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="47" t="inlineStr">
@@ -11235,12 +11890,17 @@
         <v>2</v>
       </c>
       <c r="E149" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F149" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G149" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F149" s="47" t="n">
+      <c r="H149" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G149" s="2" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="47" t="inlineStr">
@@ -11262,12 +11922,17 @@
         <v>2</v>
       </c>
       <c r="E150" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F150" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G150" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F150" s="47" t="n">
+      <c r="H150" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G150" s="2" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="47" t="inlineStr">
@@ -11289,12 +11954,17 @@
         <v>2</v>
       </c>
       <c r="E151" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F151" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G151" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F151" s="47" t="n">
+      <c r="H151" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G151" s="2" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="47" t="inlineStr">
@@ -11316,12 +11986,17 @@
         <v>37</v>
       </c>
       <c r="E152" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F152" s="47" t="n">
-        <v>-22.2</v>
-      </c>
-      <c r="G152" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G152" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H152" s="47" t="n">
+        <v>-14.8</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="46" t="inlineStr">
@@ -11346,9 +12021,14 @@
         <v>5</v>
       </c>
       <c r="F153" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G153" s="2" t="n"/>
+      <c r="H153" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="46" t="inlineStr">
@@ -11373,9 +12053,14 @@
         <v>1</v>
       </c>
       <c r="F154" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G154" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G154" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" s="46" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="47" t="inlineStr">
@@ -11400,9 +12085,14 @@
         <v>0.5</v>
       </c>
       <c r="F155" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H155" s="47" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G155" s="2" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="47" t="inlineStr">
@@ -11424,12 +12114,17 @@
         <v>1</v>
       </c>
       <c r="E156" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F156" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G156" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F156" s="47" t="n">
+      <c r="H156" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G156" s="2" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="47" t="inlineStr">
@@ -11451,12 +12146,17 @@
         <v>2</v>
       </c>
       <c r="E157" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F157" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G157" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F157" s="47" t="n">
+      <c r="H157" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G157" s="2" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="47" t="inlineStr">
@@ -11478,12 +12178,17 @@
         <v>3</v>
       </c>
       <c r="E158" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F158" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G158" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F158" s="47" t="n">
+      <c r="H158" s="47" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G158" s="2" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="47" t="inlineStr">
@@ -11505,12 +12210,17 @@
         <v>1</v>
       </c>
       <c r="E159" s="47" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F159" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G159" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" s="47" t="n">
         <v>-1</v>
       </c>
-      <c r="G159" s="2" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="47" t="inlineStr">
@@ -11532,12 +12242,17 @@
         <v>6</v>
       </c>
       <c r="E160" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F160" s="47" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="G160" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G160" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H160" s="47" t="n">
+        <v>-2.4</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="46" t="inlineStr">
@@ -11562,9 +12277,14 @@
         <v>5</v>
       </c>
       <c r="F161" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G161" s="2" t="n"/>
+      <c r="H161" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="46" t="inlineStr">
@@ -11589,9 +12309,14 @@
         <v>5</v>
       </c>
       <c r="F162" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G162" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G162" s="2" t="n"/>
+      <c r="H162" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="46" t="inlineStr">
@@ -11618,7 +12343,12 @@
       <c r="F163" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="G163" s="2" t="n"/>
+      <c r="G163" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H163" s="46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="47" t="inlineStr">
@@ -11640,12 +12370,17 @@
         <v>1</v>
       </c>
       <c r="E164" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F164" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G164" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F164" s="47" t="n">
+      <c r="H164" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G164" s="2" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="47" t="inlineStr">
@@ -11667,12 +12402,17 @@
         <v>1</v>
       </c>
       <c r="E165" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F165" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G165" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F165" s="47" t="n">
+      <c r="H165" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G165" s="2" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="46" t="inlineStr">
@@ -11697,9 +12437,14 @@
         <v>1</v>
       </c>
       <c r="F166" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G166" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G166" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" s="46" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="47" t="inlineStr">
@@ -11724,9 +12469,14 @@
         <v>0.5</v>
       </c>
       <c r="F167" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G167" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H167" s="47" t="n">
         <v>-1</v>
       </c>
-      <c r="G167" s="2" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="47" t="inlineStr">
@@ -11748,12 +12498,17 @@
         <v>2</v>
       </c>
       <c r="E168" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F168" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G168" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F168" s="47" t="n">
+      <c r="H168" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G168" s="2" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="47" t="inlineStr">
@@ -11775,12 +12530,17 @@
         <v>1</v>
       </c>
       <c r="E169" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F169" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G169" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F169" s="47" t="n">
+      <c r="H169" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G169" s="2" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="47" t="inlineStr">
@@ -11802,12 +12562,17 @@
         <v>1</v>
       </c>
       <c r="E170" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F170" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G170" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F170" s="47" t="n">
+      <c r="H170" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G170" s="2" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="47" t="inlineStr">
@@ -11829,12 +12594,17 @@
         <v>1</v>
       </c>
       <c r="E171" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F171" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G171" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F171" s="47" t="n">
+      <c r="H171" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G171" s="2" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="47" t="inlineStr">
@@ -11856,12 +12626,17 @@
         <v>1</v>
       </c>
       <c r="E172" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F172" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G172" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="F172" s="47" t="n">
+      <c r="H172" s="47" t="n">
         <v>-3</v>
       </c>
-      <c r="G172" s="2" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="47" t="inlineStr">
@@ -11883,12 +12658,17 @@
         <v>79</v>
       </c>
       <c r="E173" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F173" s="47" t="n">
-        <v>-47.4</v>
-      </c>
-      <c r="G173" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G173" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H173" s="47" t="n">
+        <v>-31.6</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="46" t="inlineStr">
@@ -11915,7 +12695,12 @@
       <c r="F174" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="G174" s="2" t="n"/>
+      <c r="G174" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" s="46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="47" t="inlineStr">
@@ -11940,9 +12725,14 @@
         <v>0.5</v>
       </c>
       <c r="F175" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G175" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H175" s="47" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G175" s="2" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="47" t="inlineStr">
@@ -11964,12 +12754,17 @@
         <v>2</v>
       </c>
       <c r="E176" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F176" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G176" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F176" s="47" t="n">
+      <c r="H176" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G176" s="2" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="47" t="inlineStr">
@@ -11991,12 +12786,17 @@
         <v>2</v>
       </c>
       <c r="E177" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F177" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G177" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F177" s="47" t="n">
+      <c r="H177" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G177" s="2" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="47" t="inlineStr">
@@ -12018,12 +12818,17 @@
         <v>1</v>
       </c>
       <c r="E178" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F178" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G178" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F178" s="47" t="n">
+      <c r="H178" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G178" s="2" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="47" t="inlineStr">
@@ -12045,12 +12850,17 @@
         <v>1</v>
       </c>
       <c r="E179" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F179" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G179" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="F179" s="47" t="n">
+      <c r="H179" s="47" t="n">
         <v>-3</v>
       </c>
-      <c r="G179" s="2" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="47" t="inlineStr">
@@ -12072,12 +12882,17 @@
         <v>17</v>
       </c>
       <c r="E180" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F180" s="47" t="n">
-        <v>-10.2</v>
-      </c>
-      <c r="G180" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G180" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H180" s="47" t="n">
+        <v>-6.8</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="46" t="inlineStr">
@@ -12102,9 +12917,14 @@
         <v>5</v>
       </c>
       <c r="F181" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G181" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G181" s="2" t="n"/>
+      <c r="H181" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="46" t="inlineStr">
@@ -12129,9 +12949,14 @@
         <v>5</v>
       </c>
       <c r="F182" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G182" s="2" t="n"/>
+      <c r="H182" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="46" t="inlineStr">
@@ -12158,7 +12983,12 @@
       <c r="F183" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="G183" s="2" t="n"/>
+      <c r="G183" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H183" s="46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="47" t="inlineStr">
@@ -12183,9 +13013,14 @@
         <v>0.5</v>
       </c>
       <c r="F184" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H184" s="47" t="n">
         <v>-1</v>
       </c>
-      <c r="G184" s="2" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="47" t="inlineStr">
@@ -12207,12 +13042,17 @@
         <v>1</v>
       </c>
       <c r="E185" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F185" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G185" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F185" s="47" t="n">
+      <c r="H185" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G185" s="2" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="47" t="inlineStr">
@@ -12234,12 +13074,17 @@
         <v>2</v>
       </c>
       <c r="E186" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F186" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G186" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F186" s="47" t="n">
+      <c r="H186" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G186" s="2" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="47" t="inlineStr">
@@ -12261,12 +13106,17 @@
         <v>1</v>
       </c>
       <c r="E187" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F187" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G187" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F187" s="47" t="n">
+      <c r="H187" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G187" s="2" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="46" t="inlineStr">
@@ -12291,9 +13141,14 @@
         <v>5</v>
       </c>
       <c r="F188" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G188" s="2" t="n"/>
+      <c r="H188" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="46" t="inlineStr">
@@ -12318,9 +13173,14 @@
         <v>1</v>
       </c>
       <c r="F189" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H189" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="G189" s="2" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="47" t="inlineStr">
@@ -12342,12 +13202,17 @@
         <v>2</v>
       </c>
       <c r="E190" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F190" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G190" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F190" s="47" t="n">
+      <c r="H190" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G190" s="2" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="47" t="inlineStr">
@@ -12369,12 +13234,17 @@
         <v>2</v>
       </c>
       <c r="E191" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F191" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G191" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F191" s="47" t="n">
+      <c r="H191" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G191" s="2" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="47" t="inlineStr">
@@ -12396,12 +13266,17 @@
         <v>50</v>
       </c>
       <c r="E192" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F192" s="47" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G192" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G192" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H192" s="47" t="n">
+        <v>-20</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="46" t="inlineStr">
@@ -12426,9 +13301,14 @@
         <v>5</v>
       </c>
       <c r="F193" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G193" s="2" t="n"/>
+      <c r="H193" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="46" t="inlineStr">
@@ -12453,9 +13333,14 @@
         <v>1</v>
       </c>
       <c r="F194" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G194" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G194" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" s="46" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="47" t="inlineStr">
@@ -12480,9 +13365,14 @@
         <v>0.5</v>
       </c>
       <c r="F195" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H195" s="47" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G195" s="2" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="47" t="inlineStr">
@@ -12504,12 +13394,17 @@
         <v>3</v>
       </c>
       <c r="E196" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F196" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G196" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F196" s="47" t="n">
+      <c r="H196" s="47" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G196" s="2" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="47" t="inlineStr">
@@ -12531,12 +13426,17 @@
         <v>2</v>
       </c>
       <c r="E197" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F197" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G197" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F197" s="47" t="n">
+      <c r="H197" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G197" s="2" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="47" t="inlineStr">
@@ -12558,12 +13458,17 @@
         <v>2</v>
       </c>
       <c r="E198" s="47" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F198" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G198" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" s="47" t="n">
         <v>-2</v>
       </c>
-      <c r="G198" s="2" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="47" t="inlineStr">
@@ -12585,12 +13490,17 @@
         <v>32</v>
       </c>
       <c r="E199" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F199" s="47" t="n">
-        <v>-19.2</v>
-      </c>
-      <c r="G199" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G199" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H199" s="47" t="n">
+        <v>-12.8</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="46" t="inlineStr">
@@ -12615,9 +13525,14 @@
         <v>5</v>
       </c>
       <c r="F200" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G200" s="2" t="n"/>
+      <c r="H200" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="46" t="inlineStr">
@@ -12642,9 +13557,14 @@
         <v>5</v>
       </c>
       <c r="F201" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G201" s="2" t="n"/>
+      <c r="H201" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="46" t="inlineStr">
@@ -12669,9 +13589,14 @@
         <v>1</v>
       </c>
       <c r="F202" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G202" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G202" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" s="46" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="47" t="inlineStr">
@@ -12696,9 +13621,14 @@
         <v>0.5</v>
       </c>
       <c r="F203" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H203" s="47" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G203" s="2" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="47" t="inlineStr">
@@ -12720,12 +13650,17 @@
         <v>1</v>
       </c>
       <c r="E204" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F204" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G204" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F204" s="47" t="n">
+      <c r="H204" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G204" s="2" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="47" t="inlineStr">
@@ -12747,12 +13682,17 @@
         <v>1</v>
       </c>
       <c r="E205" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F205" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G205" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F205" s="47" t="n">
+      <c r="H205" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G205" s="2" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="47" t="inlineStr">
@@ -12774,12 +13714,17 @@
         <v>1</v>
       </c>
       <c r="E206" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F206" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G206" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F206" s="47" t="n">
+      <c r="H206" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G206" s="2" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="47" t="inlineStr">
@@ -12801,12 +13746,17 @@
         <v>1</v>
       </c>
       <c r="E207" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F207" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G207" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F207" s="47" t="n">
+      <c r="H207" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G207" s="2" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="46" t="inlineStr">
@@ -12833,7 +13783,12 @@
       <c r="F208" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="G208" s="2" t="n"/>
+      <c r="G208" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H208" s="46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="47" t="inlineStr">
@@ -12855,12 +13810,17 @@
         <v>1</v>
       </c>
       <c r="E209" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F209" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G209" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F209" s="47" t="n">
+      <c r="H209" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G209" s="2" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="47" t="inlineStr">
@@ -12882,12 +13842,17 @@
         <v>1</v>
       </c>
       <c r="E210" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F210" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G210" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F210" s="47" t="n">
+      <c r="H210" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G210" s="2" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="47" t="inlineStr">
@@ -12909,12 +13874,17 @@
         <v>2</v>
       </c>
       <c r="E211" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F211" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G211" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="F211" s="47" t="n">
+      <c r="H211" s="47" t="n">
         <v>-6</v>
       </c>
-      <c r="G211" s="2" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="47" t="inlineStr">
@@ -12936,12 +13906,17 @@
         <v>15</v>
       </c>
       <c r="E212" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F212" s="47" t="n">
-        <v>-9</v>
-      </c>
-      <c r="G212" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G212" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H212" s="47" t="n">
+        <v>-6</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="47" t="inlineStr">
@@ -12966,9 +13941,14 @@
         <v>0.5</v>
       </c>
       <c r="F213" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H213" s="47" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G213" s="2" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="47" t="inlineStr">
@@ -12990,12 +13970,17 @@
         <v>1</v>
       </c>
       <c r="E214" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F214" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G214" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F214" s="47" t="n">
+      <c r="H214" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G214" s="2" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="47" t="inlineStr">
@@ -13017,12 +14002,17 @@
         <v>1</v>
       </c>
       <c r="E215" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F215" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G215" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F215" s="47" t="n">
+      <c r="H215" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G215" s="2" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="47" t="inlineStr">
@@ -13044,12 +14034,17 @@
         <v>4</v>
       </c>
       <c r="E216" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F216" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G216" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="F216" s="47" t="n">
+      <c r="H216" s="47" t="n">
         <v>-12</v>
       </c>
-      <c r="G216" s="2" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="47" t="inlineStr">
@@ -13071,12 +14066,17 @@
         <v>1</v>
       </c>
       <c r="E217" s="47" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F217" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G217" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H217" s="47" t="n">
         <v>-1</v>
       </c>
-      <c r="G217" s="2" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="47" t="inlineStr">
@@ -13098,12 +14098,17 @@
         <v>1</v>
       </c>
       <c r="E218" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F218" s="47" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G218" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G218" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H218" s="47" t="n">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="46" t="inlineStr">
@@ -13128,9 +14133,14 @@
         <v>5</v>
       </c>
       <c r="F219" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G219" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G219" s="2" t="n"/>
+      <c r="H219" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="46" t="inlineStr">
@@ -13155,9 +14165,14 @@
         <v>1</v>
       </c>
       <c r="F220" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G220" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H220" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="G220" s="2" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="47" t="inlineStr">
@@ -13179,12 +14194,17 @@
         <v>1</v>
       </c>
       <c r="E221" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F221" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G221" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F221" s="47" t="n">
+      <c r="H221" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G221" s="2" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="47" t="inlineStr">
@@ -13206,12 +14226,17 @@
         <v>1</v>
       </c>
       <c r="E222" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F222" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G222" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F222" s="47" t="n">
+      <c r="H222" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G222" s="2" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="47" t="inlineStr">
@@ -13233,12 +14258,17 @@
         <v>2</v>
       </c>
       <c r="E223" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F223" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G223" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F223" s="47" t="n">
+      <c r="H223" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G223" s="2" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="47" t="inlineStr">
@@ -13260,12 +14290,17 @@
         <v>11</v>
       </c>
       <c r="E224" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F224" s="47" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="G224" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G224" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H224" s="47" t="n">
+        <v>-4.4</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="46" t="inlineStr">
@@ -13290,9 +14325,14 @@
         <v>5</v>
       </c>
       <c r="F225" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G225" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G225" s="2" t="n"/>
+      <c r="H225" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="46" t="inlineStr">
@@ -13319,7 +14359,12 @@
       <c r="F226" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="G226" s="2" t="n"/>
+      <c r="G226" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H226" s="46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="47" t="inlineStr">
@@ -13341,12 +14386,17 @@
         <v>1</v>
       </c>
       <c r="E227" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F227" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G227" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F227" s="47" t="n">
+      <c r="H227" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G227" s="2" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="47" t="inlineStr">
@@ -13368,12 +14418,17 @@
         <v>2</v>
       </c>
       <c r="E228" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F228" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G228" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="F228" s="47" t="n">
+      <c r="H228" s="47" t="n">
         <v>-6</v>
       </c>
-      <c r="G228" s="2" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="46" t="inlineStr">
@@ -13398,9 +14453,14 @@
         <v>5</v>
       </c>
       <c r="F229" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G229" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G229" s="2" t="n"/>
+      <c r="H229" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="46" t="inlineStr">
@@ -13425,9 +14485,14 @@
         <v>1</v>
       </c>
       <c r="F230" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G230" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H230" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="G230" s="2" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="47" t="inlineStr">
@@ -13449,12 +14514,17 @@
         <v>2</v>
       </c>
       <c r="E231" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F231" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G231" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F231" s="47" t="n">
+      <c r="H231" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G231" s="2" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="47" t="inlineStr">
@@ -13476,12 +14546,17 @@
         <v>2</v>
       </c>
       <c r="E232" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F232" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G232" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F232" s="47" t="n">
+      <c r="H232" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G232" s="2" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="47" t="inlineStr">
@@ -13503,12 +14578,17 @@
         <v>5</v>
       </c>
       <c r="E233" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F233" s="47" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G233" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G233" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H233" s="47" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="46" t="inlineStr">
@@ -13533,9 +14613,14 @@
         <v>5</v>
       </c>
       <c r="F234" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G234" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G234" s="2" t="n"/>
+      <c r="H234" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="46" t="inlineStr">
@@ -13560,9 +14645,14 @@
         <v>5</v>
       </c>
       <c r="F235" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G235" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G235" s="2" t="n"/>
+      <c r="H235" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="46" t="inlineStr">
@@ -13587,9 +14677,14 @@
         <v>1</v>
       </c>
       <c r="F236" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G236" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H236" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="G236" s="2" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="47" t="inlineStr">
@@ -13611,12 +14706,17 @@
         <v>1</v>
       </c>
       <c r="E237" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F237" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G237" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F237" s="47" t="n">
+      <c r="H237" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G237" s="2" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="47" t="inlineStr">
@@ -13638,12 +14738,17 @@
         <v>1</v>
       </c>
       <c r="E238" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F238" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G238" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F238" s="47" t="n">
+      <c r="H238" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G238" s="2" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="47" t="inlineStr">
@@ -13665,12 +14770,17 @@
         <v>2</v>
       </c>
       <c r="E239" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F239" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G239" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="H239" s="47" t="n">
         <v>-4</v>
       </c>
-      <c r="G239" s="2" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="46" t="inlineStr">
@@ -13695,9 +14805,14 @@
         <v>5</v>
       </c>
       <c r="F240" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G240" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G240" s="2" t="n"/>
+      <c r="H240" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="46" t="inlineStr">
@@ -13722,9 +14837,14 @@
         <v>1</v>
       </c>
       <c r="F241" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G241" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H241" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="G241" s="2" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="47" t="inlineStr">
@@ -13749,9 +14869,14 @@
         <v>0.5</v>
       </c>
       <c r="F242" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G242" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H242" s="47" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G242" s="2" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="47" t="inlineStr">
@@ -13773,12 +14898,17 @@
         <v>1</v>
       </c>
       <c r="E243" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F243" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G243" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F243" s="47" t="n">
+      <c r="H243" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G243" s="2" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="47" t="inlineStr">
@@ -13800,12 +14930,17 @@
         <v>2</v>
       </c>
       <c r="E244" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F244" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G244" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F244" s="47" t="n">
+      <c r="H244" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G244" s="2" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="47" t="inlineStr">
@@ -13827,12 +14962,17 @@
         <v>1</v>
       </c>
       <c r="E245" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F245" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G245" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F245" s="47" t="n">
+      <c r="H245" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G245" s="2" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="47" t="inlineStr">
@@ -13854,12 +14994,17 @@
         <v>1</v>
       </c>
       <c r="E246" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F246" s="47" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="G246" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G246" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H246" s="47" t="n">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="46" t="inlineStr">
@@ -13884,9 +15029,14 @@
         <v>1</v>
       </c>
       <c r="F247" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G247" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G247" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H247" s="46" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="47" t="inlineStr">
@@ -13911,9 +15061,14 @@
         <v>0.5</v>
       </c>
       <c r="F248" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G248" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H248" s="47" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G248" s="2" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="47" t="inlineStr">
@@ -13935,12 +15090,17 @@
         <v>2</v>
       </c>
       <c r="E249" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F249" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G249" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F249" s="47" t="n">
+      <c r="H249" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G249" s="2" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="47" t="inlineStr">
@@ -13962,12 +15122,17 @@
         <v>1</v>
       </c>
       <c r="E250" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F250" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G250" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F250" s="47" t="n">
+      <c r="H250" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G250" s="2" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="47" t="inlineStr">
@@ -13989,12 +15154,17 @@
         <v>2</v>
       </c>
       <c r="E251" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F251" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G251" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="F251" s="47" t="n">
+      <c r="H251" s="47" t="n">
         <v>-6</v>
       </c>
-      <c r="G251" s="2" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="47" t="inlineStr">
@@ -14016,12 +15186,17 @@
         <v>4</v>
       </c>
       <c r="E252" s="47" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F252" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G252" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H252" s="47" t="n">
         <v>-4</v>
       </c>
-      <c r="G252" s="2" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="47" t="inlineStr">
@@ -14043,12 +15218,17 @@
         <v>5</v>
       </c>
       <c r="E253" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F253" s="47" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G253" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G253" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H253" s="47" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="46" t="inlineStr">
@@ -14073,9 +15253,14 @@
         <v>1</v>
       </c>
       <c r="F254" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G254" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H254" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="G254" s="2" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="47" t="inlineStr">
@@ -14100,9 +15285,14 @@
         <v>0.5</v>
       </c>
       <c r="F255" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G255" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H255" s="47" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G255" s="2" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="47" t="inlineStr">
@@ -14124,12 +15314,17 @@
         <v>1</v>
       </c>
       <c r="E256" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F256" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G256" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F256" s="47" t="n">
+      <c r="H256" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G256" s="2" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="47" t="inlineStr">
@@ -14151,12 +15346,17 @@
         <v>4</v>
       </c>
       <c r="E257" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F257" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G257" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F257" s="47" t="n">
+      <c r="H257" s="47" t="n">
         <v>-2.4</v>
       </c>
-      <c r="G257" s="2" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="47" t="inlineStr">
@@ -14178,12 +15378,17 @@
         <v>2</v>
       </c>
       <c r="E258" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F258" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G258" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F258" s="47" t="n">
+      <c r="H258" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G258" s="2" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="47" t="inlineStr">
@@ -14205,12 +15410,17 @@
         <v>1</v>
       </c>
       <c r="E259" s="47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F259" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G259" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="F259" s="47" t="n">
+      <c r="H259" s="47" t="n">
         <v>-3</v>
       </c>
-      <c r="G259" s="2" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="47" t="inlineStr">
@@ -14232,12 +15442,17 @@
         <v>11</v>
       </c>
       <c r="E260" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F260" s="47" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="G260" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G260" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H260" s="47" t="n">
+        <v>-4.4</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="46" t="inlineStr">
@@ -14262,9 +15477,14 @@
         <v>5</v>
       </c>
       <c r="F261" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G261" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G261" s="2" t="n"/>
+      <c r="H261" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="46" t="inlineStr">
@@ -14289,9 +15509,14 @@
         <v>1</v>
       </c>
       <c r="F262" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G262" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="G262" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H262" s="46" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="47" t="inlineStr">
@@ -14316,9 +15541,14 @@
         <v>0.5</v>
       </c>
       <c r="F263" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G263" s="47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H263" s="47" t="n">
         <v>-0.5</v>
       </c>
-      <c r="G263" s="2" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="47" t="inlineStr">
@@ -14340,12 +15570,17 @@
         <v>1</v>
       </c>
       <c r="E264" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F264" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G264" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F264" s="47" t="n">
+      <c r="H264" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G264" s="2" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="47" t="inlineStr">
@@ -14367,12 +15602,17 @@
         <v>2</v>
       </c>
       <c r="E265" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F265" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G265" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F265" s="47" t="n">
+      <c r="H265" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G265" s="2" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="47" t="inlineStr">
@@ -14394,12 +15634,17 @@
         <v>2</v>
       </c>
       <c r="E266" s="47" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F266" s="47" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="G266" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="G266" s="47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H266" s="47" t="n">
+        <v>-0.8</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="46" t="inlineStr">
@@ -14424,9 +15669,14 @@
         <v>5</v>
       </c>
       <c r="F267" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G267" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G267" s="2" t="n"/>
+      <c r="H267" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="46" t="inlineStr">
@@ -14451,9 +15701,14 @@
         <v>5</v>
       </c>
       <c r="F268" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G268" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="G268" s="2" t="n"/>
+      <c r="H268" s="46" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="46" t="inlineStr">
@@ -14478,9 +15733,14 @@
         <v>1</v>
       </c>
       <c r="F269" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G269" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H269" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="G269" s="2" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="47" t="inlineStr">
@@ -14502,12 +15762,17 @@
         <v>1</v>
       </c>
       <c r="E270" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F270" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G270" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F270" s="47" t="n">
+      <c r="H270" s="47" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G270" s="2" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="47" t="inlineStr">
@@ -14529,18 +15794,23 @@
         <v>2</v>
       </c>
       <c r="E271" s="47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F271" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G271" s="47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F271" s="47" t="n">
+      <c r="H271" s="47" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G271" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G39"/>
+  <autoFilter ref="A2:H39"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/historico/semana_319.xlsx
+++ b/data/historico/semana_319.xlsx
@@ -5115,7 +5115,7 @@
       </c>
       <c r="B6" s="36" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="C6" s="36" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="C7" s="36" t="inlineStr">

--- a/data/historico/semana_319.xlsx
+++ b/data/historico/semana_319.xlsx
@@ -5115,7 +5115,7 @@
       </c>
       <c r="B6" s="36" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="C6" s="36" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="C7" s="36" t="inlineStr">

--- a/data/historico/semana_319.xlsx
+++ b/data/historico/semana_319.xlsx
@@ -5137,7 +5137,7 @@
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="C7" s="36" t="inlineStr">

--- a/data/historico/semana_319.xlsx
+++ b/data/historico/semana_319.xlsx
@@ -5137,7 +5137,7 @@
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="C7" s="36" t="inlineStr">

--- a/data/historico/semana_319.xlsx
+++ b/data/historico/semana_319.xlsx
@@ -5137,7 +5137,7 @@
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="C7" s="36" t="inlineStr">

--- a/data/historico/semana_319.xlsx
+++ b/data/historico/semana_319.xlsx
@@ -5137,7 +5137,7 @@
       </c>
       <c r="B7" s="36" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="C7" s="36" t="inlineStr">

--- a/data/historico/semana_319.xlsx
+++ b/data/historico/semana_319.xlsx
@@ -5071,7 +5071,7 @@
       </c>
       <c r="B4" s="36" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="C4" s="36" t="inlineStr">
